--- a/enviando/empresas_descricoes.xlsx
+++ b/enviando/empresas_descricoes.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -469,537 +469,1265 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>expresso-nordeste</t>
+          <t>trans-acreana-turismo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Expresso Nordeste</t>
+          <t>Trans Acreana Turismo</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1963, a Expresso Nordeste é uma empresa com uma longa trajetória no setor de fretamento e turismo, atuando de forma autorizada pela ANTT (Agência Nacional de Transportes Terrestres).
-A empresa opera em diversos estados, como São Paulo, Paraná, Santa Catarina e Rio Grande do Sul, proporcionando viagens que priorizam o conforto e a segurança, conectando várias cidades por meio de roteiros eficientes.
-Sua frota é composta por ônibus de diferentes categorias, incluindo Executivo e Semi-Leito, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, para que você tenha uma experiência agradável durante suas viagens.
-Para reservar uma viagem com a Expresso Nordeste, você pode utilizar a Buser, que oferece um processo totalmente digital, combinando a tradição da empresa com a conveniência do ambiente online.</t>
+          <t>Fundada em 2009, a Trans Acreana Turismo se destaca como uma das principais empresas de fretamento e turismo no Acre, sendo reconhecida por sua tradição e a qualidade dos serviços oferecidos. Regulamentada pela ANTT, a companhia opera em rotas interestaduais de maneira segura e confiável.
+Com uma frota moderna, a Trans Acreana disponibiliza diversas categorias de veículos, que incluem opções com poltronas reclináveis, Wi-Fi via satélite e entradas USB. Isso proporciona conforto e comodidade para todos que embarcam em suas viagens.
+As principais rotas conectam a capital, Rio Branco, a várias cidades do interior do Acre e até ao Peru, o que a torna uma escolha popular para quem deseja explorar novos destinos.
+Para reservar uma viagem com a Trans Acreana, você pode contar com a Buser, uma plataforma digital que torna o processo prático e seguro, unindo a tradição da empresa à inovação no transporte.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Expresso Nordeste na Buser e desfrute de um serviço de alta qualidade.
-Especializada em fretamento e turismo, a Expresso Nordeste oferece soluções completas para grupos e eventos, com diversas rotas disponíveis em todo o Brasil.
-Ao reservar sua viagem de ônibus com a Expresso Nordeste na Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e a praticidade da remarcação, tudo para que sua experiência de viagem seja tranquila e descomplicada.</t>
+          <t>Descubra sua viagem com a Trans Acreana Turismo na Buser, desfrutando de todo o conforto e segurança que você merece.
+A Trans Acreana Turismo se dedica ao fretamento e ao turismo, apresentando roteiros incríveis que conectam várias cidades do Acre e até mesmo a famosa linha internacional para o Peru.
+Ao reservar sua viagem de ônibus da Trans Acreana Turismo na Buser, você tem à disposição um atendimento 24 horas, poltronas confortáveis e um processo de reserva online descomplicado, tudo pensado para tornar sua experiência de viagem a mais agradável possível.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>expresso-sao-luiz</t>
+          <t>anatur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Expresso São Luiz</t>
+          <t>Anatur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1950 por Abadio Pereira Cardoso, a Expresso São Luiz é uma empresa com sede em Goiânia, Goiás, que possui mais de 70 anos de experiência em fretamento e turismo, sempre em conformidade com as regulamentações da ANTT.
-Com foco na região Centro-Oeste, a empresa oferece viagens para diversos destinos em estados como Mato Grosso, Goiás, Bahia e Pernambuco, priorizando o conforto e a segurança de seus passageiros.
-A frota conta com veículos convencionais e executivos, todos equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável durante a viagem.
-Para reservar sua viagem com a Expresso São Luiz, você pode utilizar a Buser, que oferece um processo totalmente digital e seguro para facilitar sua experiência.</t>
+          <t>Fundada em 1994, a Anatur Turismo é uma empresa respeitada no setor de transporte de passageiros, atuando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres) para fretamento interestadual. Com mais de 29 anos de experiência, a Anatur se destaca pela qualidade em viagens de turismo em todo o Brasil.
+A empresa conecta diversas cidades, oferecendo roteiros personalizados e uma experiência de viagem inesquecível, sempre priorizando o conforto e a segurança dos passageiros.
+Sua frota é composta por veículos modernos, que proporcionam comodidades como ar-condicionado e poltronas reclináveis, garantindo uma viagem agradável.
+Para planejar sua viagem com a Anatur, você pode utilizar a Buser, que disponibiliza um processo 100% digital para reservar suas viagens de maneira prática e segura.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Agende sua viagem com a Expresso São Luiz através da Buser e desfrute da comodidade e segurança que o fretamento oferece.
-Com sede em Goiânia - GO, a Expresso São Luiz acumula mais de 70 anos de experiência, focando no fretamento para turismo e viagens em grupo. A empresa se destaca por oferecer serviços personalizados para várias regiões do Brasil.
-Ao escolher a Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e um processo de reserva totalmente online, o que torna sua viagem ainda mais prática e tranquila.</t>
+          <t>Reserve sua viagem com a Anatur diretamente pela Buser, aproveitando toda a praticidade que você merece.
+A Anatur se destaca no fretamento e no transporte para turismo, proporcionando soluções de mobilidade para grupos em várias regiões do Brasil.
+Ao reservar sua viagem de ônibus da Anatur na Buser, você conta com atendimento 24h, cancelamento grátis e poltronas confortáveis, o que torna sua experiência tranquila do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>viacao-sertaneja</t>
+          <t>expresso-diamante</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viação Sertaneja</t>
+          <t>Expresso Diamante</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1955, a Viação Sertaneja se destaca no setor de fretamento e turismo, atuando sob a autorização da ANTT (Agência Nacional de Transportes Terrestres). A empresa é reconhecida pela sua tradição e pelo foco na segurança e qualidade no transporte de passageiros.
-Com uma frota de mais de 163 veículos, a Viação Sertaneja conecta diversas cidades, oferecendo um serviço que prioriza conforto e eficiência. Suas rotas abrangem destinos em Minas Gerais e em outras regiões, atendendo a diversas demandas de viagem.
-A frota inclui ônibus de diferentes categorias, proporcionando comodidades como ar-condicionado e poltronas reclináveis, tudo para garantir uma experiência agradável aos passageiros.
-Para viajar com a Viação Sertaneja, você pode utilizar a plataforma da Buser, que disponibiliza um processo digital seguro e prático para reservar suas viagens de fretamento.</t>
+          <t>Fundada em 2018 em Goiânia, Goiás, a Expresso Diamante se destaca no setor de fretamento e turismo, com autorização da ANTT para operar rotas interestaduais.
+A empresa conecta cidades nas regiões Centro-Oeste, Sudeste e Sul, oferecendo trajetos como Goiânia a Curitiba, Florianópolis e São Paulo, sempre priorizando o conforto e a segurança dos passageiros.
+Sua frota moderna é composta por ônibus semi-leito e Double Decker, que contam com ar-condicionado, Wi-Fi e banheiros a bordo para uma viagem mais agradável.
+Para reservar sua viagem com a Expresso Diamante, você pode utilizar a Buser, que proporciona um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Sertaneja através da Buser e aproveite toda a conveniência que você merece. 
-A Viação Sertaneja se destaca como uma empresa especializada em fretamento e turismo, oferecendo transporte para grupos em diversas localidades. Com uma frota moderna e uma equipe capacitada, ela proporciona uma experiência de viagem confortável e segura.
-Ao escolher a Buser, você tem à disposição um atendimento 24 horas, a opção de cancelamento grátis e preços acessíveis, o que torna sua reserva prática e descomplicada.</t>
+          <t>Reserve sua viagem com a Expresso Diamante diretamente na Buser, aproveitando toda a praticidade e segurança que oferecemos.
+A Expresso Diamante, com sede em Goiânia, é especializada em fretamento para turismo e eventos, conectando várias cidades das regiões Centro-Oeste, Sudeste e Sul do Brasil.
+Ao optar por uma viagem de ônibus da Expresso Diamante na Buser, você se beneficia de atendimento 24 horas, poltronas confortáveis e a conveniência de um processo de reserva totalmente online, tornando sua experiência ainda mais satisfatória.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>cruzeiro-do-sul-transportes</t>
+          <t>galaxia-turismo</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cruzeiro do Sul Transportes</t>
+          <t>Galaxia Turismo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Fundada em junho de 1977 em Campo Grande, Mato Grosso do Sul, a Cruzeiro do Sul Transportes é uma empresa que se destaca pela sua tradição no setor de fretamento, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres).
-Com quase cinco décadas de atuação, a empresa é reconhecida pelo conforto e segurança que oferece em suas operações, conectando várias cidades do Centro-Oeste e estados vizinhos.
-A frota da Cruzeiro do Sul conta com veículos das categorias convencional e executivo, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi para tornar sua viagem ainda mais agradável.
-Para reservar sua viagem com a Cruzeiro do Sul, você pode acessar a Buser, que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada há 25 anos, a Galaxia Turismo é uma empresa de fretamento rodoviário com sede em Contagem, Minas Gerais, reconhecida por sua experiência em criar pacotes de viagem para destinos populares como Caldas Novas, Olímpia e Angra dos Reis, sempre em conformidade com as normas da ANTT.
+A empresa se destaca ao oferecer viagens em grupo, utilizando ônibus modernos que contam com serviços adicionais, como a reserva de hotéis e guias turísticos credenciados, proporcionando conforto e segurança aos passageiros.
+Sua frota é composta por veículos equipados com comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante os trajetos.
+Para viajar com a Galaxia Turismo, você pode utilizar a plataforma da Buser, que facilita um processo digital seguro e prático para reservar suas viagens.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Cruzeiro do Sul Transportes pela Buser e desfrute de toda a praticidade que você merece.
-A Cruzeiro do Sul Transportes é uma empresa consolidada no Mato Grosso do Sul, focada em fretamento para turismo e viagens em grupo. Ela oferece roteiros personalizados e experiências que ficam na memória.
-Ao agendar sua viagem de ônibus com a Cruzeiro do Sul Transportes na Buser, você tem à disposição atendimento 24h, poltronas confortáveis e a facilidade de remarcação, proporcionando uma experiência tranquila e segura do início ao fim.</t>
+          <t>Reserve sua viagem com a Galaxia Turismo pela Buser e desfrute de conforto e praticidade ao longo de sua jornada.
+A Galaxia Turismo é uma agência dedicada ao fretamento rodoviário, oferecendo pacotes de viagens em grupo para destinos incríveis como Caldas Novas, Olímpia e Porto Seguro. Além disso, disponibilizamos serviços como reserva de hotéis e guias turísticos.
+Ao agendar sua viagem de ônibus com a Galaxia Turismo na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e acessível.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gadotti-turismo</t>
+          <t>horizonte-turismo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Gadotti Turismo</t>
+          <t>Horizonte Turismo</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fundada no sul do Brasil, a Viação Gadotti é uma empresa com longa trajetória no setor de fretamento e turismo. É amplamente reconhecida pela qualidade de seu atendimento e pela segurança que oferece nas viagens, contando com autorização da ANTT para operar rotas interestaduais.
-A empresa liga diversas cidades, com ênfase nas rotas entre São Paulo e Santa Catarina, sempre prezando pelo conforto e pela organização dos viajantes.
-Sua frota inclui veículos modernos, equipados com Wi-Fi, poltronas reclináveis e ar-condicionado, proporcionando uma experiência agradável ao longo das viagens.
-Para reservar sua viagem com a Gadotti, você pode usar a Buser, que oferece um processo totalmente digital e acessível, combinando a tradição da empresa com a praticidade necessária nos dias de hoje.</t>
+          <t>Fundada em Belo Horizonte, Minas Gerais, a Horizonte Turismo é uma empresa especializada em fretamento e turismo, destacando-se no transporte de artistas e na realização de grandes eventos. Regida pela ANTT, a empresa é conhecida pela qualidade e segurança que oferece em suas viagens.
+Com uma frota de ônibus de alto padrão, incluindo modelos Double Decker, a Horizonte proporciona conforto em suas rotas de longa distância, atendendo a diversas necessidades de fretamento e excursões.
+Os veículos contam com comodidades como ar-condicionado e poltronas reclináveis, o que contribui para uma experiência agradável ao longo da viagem.
+Para reservar sua viagem com a Horizonte Turismo, você pode utilizar a Buser, um canal digital que torna o processo mais prático e seguro.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Gadotti Turismo diretamente pela Buser e aproveite a praticidade e o conforto que oferecemos.
-A Gadotti Turismo é conhecida por seus pacotes rodoviários bem planejados, que trazem segurança e tranquilidade a cada destino. Com uma frota moderna e motoristas capacitados, garantimos uma experiência de viagem de alta qualidade.
-Ao escolher a Buser, você desfruta de vantagens adicionais, como atendimento 24 horas, cancelamento grátis e poltronas confortáveis, tornando sua experiência ainda mais agradável e flexível.</t>
+          <t>Reserve sua viagem com a Horizonte Turismo na Buser, desfrutando de conforto e praticidade.
+A Horizonte Turismo se destaca no setor de fretamento e turismo, proporcionando transporte para excursões e eventos em todo o Brasil, com uma frota de ônibus de alto padrão.
+Ao fazer sua reserva de viagem com a Horizonte Turismo na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e flexível.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>arte-transportes</t>
+          <t>matriz-transportes</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Arte Transportes</t>
+          <t>Matriz Transportes</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fundada há muitos anos, a Arte Transportes é uma empresa de fretamento e turismo com sede em Porteirinha, Minas Gerais, reconhecida pela excelência em suas operações, sempre em conformidade com a regulamentação da ANTT.
-A companhia conecta diversas cidades nos estados de Minas Gerais, São Paulo e Bahia, priorizando o conforto e a segurança de seus passageiros durante as viagens.
-Sua frota conta com veículos modernos, equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, o que garante uma experiência agradável a todos a bordo.
-Para viajar com a Arte Transportes, você pode reservar suas viagens através da Buser, um canal prático e seguro que facilita o planejamento de roteiros de fretamento.</t>
+          <t>Fundada em 1992, a Matriz Transportes, com sede em Goiânia (GO), é uma empresa de transporte rodoviário de passageiros reconhecida pela sua confiabilidade e qualidade no setor, atuando em conformidade com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
+Com mais de 30 anos de experiência, a empresa se destaca pelo conforto e segurança que proporciona em suas viagens, conectando cidades como Goiânia, Cuiabá, Palmas, Porto Velho e Rio Branco.
+Sua frota é composta por diferentes categorias de veículos, oferecendo comodidades como ar-condicionado, poltronas reclináveis e wi-fi, tudo pensado para tornar a sua viagem mais agradável.
+Ao escolher viajar com a Matriz Transportes, você pode utilizar a Buser, que oferece um processo 100% digital para a compra da sua viagem, unindo tradição e praticidade.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Descubra sua viagem com a Arte Transportes na Buser, onde o conforto e a praticidade estão sempre em primeiro lugar.
-A Arte Transportes é uma empresa dedicada ao fretamento e ao turismo, com rotas que ligam Minas Gerais, São Paulo e Bahia, sempre buscando oferecer a qualidade que você espera.
-Ao reservar sua viagem de ônibus com a Arte Transportes na Buser, você tem acesso a atendimento 24 horas, remarcação simples e poltronas confortáveis, o que torna sua experiência ainda mais prazerosa.</t>
+          <t>Reserve sua viagem com a Matriz Transportes na Buser e aproveite a praticidade e segurança que oferecemos.
+A Matriz Transportes é uma empresa brasileira com sede em Goiânia, especializada no transporte rodoviário de passageiros e cargas, ligando diversas cidades nos estados de Goiás, Acre, Pará, Rondônia, Tocantins e Mato Grosso.
+Ao optar pela Buser, você vivencia uma viagem segura, com poltronas confortáveis e um processo de compra 100% online, o que facilita ainda mais a sua experiência. Além disso, nosso atendimento está disponível 24 horas, garantindo que você tenha suporte sempre que precisar.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>viacao-sete</t>
+          <t>mm-turismo</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Viação Sete</t>
+          <t>MM Turismo</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fundada em maio de 2012, a Viação Sete se destaca no setor de fretamento e turismo, oferecendo serviços autorizados pela ANTT. Com atuação nas regiões Nordeste e Centro-Oeste, a empresa estabelece conexões entre mais de 50 localidades nos estados do Piauí, Maranhão, Bahia, Goiás e no Distrito Federal.
-Com um forte compromisso com conforto e segurança, a Viação Sete realiza viagens fretadas para diversas ocasiões, como turismo, eventos corporativos, escolares, religiosos e shows.
-Sua frota é composta por diferentes categorias de veículos, que oferecem comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante a viagem.
-Para viajar com a Viação Sete, você pode reservar sua viagem de forma prática e segura através da Buser, com um processo 100% digital à sua disposição.</t>
+          <t>Fundada em Belo Horizonte (MG), a MM Turismo é uma empresa bem estabelecida no setor de fretamento e turismo, devidamente autorizada pela ANTT. Com anos de atuação, a empresa se destaca pela busca constante por conforto e segurança em suas viagens, conectando diversas cidades e destinos.
+A frota da MM Turismo conta com ônibus em diferentes categorias, oferecendo comodidades como Wi-Fi, poltronas reclináveis, ar-condicionado e sanitários, proporcionando uma experiência agradável para os passageiros.
+Para viajar com a MM Turismo, você pode reservar suas viagens de maneira prática e segura através da plataforma Buser, que disponibiliza um processo 100% digital, livre de taxas abusivas.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Sete diretamente na Buser e desfrute de conforto e segurança a cada trecho percorrido.
-A Viação Sete se dedica ao fretamento para turismo, eventos e viagens em grupo, disponibilizando serviços que interligam diversas localidades no Nordeste e Centro-Oeste do Brasil.
-Ao reservar sua viagem de ônibus da Viação Sete na Buser, você terá acesso a atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais prática e agradável.</t>
+          <t>Reserve sua viagem com a MM Turismo diretamente pela Buser e desfrute da facilidade e segurança do fretamento.
+A MM Turismo é especialista em fretamento e turismo, proporcionando soluções para excursões e viagens em grupo, sempre focada em atender às expectativas dos clientes.
+Optando pela MM Turismo na Buser, você tem à disposição poltronas confortáveis, atendimento 24 horas e a conveniência de reservar sua viagem online, tudo pensado para oferecer um deslocamento tranquilo e eficiente.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>viacao-sudeste</t>
+          <t>viacao-marlim</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Viação Sudeste</t>
+          <t>Viação Marlim</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1992, a Viação Sudeste é uma empresa de transporte rodoviário com sede em Cachoeiro de Itapemirim, Espírito Santo. Ela se destaca por sua atuação no transporte de passageiros e está regulamentada pela ANTT (Agência Nacional de Transportes Terrestres).
-A Viação Sudeste conecta diversos municípios do Sul capixaba, incluindo Cachoeiro de Itapemirim, Marataízes, Piúma, Guarapari e a capital Vitória, sempre priorizando a segurança e o conforto durante as viagens.
-Com uma frota de cerca de 85 ônibus, a empresa disponibiliza veículos bem equipados para assegurar uma experiência prazerosa ao longo do trajeto.
-Para planejar sua viagem com a Viação Sudeste, você pode contar com a Buser, que possibilita um processo totalmente digital para a compra da sua passagem, oferecendo praticidade e segurança.</t>
+          <t>Fundada na década de 1980, a Viação Marlim é uma empresa de transporte rodoviário de passageiros e cargas, com sede em Ariquemes, Rondônia. Reconhecida por sua tradição na Região Norte do Brasil, atua em conformidade com as regulamentações da ANTT.
+A Viação Marlim conecta diversas cidades nos estados de Rondônia, Mato Grosso, Goiás e Acre, oferecendo serviços de viagens intermunicipais e interestaduais, sempre com ênfase em conforto e segurança.
+Sua frota inclui ônibus convencionais, executivos e semi-leitos, todos equipados com comodidades como Wi-Fi e ar-condicionado, garantindo uma experiência agradável ao longo do trajeto.
+Para viajar com a Viação Marlim, você pode utilizar a plataforma da Buser, que facilita a compra da sua viagem de forma digital, unindo tradição e praticidade na sua mobilidade.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Garanta sua viagem de ônibus com a Viação Sudeste na Buser e aproveite toda a praticidade que você merece.
-A Viação Sudeste é uma empresa de transporte rodoviário que liga várias cidades do Sul do Espírito Santo, facilitando o deslocamento entre os municípios e a capital, Vitória.
-Optando pela Buser, você conta com atendimento 24 horas, a segurança de uma viagem tranquila e preços acessíveis, o que torna sua experiência muito mais agradável.
-Viaje com conforto e facilidade, desfrutando da conveniência de comprar sua viagem online.</t>
+          <t>Reserve sua viagem de ônibus com a Viação Marlim na Buser, com toda a praticidade e segurança que você merece.
+A Viação Marlim é uma respeitada empresa de transporte rodoviário, oferecendo viagens intermunicipais e interestaduais que conectam várias cidades nos estados de Rondônia, Mato Grosso, Goiás e Acre.
+Optar pela Viação Marlim na Buser significa desfrutar de uma viagem segura, com poltronas confortáveis e um processo de compra simples e totalmente online, tornando sua experiência ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>viacao-xavante</t>
+          <t>evt-transportes</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Viação Xavante</t>
+          <t>EVT Transportes</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1969 em Barra do Garças (MT), a Viação Xavante é uma referência no setor de fretamento, sendo regulamentada pela ANTT e reconhecida pela qualidade e atenção à segurança de seus passageiros.
-Com mais de 50 anos de experiência, a empresa conecta mais de 100 cidades em estados como Mato Grosso, Goiás, Pará, Tocantins e Maranhão, sempre com o objetivo de proporcionar conforto em suas viagens.
-Sua frota conta com ônibus das categorias Convencional e Leito, todos equipados com ar-condicionado, poltronas reclináveis e sanitário, garantindo uma experiência agradável durante os trajetos.
-Para reservar sua viagem com a Viação Xavante, você pode utilizar a Buser, que oferece um processo totalmente digital e seguro, facilitando sua jornada.</t>
+          <t>Fundada em 2015, a EVT Transportes se destaca no setor de fretamento e turismo, contando com autorização da ANTT para operar viagens interestaduais. Desde o seu início como um pequeno serviço de táxi, a empresa tem expandido suas operações, sempre priorizando o conforto e a segurança dos passageiros.
+A EVT Transportes liga diversas cidades, oferecendo serviços de fretamento para excursões e turismo, com uma frota moderna e padronizada que atende às necessidades dos viajantes.
+Os veículos são projetados para proporcionar uma experiência agradável, mesmo que não sejam fornecidos detalhes específicos sobre as categorias de ônibus.
+Para reservar sua viagem com a EVT Transportes, basta acessar a plataforma da Buser, que proporciona um processo totalmente digital e livre de taxas excessivas.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Xavante diretamente pela Buser, aproveitando toda a praticidade que você merece.
-A Viação Xavante se destaca no setor de fretamento e turismo, disponibilizando serviços de transporte para várias regiões do Brasil, sempre com conforto e segurança.
-Ao escolher a Buser, sua viagem se torna ainda mais interessante: você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, proporcionando uma experiência tranquila do início ao fim.</t>
+          <t>Reserve sua viagem com a EVT Transportes diretamente na Buser e desfrute de toda a comodidade do fretamento.
+A EVT Transportes é uma empresa dedicada ao fretamento e turismo, disponibilizando serviços de transporte para excursões e viagens fechadas, sempre priorizando o conforto e a segurança.
+Ao reservar sua viagem de ônibus da EVT Transportes na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de um processo totalmente online, o que proporciona uma experiência tranquila do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>expresso-floriano</t>
+          <t>lopes-tur</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Expresso Floriano</t>
+          <t>Lopes Tur</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2001, a Expresso Floriano se destaca no transporte rodoviário, atuando sob a regulamentação da ANTT (Agência Nacional de Transportes Terrestres) em suas operações interestaduais. Em pouco tempo, a empresa se tornou uma referência na região, especialmente no Piauí.
-Com sede em Teresina, a Expresso Floriano opera viagens para várias cidades do interior e do sul do estado, como Floriano, Bom Jesus e Canto do Buriti, sempre com foco em proporcionar conforto e segurança aos passageiros.
-Sua frota conta com ônibus semileito e leito, equipados com ar-condicionado e Wi-Fi, ideais para viagens de média e longa distância.
-Você pode adquirir suas viagens com a Expresso Floriano de forma prática e segura através da Buser, que disponibiliza um processo 100% digital, tornando a compra ainda mais simples.</t>
+          <t>Fundada em 1978, a Lopes Tur, também conhecida como Lopes Turismo e Transporte Ltda., é uma empresa de transporte rodoviário com sede em Carazinho, Rio Grande do Sul. A empresa se destaca pela qualidade e segurança em suas operações, sempre em conformidade com a regulamentação da ANTT.
+A Lopes Tur oferece viagens interestaduais que conectam o Sul ao Nordeste do Brasil. Suas rotas passam por estados como Santa Catarina, Paraná, São Paulo, Minas Gerais, Goiás, Tocantins e Maranhão, com especial atenção para a linha Carazinho-Balsas.
+A frota da Lopes Tur conta com ônibus das categorias convencional, executivo e semi-leito/leito, todos equipados com ar-condicionado e poltronas reclináveis, garantindo conforto durante a viagem.
+Para reservar sua viagem com a Lopes Tur, você pode utilizar a Buser, que proporciona um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Adquira sua viagem de ônibus da Expresso Floriano na Buser, com toda a conveniência e segurança que você procura.
-A Expresso Floriano, localizada em Teresina, no Piauí, é especializada em transporte rodoviário intermunicipal e interestadual, proporcionando viagens confortáveis para várias cidades do interior piauiense.
-Ao escolher a Buser, sua experiência se torna ainda mais satisfatória: você tem acesso a atendimento 24 horas, preços acessíveis e a facilidade de comprar ou reservar online, garantindo uma jornada tranquila e descomplicada.</t>
+          <t>Reserve sua viagem com a Lopes Tur pela Buser e experimente a praticidade do fretamento rodoviário.
+A Lopes Tur se destaca na realização de fretamentos e na organização de excursões rodoviárias, estabelecendo conexões entre o Sul e o Nordeste do Brasil, sempre priorizando o conforto e a satisfação dos passageiros.
+Ao reservar sua viagem de ônibus com a Lopes Tur na Buser, você conta com atendimento 24 horas, viagens seguras e a opção de cancelamento grátis, proporcionando uma experiência tranquila e sem imprevistos.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>primar-turismo</t>
+          <t>natal-turismo</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Primar Turismo</t>
+          <t>Natal Turismo</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2005, a Primar Turismo é uma empresa de fretamento de passageiros com sede em Botucatu, São Paulo, e é conhecida pela qualidade e conforto em seus serviços, sempre seguindo as regulamentações da ANTT (Agência Nacional de Transportes Terrestres).
-Com mais de 15 anos de experiência, a Primar Turismo oferece serviços de fretamento e excursões, ligando cidades do interior paulista a destinos incríveis no litoral do Rio de Janeiro, como Paraty e Angra dos Reis.
-A frota da empresa é composta por ônibus modernos nas categorias semi-leito, executivo e Double Decker, todos equipados com ar-condicionado, Wi-Fi, poltronas reclináveis e tomadas USB individuais.
-Por meio da plataforma Buser, você pode reservar uma viagem com a Primar Turismo de maneira prática e segura, combinando a tradição da empresa com inovações no setor.</t>
+          <t>Fundada na década de 1980, a Natal Turismo, oficialmente Transportadora Turística Natal Ltda., é uma empresa reconhecida no setor de fretamento e turismo em Mogi das Cruzes, São Paulo. Com autorização da ANTT, a empresa é conhecida pela segurança e pontualidade em suas operações.
+A Natal Turismo conecta diversas cidades do Brasil, oferecendo fretamento para empresas e viagens rodoviárias, além de aluguel de veículos para turismo, sempre com atenção ao conforto dos passageiros.
+Sua frota inclui ônibus modernos, vans e micro-ônibus, todos equipados com ar-condicionado e comodidades que tornam a viagem mais agradável.
+Os serviços da Natal Turismo estão disponíveis através da Buser, que simplifica o processo de reserva, combinando a tradição da empresa com a conveniência do ambiente digital.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Primar Turismo diretamente pelo Buser, aproveitando toda a praticidade que você busca.
-A Primar Turismo é uma empresa especializada em fretamento e turismo, proporcionando roteiros para destinos deslumbrantes, como o litoral do Rio de Janeiro.
-Ao escolher a Buser, você desfruta de ainda mais benefícios, como atendimento 24 horas, poltronas aconchegantes e a facilidade de cancelamento grátis, permitindo que sua experiência de viagem seja tranquila e confortável.</t>
+          <t>Reserve sua viagem com a Natal Turismo pela Buser, desfrutando de total comodidade e segurança.
+A Natal Turismo é especializada em fretamento e oferece transporte para empresas, excursões e aluguel de veículos para turismo, contando com uma frota moderna e bem equipada.
+Ao reservar sua viagem de ônibus com a Natal Turismo na Buser, você tem à disposição um atendimento 24 horas, poltronas confortáveis e a conveniência de um processo de reserva 100% online, proporcionando praticidade do início ao fim.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>viacao-paraibuna</t>
+          <t>star-bus</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Viação Paraibuna</t>
+          <t>Star Bus</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fundada há mais de 30 anos, a Viação Paraibuna se destaca pela qualidade e profissionalismo no fretamento e turismo, atuando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
-A empresa conecta diversas regiões de Minas Gerais e realiza trajetos em direção ao Rio de Janeiro, sempre com foco no conforto e na segurança dos passageiros.
-Sua frota é composta por veículos que contam com comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante as viagens.
-Para viajar com a Viação Paraibuna, você pode utilizar a Buser, que proporciona um processo digital seguro para reservar suas viagens, combinando tradição e praticidade.</t>
+          <t>Com mais de 20 anos de experiência, a Star Bus Turismo é uma empresa de fretamento rodoviário localizada em Uberlândia, Minas Gerais. Reconhecida no setor, a companhia atua sob a supervisão da ANTT, oferecendo serviços de fretamento intermunicipal, interestadual e internacional.
+A Star Bus liga cidades como Belo Horizonte, Uberlândia e Uberaba, sempre priorizando o conforto e a segurança durante as viagens.
+Sua frota conta com diferentes tipos de veículos, garantindo aos passageiros comodidades como Wi-Fi, poltronas reclináveis e ar-condicionado.
+Para viajar com a Star Bus, você pode reservar sua viagem pela Buser, que disponibiliza um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Paraibuna diretamente pela Buser, de forma prática e segura.
-A Viação Paraibuna se destaca no fretamento e turismo, oferecendo serviços de transporte para excursões e viagens em grupo, sempre com foco na qualidade e no conforto.
-Ao reservar sua viagem de ônibus da Viação Paraibuna na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, proporcionando uma experiência tranquila do início ao fim.</t>
+          <t>Reserve sua viagem com a Star Bus diretamente pela Buser e desfrute de conforto e segurança em cada trajeto.
+A Star Bus é especializada no fretamento de ônibus para turismo e viagens em grupo, oferecendo rotas que ligam cidades como Belo Horizonte, Uberlândia e Uberaba.
+Ao optar pela Star Bus na Buser, você se beneficia de atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples e eficiente.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>expresso-auge</t>
+          <t>viacao-pai-eterno</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>EXPRESSO AUGE</t>
+          <t>Viação Pai Eterno</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fundada em Feira de Santana, na Bahia, a Expresso Auge é uma empresa bem estabelecida no setor de fretamento e turismo, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres). Com uma forte presença em rotas interestaduais, ela conecta importantes cidades como São Paulo, Minas Gerais e Bahia.
-A Expresso Auge se destaca por oferecer serviços em ônibus nas categorias convencional, semi-leito e leito, sempre priorizando o conforto e a segurança dos passageiros durante as viagens.
-Os veículos são equipados com diversas comodidades, incluindo ar-condicionado e poltronas reclináveis, para proporcionar uma experiência agradável.
-Para reservar sua viagem com a Expresso Auge, você pode utilizar a Buser, que disponibiliza um processo totalmente digital e seguro.</t>
+          <t>Fundada em um ano que não está registrado, a Viação Pai Eterno se destaca pelo seu serviço de fretamento entre Minas Gerais e São Paulo, operando de acordo com as normas da ANTT.
+A empresa oferece conexões entre Frutal (MG) e São Paulo (SP), incluindo paradas em cidades como Fronteira (MG), Icém (SP), Nova Granada (SP), São José do Rio Preto (SP) e Campinas (SP), sempre priorizando o conforto e a segurança dos passageiros.
+Com uma frota de ônibus da categoria Semi-Leito, os viajantes desfrutam de poltronas reclináveis e espaço extra, garantindo uma experiência agradável durante toda a viagem.
+Para reservar sua viagem com a Viação Pai Eterno, você pode acessar a plataforma da Buser, que proporciona um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a EXPRESO AUGE diretamente na Buser e desfrute de praticidade e conforto.
-A EXPRESO AUGE é uma empresa focada em fretamento e turismo, ligando várias cidades, especialmente nas regiões Sudeste e Nordeste do Brasil. Você encontrará opções de transporte em ônibus convencional, semi-leito e leito.
-Ao reservar sua viagem de ônibus com a EXPRESO AUGE na Buser, você tem à disposição atendimento 24 horas, uma experiência de viagem segura e a facilidade de remarcação, o que torna tudo ainda mais tranquilo.</t>
+          <t>Reserve sua viagem com a Viação Pai Eterno diretamente pela Buser, aproveitando toda a praticidade e conforto que oferecemos.
+A Viação Pai Eterno é especializada em fretamento, proporcionando viagens personalizadas para grupos e eventos. Nossa frota de ônibus semi-leito assegura um conforto superior durante os trajetos.
+Ao reservar sua viagem de ônibus da Viação Pai Eterno na Buser, você se beneficia de atendimento 24 horas, a possibilidade de cancelamento grátis e um processo totalmente online, tornando sua experiência de viagem ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>lideranca-turismo</t>
+          <t>amado-turismo</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Liderança Turismo</t>
+          <t>Amado Turismo</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1988, a Liderança Turismo é uma empresa brasileira bem conhecida no setor de fretamento, atuando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres). Com operações nos estados de Goiás, Tocantins, Pará, Maranhão e no Distrito Federal, a empresa se destaca pela excelência em serviços de viagem.
-Dispomos de uma frota diversificada, que inclui ônibus convencionais, executivos e leitos, todos equipados com comodidades como Wi-Fi e ar-condicionado, proporcionando conforto e segurança aos passageiros.
-A Liderança Turismo conecta cidades importantes e oferece experiências de viagem memoráveis a seus clientes. Para facilitar suas reservas, a empresa está presente na plataforma Buser, que proporciona um processo totalmente digital, unindo tradição e praticidade.</t>
+          <t>Fundada em 2010, a Amado Turismo é uma empresa bem reconhecida no setor de transporte rodoviário de passageiros, operando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres). O que a destaca é a oferta de serviços tanto de linhas regulares quanto de fretamento para turismo, conectando importantes cidades de Goiás, Tocantins e Maranhão.
+Sua frota é composta por ônibus convencionais que priorizam o conforto e a segurança dos viajantes. Os veículos contam com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante as viagens.
+Você pode adquirir sua passagem de forma prática e digital na plataforma da Buser, que torna o processo de compra e reserva muito mais fácil.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Liderança Turismo diretamente pela Buser, aproveitando conforto e praticidade.
-A Liderança Turismo é uma empresa brasileira dedicada ao fretamento e ao turismo, oferecendo serviços de transporte rodoviário em diversos estados, como Goiás e Tocantins, com ônibus que proporcionam conforto e qualidade.
-Ao reservar sua viagem de ônibus da Liderança Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a opção de cancelamento grátis, assegurando uma experiência tranquila do começo ao fim.</t>
+          <t>Adquira sua passagem de ônibus da Amado Turismo por meio da Buser e desfrute de uma experiência prática e segura.
+A Amado Turismo opera linhas regulares de ônibus e também realiza fretamento para excursões, oferecendo transporte entre várias regiões do Brasil, como Goiás, Tocantins e Maranhão.
+Optar pela Buser significa contar com atendimento 24 horas, garantindo suporte sempre que necessário. A possibilidade de remarcação e os preços acessíveis tornam sua viagem ainda mais conveniente e fácil.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="120" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>luxor</t>
+          <t>belos-montes-viagens</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Luxor</t>
+          <t>Belos Montes Viagens</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fundada há 11 anos em Natal, RN, a Luxor Viagens e Turismo se destaca no setor de fretamento e turismo, sendo autorizada pela ANTT para operar viagens interestaduais.
-Com um compromisso com o conforto e a segurança, a Luxor conecta uma variedade de destinos e oferece serviços personalizados de fretamento para grupos e eventos.
-Sua frota é composta por veículos variados, equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável ao longo das viagens.
-Os serviços da Luxor podem ser reservados através da Buser, que oferece um processo 100% digital, combinando tradição e praticidade para facilitar o planejamento da sua viagem.</t>
+          <t>Fundada em 2013 em Montes Claros, Minas Gerais, a Belos Montes Viagens se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres).
+A empresa é especialista em fretamento contínuo e eventual, conectando Montes Claros a destinos importantes como Belo Horizonte e Brasília. Além disso, oferece pacotes turísticos para lugares como Porto Seguro, Aparecida e Maceió.
+Sua frota conta com ônibus modernos, incluindo modelos de dois andares e veículos das categorias leito e semi-leito, proporcionando conforto em todas as viagens.
+Para reservar sua viagem com a Belos Montes Viagens, você pode usar a Buser, que disponibiliza um processo totalmente digital, tornando mais fácil encontrar os serviços de fretamento que você precisa.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Explore Luxor, o maior museu ao ar livre do mundo! Esta cidade egípcia, famosa por suas impressionantes ruínas e templos, como os do Vale dos Reis, é um destino que não pode faltar na lista dos apaixonados por história. Ao escolher a Buser, você terá uma viagem segura e confortável, com preços que realmente cabem no seu bolso. Reserve sua passagem online de maneira simples e aproveite a tranquilidade do cancelamento grátis e da remarcação fácil. Não deixe passar a chance de descobrir a fascinante herança do Egito. Adquira sua passagem agora e embarque nessa aventura inesquecível!</t>
+          <t>Reserve sua viagem com a Belos Montes Viagens diretamente pela Buser, onde conforto e praticidade se encontram.
+A Belos Montes Viagens é uma empresa dedicada ao fretamento e turismo, disponibilizando pacotes para destinos populares e excursões em grupo, sempre com ônibus modernos e confortáveis.
+Ao optar pela Buser, você conta com uma experiência de viagem segura e tranquila, com atendimento 24 horas e a vantagem do cancelamento grátis, o que torna cada deslocamento mais flexível e acessível.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>penedo-turismo</t>
+          <t>sao-jose-viagens</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Penedo Turismo</t>
+          <t>São José Viagens</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A Penedo Turismo, uma referência no setor de fretamento, oferece serviços de viagem desde sua fundação, sempre operando com autorização da ANTT. A empresa se destaca por suas conexões turísticas, tornando a experiência de viajar para diversos destinos muito mais acessível e agradável.
-Com uma frota diversificada, a Penedo Turismo assegura conforto e segurança em cada viagem, utilizando ônibus equipados com ar-condicionado e poltronas reclináveis. A companhia conecta cidades estratégicas, proporcionando viagens relaxantes e confortáveis.
-Ao planejar sua viagem, a Penedo Turismo se junta à Buser como parceira oficial, permitindo que os clientes reservem suas viagens de maneira prática e segura, através de um processo totalmente digital.</t>
+          <t>Fundada há quase 80 anos em Belo Horizonte, a São José Viagens é uma operadora de destaque, conhecida por sua tradição em fretamento e turismo, e possui autorização da ANTT para realizar operações interestaduais.
+A empresa se diferencia ao oferecer viagens em grupo, priorizando conforto e segurança, enquanto conecta diversas rotas e destinos tanto dentro quanto fora de Minas Gerais.
+Com uma frota variada, a São José Viagens disponibiliza veículos equipados com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência agradável durante as viagens.
+Para viajar com a São José Viagens, você pode reservar diretamente pelo canal digital da Buser, que oferece um processo totalmente online e livre de taxas excessivas.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Descubra sua viagem com a Penedo Turismo diretamente pela Buser, aproveitando toda a conveniência que você merece.
-A Penedo Turismo é especializada em fretamento e turismo, oferecendo serviços de transporte para excursões e viagens em grupo, sempre com qualidade e eficiência.
-Ao reservar sua viagem de ônibus da Penedo Turismo na Buser, você conta com atendimento 24 horas, preços acessíveis e poltronas confortáveis, o que proporciona uma experiência tranquila e agradável.</t>
+          <t>Reserve sua viagem com a São José Viagens diretamente na Buser e desfrute de toda a comodidade e segurança que oferecemos.
+A São José Viagens é uma respeitada operadora e agência de turismo com sede em Belo Horizonte, focada em excursões e viagens em grupo, apresentando roteiros tanto nacionais quanto internacionais.
+Ao fazer sua reserva de viagem de ônibus com a São José Viagens na Buser, você tem à disposição atendimento 24 horas, facilidade na remarcação e poltronas confortáveis, tornando seu trajeto relaxante e agradável.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="120" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>turissul</t>
+          <t>expresso-satelite-norte</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Turissul</t>
+          <t>EXPRESSO SATELITE NORTE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2000, a Turissul é uma renomada empresa de fretamento e turismo, autorizada pela ANTT e com sede em Tubarão, Santa Catarina. Com mais de vinte anos de experiência, a empresa se destaca na realização de viagens voltadas para turismo, compras e eventos.
-A Turissul conecta diversas cidades e oferece roteiros que incluem destinos populares como São Paulo e Arraial do Cabo, sempre priorizando o conforto e a segurança de seus passageiros.
-Sua frota conta com ônibus leito e semi-leito, equipados com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência agradável durante a viagem.
-Para reservar sua viagem com a Turissul, você pode utilizar a Buser, que oferece um processo 100% digital e seguro, unindo a tradição da empresa com a praticidade moderna.</t>
+          <t>Fundada em fevereiro de 1996, a Expresso Satélite Norte se destaca no setor de transporte rodoviário, sendo reconhecida pela qualidade e segurança de seus serviços, sempre em conformidade com as regulamentações da ANTT (Agência Nacional de Transportes Terrestres).
+A empresa oferece conexões entre diversos estados nas regiões Centro-Oeste, Norte e Nordeste do Brasil, com foco em viagens de longa distância que priorizam o conforto. Você pode escolher entre opções de ônibus Executivo, Leito e Leito-Cama, todas projetadas para proporcionar uma experiência agradável.
+Com uma frota moderna equipada com poltronas reclináveis, a Expresso Satélite Norte também disponibiliza serviços de encomendas e fretamento, ampliando suas possibilidades de transporte.
+Para tornar sua experiência ainda mais prática, a Expresso Satélite Norte está integrada à plataforma da Buser, permitindo que você reserve seu fretamento de forma 100% digital e segura.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Turissul diretamente na Buser e aproveite a praticidade e o conforto que você merece.
-A Turissul é uma empresa especializada em fretamento e turismo, oferecendo roteiros para compras, turismo religioso e eventos, sempre com veículos confortáveis e seguros.
-Ao reservar sua viagem de ônibus da Turissul na Buser, você tem à disposição atendimento 24 horas, a opção de cancelamento grátis e a facilidade de fazer sua reserva online, o que torna sua experiência ainda mais simples e acessível.</t>
+          <t>Reserve sua viagem com o Expresso Satélite Norte na Buser e desfrute de conforto e praticidade.
+O Expresso Satélite Norte se especializa em fretamento e turismo, disponibilizando roteiros que conectam diversas regiões do Brasil, incluindo o Centro-Oeste, Norte e Nordeste.
+Optar pela Buser significa embarcar em uma viagem segura, com poltronas confortáveis e atendimento 24 horas, o que torna sua experiência ainda mais prazerosa.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>viacao-arca</t>
+          <t>jc-turismo</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Viação Arca</t>
+          <t>JC Turismo</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 22 de outubro de 1996, a Viação Arca se destaca no setor de fretamento e turismo, com autorização da ANTT (Agência Nacional de Transportes Terrestres) para operar em rotas interestaduais.
-A empresa tem como prioridade oferecer conforto e segurança, ligando importantes cidades e regiões, especialmente na Grande São Paulo. Com mais de 25 anos de experiência, a Viação Arca é reconhecida pela qualidade no transporte de passageiros.
-A frota da Viação Arca conta com veículos convencionais e executivos, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável durante suas viagens.
-Para viajar com a Viação Arca, você pode utilizar a Buser, que disponibiliza um processo digital para reservas, garantindo segurança e praticidade ao planejar sua viagem.</t>
+          <t>Fundada em 1994 e situada em Valinhos, São Paulo, a JC Turismo se destaca no segmento de fretamento e transporte rodoviário, operando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres). A empresa é conhecida pela eficiência e qualidade de suas operações, oferecendo serviços de fretamento contínuo e eventual para eventos e excursões.
+A frota da JC Turismo conta com ônibus e micro-ônibus, priorizando sempre o conforto e a segurança dos passageiros. Os veículos são equipados para proporcionar uma experiência agradável, tanto em trajetos municipais quanto intermunicipais.
+Para viajar com a JC Turismo, você pode reservar suas viagens pela plataforma Buser, que oferece um processo totalmente digital e seguro, combinando tradição e inovação na mobilidade.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Arca diretamente pela Buser e aproveite a praticidade e o conforto que oferecemos.
-A Viação Arca se destaca no fretamento e turismo, disponibilizando uma gama de roteiros que ligam importantes cidades e regiões, perfeita para grupos e excursões.
-Optando pela Viação Arca na Buser, você tem acesso a atendimento 24 horas, cancelamento grátis e poltronas confortáveis, tudo para tornar sua viagem mais agradável e segura.</t>
+          <t>Reserve sua viagem com a JC Turismo diretamente na Buser e desfrute de uma experiência prática e segura.
+A JC Turismo é uma empresa dedicada ao fretamento empresarial e ao turismo, oferecendo serviços de transporte rodoviário para excursões e eventos, sempre priorizando o conforto dos passageiros.
+Ao escolher a Buser, você tem à disposição uma viagem segura, poltronas confortáveis e atendimento 24 horas, o que torna sua experiência mais tranquila e acessível.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>jamjoy-viacao</t>
+          <t>marlim-azul-turismo</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Jamjoy Viação</t>
+          <t>Marlim Azul Turismo</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fundada como pioneira no transporte rodoviário do norte do Tocantins, a Jamjoy Viação se destaca por sua tradição e pela atenção à segurança e ao conforto dos passageiros. A empresa é autorizada pela ANTT, o que assegura a regulamentação de suas operações interestaduais.
-Com uma operação consolidada, a Jamjoy conecta diversos destinos na região, sempre priorizando qualidade e eficiência em seus serviços.
-Sua frota é composta por veículos modernos, que oferecem comodidade durante as viagens, com recursos como ar-condicionado e poltronas reclináveis.
-Os passageiros podem realizar suas viagens com a Jamjoy Viação através da Buser, desfrutando de um processo totalmente digital e seguro para a aquisição de suas passagens.</t>
+          <t>Fundada em 2000, a Marlim Azul se destacou no setor de fretamento e turismo no Espírito Santo, sendo reconhecida pela ANTT. Com 25 anos de trajetória, a empresa se firmou como uma referência em viagens de turismo e fretamento.
+A Marlim Azul prioriza o conforto e a segurança, conectando diversas cidades e destinos tanto dentro do estado quanto em rotas interestaduais, sempre buscando atender às expectativas dos passageiros.
+Sua frota é composta por ônibus equipados com climatização, poltronas confortáveis e tecnologia de ponta, proporcionando uma experiência agradável ao longo de toda a viagem.
+Para reservar sua viagem com a Marlim Azul, você pode utilizar a plataforma da Buser, que oferece um processo 100% digital e seguro, unindo tradição e inovação na experiência de fretamento.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem de ônibus com a Jamjoy Viação na Buser e aproveite conforto e praticidade.
-A Jamjoy Viação é uma empresa renomada no transporte rodoviário, operando tanto em linhas regulares quanto em fretamento, e proporcionando conexões entre diversos destinos no Brasil.
-Ao fazer sua reserva pela Buser, você pode contar com uma experiência tranquila, que inclui poltronas confortáveis, cancelamento grátis e atendimento 24 horas para esclarecer qualquer dúvida ao longo da sua jornada.</t>
+          <t>Descubra sua próxima viagem com a Marlim Azul Turismo através da Buser, garantindo o conforto que você merece.
+A Marlim Azul Turismo se destaca no fretamento e turismo, proporcionando experiências inesquecíveis em viagens de grupo pelo Brasil e no exterior, tudo isso com uma frota moderna e segura.
+Ao reservar sua viagem de ônibus com a Marlim Azul Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples e prático, tornando sua experiência ainda mais agradável e descomplicada.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="120" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>jbl-turismo</t>
+          <t>marlu-turismo</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>JBL Turismo</t>
+          <t>Marlu Turismo</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 31 de agosto de 2007, a JBL Turismo se destaca no setor de transporte rodoviário, com autorização da ANTT, e atua em rotas tanto nacionais quanto internacionais. 
-Com sede em Canoas (RS), a empresa possui mais de 15 anos de experiência, dedicando-se a viagens de fretamento e turismo, que conectam o Sul do Brasil a destinos na Argentina, Chile e Uruguai. 
-Sua frota conta com veículos modernos, equipados com ar-condicionado, poltronas reclináveis e sanitários, proporcionando um ambiente confortável durante as viagens.
-Ao escolher viajar com a JBL Turismo, você pode reservar sua viagem de maneira prática e segura por meio da Buser, que disponibiliza um processo totalmente digital.</t>
+          <t>Com mais de 20 anos de experiência, a Marlu Turismo se destaca como uma empresa de fretamento e turismo no Brasil, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres).
+Localizada em Duque de Caxias, no estado do Rio de Janeiro, a Marlu oferece uma variedade de opções para viagens de turismo interestadual, incluindo passeios em grupo e eventos religiosos, conectando diferentes cidades e destinos.
+A frota da Marlu Turismo é composta por veículos modernos, como os ônibus de dois andares Marcopolo Paradiso G8 DD, que contam com ar-condicionado e poltronas reclináveis, proporcionando uma experiência confortável durante as viagens.
+Para facilitar a reserva da sua viagem, a Marlu Turismo é parceira da Buser, possibilitando um processo 100% digital e seguro, ideal para quem valoriza praticidade ao reservar fretamento.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a JBL Turismo através da Buser e desfrute da praticidade e segurança que você busca.
-Especializada em fretamento e turismo, a JBL Turismo oferece uma vasta seleção de roteiros que vão do Sul ao Sudeste do Brasil, além de opções internacionais.
-Optando pela Buser, você conta com atendimento 24 horas, cancelamento grátis e poltronas confortáveis, proporcionando uma experiência de viagem tranquila e satisfatória.</t>
+          <t>Reserve sua viagem com a Marlu Turismo diretamente na Buser e aproveite a combinação de conforto e praticidade.
+Com mais de 20 anos de experiência, a Marlu Turismo se destaca no fretamento e turismo, oferecendo transporte para passeios, eventos e viagens em grupo.
+Ao optar por reservar sua viagem de ônibus da Marlu Turismo na Buser, você tem acesso a um atendimento 24h, poltronas confortáveis e um processo de reserva totalmente online, tornando sua experiência de viagem mais simples e agradável do início ao fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>nobre-empresa</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Nobre Empresa</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há mais de 9 anos, a Nobre Empresa se destaca no setor de fretamento e turismo, com a autorização da ANTT para operar viagens interestaduais de forma segura e de alta qualidade.
+A empresa conecta diversas cidades, sempre buscando proporcionar conforto e eficiência aos seus clientes durante as viagens, atendendo tanto o setor corporativo quanto grupos de turismo.
+A frota da Nobre é composta por veículos modernos, que contam com Wi-Fi, poltronas reclináveis e ar-condicionado, assegurando uma experiência agradável e confortável para os viajantes.
+Para realizar sua viagem com a Nobre, você pode reservar de maneira prática através da Buser, o que torna o processo digital seguro e ágil.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Nobre Empresa diretamente pela Buser e desfrute de conforto e praticidade.
+A Nobre Empresa se destaca no fretamento de veículos para grupos, oferecendo soluções de transporte personalizadas para eventos, excursões e viagens.
+Ao reservar sua viagem de ônibus com a Nobre Empresa na Buser, você tem acesso a um atendimento 24h, poltronas confortáveis e a conveniência de realizar tudo online, sem complicações.
+Descubra a segurança e a eficiência que a Buser traz para suas viagens em grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>vanzella-transportes</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vanzella Transportes</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Com mais de 20 anos de experiência, a Vanzella Transportes é uma empresa brasileira reconhecida pela sua atuação no setor de fretamento e turismo, devidamente regulamentada pela ANTT.
+A atuação da empresa é concentrada em Mato Grosso do Sul, onde proporciona serviços de transporte tanto compartilhado quanto privativo. Isso inclui conexões do Aeroporto Internacional de Campo Grande a destinos turísticos como Bonito e Serra da Bodoquena.
+Sua frota é diversificada, contando com vans para 15 passageiros, micro-ônibus para 26 e ônibus semi-leito ou leito, assegurando um alto nível de conforto durante suas viagens.
+Para planejar sua viagem com a Vanzella, você pode fazer a reserva através da Buser, que oferece um processo digital simples e seguro.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Vanzella Transportes diretamente pela Buser e aproveite todo o conforto e a praticidade que oferecemos.
+A Vanzella Transportes se destaca no setor de fretamento e turismo, proporcionando serviços de transporte compartilhado e privativo entre Campo Grande e destinos turísticos como Bonito.
+Com a Buser, sua experiência de viagem se torna ainda mais agradável, contando com atendimento 24 horas, poltronas confortáveis e a facilidade de realizar reservas online de maneira descomplicada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>expresso-joia</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>EXPRESSO JOIA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Fundada na década de 1970 em Ibaití, no Paraná, a Expresso Jóia, anteriormente chamada de Viação Jóia, é uma empresa de transporte rodoviário de destaque, autorizada pela ANTT para operações interestaduais.
+Com mais de quarenta anos de experiência, a Expresso Jóia se destaca no fretamento de viagens turísticas, ligando cidades importantes entre os estados de São Paulo e Paraná, sempre priorizando a segurança e a qualidade dos serviços.
+A frota conta com veículos modernos, nas categorias executivo e leito, que vêm equipados com ar-condicionado e poltronas reclináveis, proporcionando conforto durante toda a viagem.
+Os interessados podem reservar suas viagens com a Expresso Jóia por meio da Buser, que oferece um processo totalmente digital, combinando praticidade com a tradição da empresa.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Expresso Jóia diretamente pela Buser e desfrute de conforto e praticidade na sua escolha.
+A Expresso Jóia se destaca no fretamento de passageiros, conectando várias cidades nos estados de São Paulo e Paraná, com opções ideais para grupos e turismo.
+Ao reservar sua viagem de ônibus da Expresso Jóia na Buser, você conta com atendimento 24 horas, uma experiência de viagem segura e a facilidade de remarcação, tornando seu planejamento muito mais tranquilo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>expresso-solucao</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Expresso Solução</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 13 de agosto de 2020 em Brasília, a Expresso Solução Transportes e Turismo se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT.
+A empresa liga o Distrito Federal a importantes cidades de Minas Gerais, como Montes Claros e Pirapora, sempre colocando o conforto e a segurança dos passageiros em primeiro lugar.
+Sua frota conta com ônibus equipados com ar-condicionado, assentos reclináveis e Wi-Fi, proporcionando uma viagem agradável e tranquila.
+As viagens com a Expresso Solução podem ser reservadas por meio da Buser, que oferece um processo digital prático e seguro para os usuários.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Expresso Solução diretamente na Buser, de forma simples e confiável.
+A Expresso Solução é uma empresa especializada em fretamento e turismo, ligando o Distrito Federal a diversas cidades de Minas Gerais e Goiás, sempre com foco no conforto e na segurança das rotas.
+Ao escolher a Buser, você encontra ainda mais vantagens, como atendimento disponível 24 horas, cancelamento grátis e poltronas confortáveis, permitindo que você relaxe e desfrute do trajeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>grandino-turismo</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Grandino Turismo</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 2021, a Grandino Turismo se destaca no setor de fretamento e viagens turísticas no Brasil, com operações regulamentadas pela ANTT (Agência Nacional de Transportes Terrestres). A empresa é bem vista por sua confiabilidade e pela qualidade dos serviços oferecidos.
+A Grandino Turismo atende diversas regiões, priorizando conforto e segurança, e conecta cidades em São Paulo e arredores, como Guarulhos e Itaquaquecetuba.
+Sua frota moderna conta com ônibus executivos, Semi-Leito e Double Deck, todos equipados com ar-condicionado, Wi-Fi, entradas USB, poltronas reclináveis e geladeiras a bordo.
+Os serviços de fretamento da Grandino Turismo podem ser reservados na Buser, proporcionando um processo totalmente digital e prático para suas viagens.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Grandino Turismo diretamente pela Buser e aproveite a praticidade e segurança que oferecemos.
+A Grandino Turismo se destaca no fretamento e nas viagens turísticas, proporcionando transporte de passageiros para várias regiões do Brasil com conforto e eficiência.
+Ao fazer sua reserva com a Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade do cancelamento grátis, o que torna sua experiência ainda mais agradável e despreocupada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>helios-empresa</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Helios Empresa</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Fundada na década de 1940 em Carazinho, no Rio Grande do Sul, a Helios é uma empresa tradicional no setor de fretamento e turismo, além de atuar em conexões interestaduais regularizadas pela ANTT.
+Com mais de 75 anos de experiência, a Helios se destaca pela segurança e conforto, operando rotas que conectam as regiões Sul, Sudeste, Centro-Oeste e Norte do Brasil.
+Sua frota é composta por ônibus convencionais, semi-leito e leito, todos equipados com poltronas acolchoadas, ar-condicionado e Wi-Fi, o que garante uma experiência agradável ao longo da viagem.
+Você pode reservar suas viagens pela Buser, que oferece um processo 100% digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Helios diretamente pela Buser e aproveite a facilidade do fretamento.
+A Helios é uma empresa brasileira com tradição no transporte rodoviário, focada em fretamento e turismo, e possui uma presença marcante em rotas intermunicipais e interestaduais.
+Ao reservar sua viagem de ônibus da Helios na Buser, você desfruta da tranquilidade de um atendimento disponível 24 horas, da conveniência de um processo de reserva online e de poltronas confortáveis, tudo pensado para tornar sua experiência mais agradável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>jr-turismo-empresa</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>JR Turismo Empresa</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 2015, a JR Turismo se destaca no setor de fretamento e turismo, sendo reconhecida pela segurança e conforto que proporciona aos seus clientes. A empresa opera em conformidade com as normas da ANTT, assegurando a qualidade no serviço de transporte.
+Com um foco especial em viagens intermunicipais e interestaduais, a JR Turismo conecta diversas cidades e oferece roteiros personalizados para passeios e excursões.
+Sua frota é composta por ônibus, micro-ônibus e vans, todos equipados com comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante a viagem.
+Para viajar com a JR Turismo, você pode reservar sua viagem através da Buser, uma plataforma digital que torna o processo de fretamento mais simples, unindo tradição e praticidade.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a JR Turismo na Buser e desfrute da praticidade e segurança que você realmente merece.
+A JR Turismo é especialista no fretamento de vans, micro-ônibus e ônibus para viagens intermunicipais e interestaduais, oferecendo serviços de alta qualidade voltados para grupos e excursões.
+Ao reservar sua viagem de ônibus da JR Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, tudo isso para proporcionar uma experiência de viagem mais tranquila e conveniente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>levare-transportes</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Levare Transportes</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em um ano não especificado, a Levare Transportes é uma empresa brasileira de transporte rodoviário de passageiros, autorizada pela ANTT, e é reconhecida por oferecer um serviço de qualidade.
+A Levare tem como prioridade o conforto, conectando importantes cidades do estado de São Paulo, como São Paulo, São José do Rio Preto e Ribeirão Preto, a destinos como Rio de Janeiro, Brasília e Belo Horizonte.
+Sua frota é composta por ônibus leito-cama, equipados com poltronas reclináveis, Wi-Fi, tomadas e serviço de bordo, proporcionando uma experiência agradável durante a viagem.
+Os passageiros podem adquirir suas viagens pela Buser, um canal digital que torna o processo de compra mais seguro e prático.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Levare Transportes diretamente na Buser e desfrute da qualidade que você merece.
+A Levare Transportes é uma empresa brasileira que se destaca por oferecer viagens de alto padrão, utilizando ônibus leito-cama e proporcionando um serviço diferenciado em rotas que ligam importantes cidades.
+Ao escolher a Buser, você tem a tranquilidade de contar com uma viagem segura, poltronas confortáveis e a praticidade de adquirir sua passagem online de forma rápida e simples. E, para completar, o atendimento 24 horas está sempre à disposição para auxiliar em qualquer necessidade que você possa ter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>roderotas</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>RodeRotas</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Com mais de 50 anos de história, a RodeRotas, também conhecida como Rotas de Viação do Triângulo, é uma empresa brasileira que atua no transporte rodoviário de passageiros, sempre em conformidade com as diretrizes da ANTT (Agência Nacional de Transportes Terrestres).
+A companhia é reconhecida por sua conexão entre cidades como Brasília, Belém, Goiânia, São Paulo, Foz do Iguaçu e Uberlândia, oferecendo viagens de longa e média distância. O foco em segurança e conforto para os passageiros é uma das suas marcas registradas.
+A frota da RodeRotas é equipada com veículos que priorizam o bem-estar dos viajantes, disponibilizando comodidades como ar-condicionado e poltronas reclináveis, o que contribui para uma experiência agradável ao longo da viagem.
+Para reservar sua viagem com a RodeRotas, você pode utilizar a Buser, que proporciona um processo de compra totalmente digital, combinando tradição e praticidade na sua mobilidade.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem de ônibus da RodeRotas na Buser e viaje com conforto e segurança.
+A RodeRotas é uma reconhecida empresa de transporte rodoviário de passageiros, atuando principalmente em trajetos de longa e média distância, ligando grandes cidades do Brasil, como Brasília, São Paulo e Foz do Iguaçu.
+Ao optar pela Buser, você usufrui de uma viagem segura, poltronas confortáveis e a praticidade de um processo de compra totalmente online, proporcionando uma experiência tranquila do início ao fim da sua jornada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>scatur-empresa</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Scatur Empresa</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em Tietê, São Paulo, a Scatur se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT. Priorizando a segurança e o conforto, a empresa oferece transporte planejado para eventos, fretamento empresarial e viagens escolares, conectando várias cidades do interior paulista, como Sumaré e Indaiatuba.
+A frota da Scatur é variada, contando com ônibus, micro-ônibus e vans, todos equipados com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma viagem agradável.
+Os serviços de viagem da Scatur podem ser reservados de maneira prática e segura por meio da Buser, que disponibiliza um processo digital eficiente.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Scatur pela Buser e desfrute de praticidade e segurança.
+A Scatur se destaca no fretamento para turismo, além de oferecer serviços de transporte escolar e empresarial, com soluções adaptadas às diversas necessidades de deslocamento.
+Ao garantir sua viagem de ônibus da Scatur na Buser, você tem acesso a atendimento 24 horas, uma experiência de viagem segura e a conveniência da remarcação, que torna seus planos ainda mais flexíveis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>actur-viagens</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Actur Viagens</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em Belo Horizonte, Minas Gerais, a Actur Viagens é uma empresa que se especializa no fretamento de veículos para turismo e eventos. Com autorização da ANTT, a empresa se destaca pela sua confiabilidade e pela qualidade no transporte rodoviário.
+Com anos de experiência no setor, a Actur oferece serviços que abrangem transporte corporativo e turismo, realizando viagens em grupo, city tours e traslados para eventos. A empresa conecta diversas cidades, garantindo uma experiência de viagem memorável.
+Sua frota é composta por ônibus, micro-ônibus, vans e carros executivos, todos projetados para proporcionar conforto e segurança durante os trajetos.
+A Actur Viagens está disponível na Buser, permitindo que você reserve suas viagens de maneira prática e segura, através de um processo totalmente digital.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Actur Viagens diretamente na Buser e tenha praticidade para todos os destinos.
+Especializada em fretamento e turismo, a Actur Viagens oferece transporte para eventos, excursões e traslados na região de Belo Horizonte.
+Ao reservar sua viagem de ônibus com a Actur Viagens na Buser, você desfruta de atendimento 24 horas, poltronas confortáveis e a facilidade de cancelar sem custos.
+Aproveite a flexibilidade e a segurança que a Buser proporciona, tornando sua experiência de viagem ainda mais tranquila e acessível.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>centauro-turismo</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Centauro Turismo</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 30 de agosto de 1989, a Centauro Turismo, localizada em Belo Horizonte (MG), é uma empresa bem reconhecida no ramo de fretamento e turismo, operando com a autorização da ANTT (Agência Nacional de Transportes Terrestres).
+A Centauro Turismo se destaca pela variedade de serviços de aluguel de ônibus, micro-ônibus e vans, atendendo a necessidades de viagens corporativas, excursões e eventos, conectando diversas cidades em Minas Gerais e regiões adjacentes.
+Sua frota moderna conta com ônibus executivos, semi-leitos e modelos Double-Decker, todos equipados com ar-condicionado e poltronas reclináveis, proporcionando um agradável conforto durante a viagem.
+Para reservar sua viagem com a Centauro Turismo, você pode utilizar a Buser, um canal oficial que oferece um processo totalmente digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Centauro Turismo pela Buser e explore destinos incríveis com todo o conforto e segurança.
+A Centauro Turismo se destaca no fretamento e aluguel de ônibus, vans e micro-ônibus, atendendo a diversas necessidades como excursões, eventos e traslados especiais. Além disso, oferece pacotes turísticos feitos sob medida para você.
+Ao optar pela Buser, você desfruta de uma experiência prática e econômica, com atendimento disponível 24 horas, poltronas confortáveis e a flexibilidade de cancelamento grátis, proporcionando tranquilidade do início ao fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>mactur-fretamentos</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Mactur Fretamentos</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 1990, a Mactur Fretamentos e Turismo está localizada em Valinhos, São Paulo, e possui mais de 30 anos de experiência no setor de transporte rodoviário, sendo regulamentada pela ANTT para operações interestaduais.
+A empresa oferece serviços de fretamento contínuo e eventual, conectando diversas cidades e destinos pelo Brasil, sempre priorizando o conforto e a segurança durante as viagens.
+Sua frota variada inclui ônibus convencionais, micro-ônibus e modelos Double Decker, todos com comodidades como ar-condicionado e Wi-Fi para garantir uma experiência agradável.
+Para viajar com a Mactur, você pode reservar diretamente pelo site da Buser, o que proporciona um processo totalmente digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Mactur Fretamentos diretamente pela Buser, onde você encontra comodidade e segurança.
+A Mactur Fretamentos e Turismo é uma empresa brasileira com mais de 30 anos de experiência, focada no fretamento de ônibus e no transporte para excursões e viagens em grupo, atuando em todo o Brasil.
+Ao realizar a reserva de sua viagem de ônibus com a Mactur Fretamentos na Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e a facilidade de cancelamento grátis, o que torna sua experiência ainda mais agradável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>mf-turismo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>MF Turismo</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Com mais de 15 anos de experiência, a MF Turismo é uma empresa respeitada no setor de fretamento e turismo, devidamente regulamentada pela ANTT para operar em rotas interestaduais.
+Focada em proporcionar experiências de viagem, tanto para turismo quanto para fretamentos empresariais, a empresa conecta diversas cidades, como Votuporanga e São José do Rio Preto, sempre com ênfase em conforto e segurança.
+A frota da MF Turismo conta com ônibus de grande porte, incluindo modelos Double Decker e semi-leito, que oferecem comodidades como ar-condicionado e poltronas reclináveis para uma viagem mais agradável.
+Para planejar sua viagem com a MF Turismo, você pode reservar pelo canal digital da Buser, que torna o processo simples e seguro.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a MF Turismo diretamente na Buser, desfrutando de praticidade e segurança.
+A MF Turismo se destaca como uma empresa especializada em fretamento e turismo, proporcionando transporte de passageiros para uma variedade de rotas. Sua frota é composta por ônibus de grande porte, micro-ônibus e vans, atendendo diferentes necessidades.
+Ao optar por uma viagem de ônibus da MF Turismo na Buser, você tem à disposição atendimento 24h, poltronas confortáveis e a facilidade de remarcação, assegurando uma experiência tranquila do início ao fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>paraquett-turismo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Paraquett Turismo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há quase cinco anos, a Paraquett Turismo, com sede em Cabo Frio (RJ), se destaca no fretamento de ônibus, prestando serviços para excursões, eventos corporativos e transferências. A empresa é autorizada pela ANTT, o que assegura a qualidade nas suas operações.
+Voltada para o conforto dos passageiros, a frota da Paraquett conta com ônibus leito e semi-leito, equipados com poltronas reclináveis e banheiros. A empresa conecta diversas cidades da Região dos Lagos, oferecendo viagens seguras e agradáveis.
+Para planejar sua viagem com a Paraquett Turismo, você pode reservar seus serviços por meio da Buser, que disponibiliza um processo digital prático e seguro.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Paraquett Turismo diretamente pela Buser e aproveite a praticidade e o conforto que oferecemos.
+A Paraquett Turismo é uma empresa dedicada ao fretamento de ônibus para viagens em grupo, excursões e eventos, localizada em Cabo Frio, no Rio de Janeiro.
+Ao reservar sua viagem de ônibus com a Paraquett Turismo na Buser, você conta com segurança, poltronas confortáveis e atendimento 24 horas, que tornam cada trajeto mais agradável e tranquilo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>transpen</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>TRANSPEN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 1996, a Transpen Transporte Coletivo e Encomendas é uma empresa brasileira de transporte rodoviário de passageiros, conhecida por sua sólida atuação no setor e regulamentada pela ANTT.
+A empresa opera principalmente em rotas nos estados de São Paulo e Paraná, com um foco especial no conforto e na segurança das viagens.
+Sua frota é composta por ônibus das categorias convencional, executivo e leito-cama, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável para os passageiros.
+Para planejar sua viagem com a Transpen, você pode acessar a Buser, que disponibiliza um processo 100% digital, combinando a tradição com a praticidade na aquisição de passagens.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem de ônibus da TRANSPEN pela Buser e experimente a praticidade de viajar com conforto.
+A TRANSPEN é uma empresa brasileira que realiza o transporte rodoviário de passageiros, ligando cidades nos estados de São Paulo e Paraná, além de outras regiões.
+Na Buser, você encontra uma viagem segura, com preços acessíveis e poltronas confortáveis, proporcionando uma experiência tranquila e descomplicada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>bella-vita-transportes</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Bella Vita Transportes</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em São Paulo, a Bella Vita Transportes é uma empresa de transporte rodoviário de passageiros com vasta experiência no setor. Regulamentada pela ANTT, a empresa assegura que suas operações interestaduais estejam em conformidade com as normas vigentes.
+A Bella Vita conecta estados importantes como São Paulo, Minas Gerais, Bahia, Sergipe, Paraná, Rio de Janeiro e Goiás, destacando-se pelo conforto e segurança que proporciona em suas viagens.
+Sua frota inclui ônibus das categorias convencional, semi-leito e leito, todos equipados com comodidades que garantem uma viagem tranquila, como ar-condicionado e poltronas reclináveis.
+Para reservar sua viagem com a Bella Vita, você pode utilizar a Buser. A plataforma oferece um processo 100% digital e seguro, combinando tradição e praticidade na compra de bilhetes.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem de ônibus com a Bella Vita Transportes pela Buser, desfrutando de praticidade e confiança.
+A Bella Vita Transportes é uma empresa brasileira que opera viagens de longa distância, ligando estados como São Paulo, Minas Gerais, Bahia, Sergipe, Paraná, Rio de Janeiro e Goiás, com uma variedade de categorias de conforto em veículos modernos.
+Optando pela Buser, você conta com uma viagem segura, atendimento disponível 24 horas e a facilidade de remarcar, o que torna sua experiência ainda mais tranquila e flexível.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>viacao-nova</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Viação Nova</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Fundada pela Expresso Adamantina, a Viação Nova é uma empresa de transporte rodoviário que atua no setor de viagens de passageiros. É reconhecida por disponibilizar bilhetes digitais e operar rotas intermunicipais e interestaduais. Sua atuação é regulamentada pela ANTT, assegurando que esteja alinhada com as normas do setor.
+A empresa conecta diversas cidades por meio de suas rotas, sempre priorizando o conforto e a segurança dos passageiros. Embora não haja informações específicas sobre a sede, a Viação Nova se destaca pela qualidade de seus serviços.
+A frota da Viação Nova é composta por veículos modernos, que oferecem comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência confortável durante toda a viagem.
+Os passageiros podem adquirir suas viagens com a Viação Nova através da plataforma digital da Buser, que oferece um processo totalmente digital, unindo a tradição da viação à conveniência das compras online.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Adquira sua viagem de ônibus da Viação Nova na Buser, com toda a praticidade e conforto que você merece.
+A Viação Nova é uma empresa de transporte rodoviário que disponibiliza bilhetes digitais para rotas intermunicipais e interestaduais, proporcionando uma experiência de viagem que é tanto eficiente quanto acessível.
+Ao fazer sua reserva pela Buser, você conta com atendimento 24 horas, a opção de cancelamento grátis e poltronas confortáveis, o que torna sua jornada ainda mais agradável e segura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>helly-tur</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Helly Tur</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há mais de 25 anos, a Helly Tur é uma empresa especializada em fretamento e turismo, com reconhecimento no setor de transporte rodoviário e autorização da ANTT para operar rotas interestaduais.
+Com sede em Franca, São Paulo, a empresa se destaca pela segurança e conforto que proporciona em suas viagens, conectando diversas cidades e estados.
+A frota da Helly Tur conta com veículos convencionais e executivos, todos equipados com ar-condicionado, Wi-Fi e poltronas reclináveis, proporcionando um trajeto agradável.
+Para viajar com a Helly Tur, você pode reservar sua viagem por meio da Buser, um canal que oferece um processo 100% digital e prático.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Helly Tur diretamente na Buser, desfrutando de praticidade e segurança.
+Com mais de 25 anos de experiência, a Helly Tur se destaca no setor de fretamento e turismo, oferecendo soluções de transporte para diversas ocasiões.
+Ao optar pela sua viagem de ônibus da Helly Tur na Buser, você tem acesso a um atendimento 24 horas, poltronas confortáveis e um processo de reserva totalmente online, garantindo que sua experiência seja agradável e descomplicada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>pioneira-transportes</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Pioneira Transportes</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 2008, a Pioneira Transportes e Logística, localizada em Hortolândia (SP), se destaca no setor de fretamento e turismo, oferecendo viagens em itinerários interestaduais. A empresa valoriza o conforto e a segurança, conectando diversas cidades com um serviço de alta qualidade.
+Com uma frota moderna e diversificada, a Pioneira conta com ônibus adaptados, equipados com infraestrutura adequada para garantir uma experiência agradável durante a viagem. Entre as comodidades disponíveis, estão ar-condicionado e poltronas reclináveis.
+Ao optar pela Pioneira Transportes, você pode reservar sua viagem de forma prática e segura através da Buser, que disponibiliza um processo totalmente digital e livre de taxas abusivas.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Pioneira Transportes pela Buser e aproveite a praticidade e a segurança que oferecemos.
+A Pioneira Transportes se destaca no fretamento e turismo, disponibilizando opções de transporte para grupos e excursões em uma variedade de destinos.
+Ao escolher a Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e um processo de reserva completamente online, o que torna sua viagem ainda mais tranquila do começo ao fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="120" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>praiatur</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>PRAIATUR</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há mais de 45 anos, a PRAIATUR é uma destacada empresa de fretamento e turismo, reconhecida pela ANTT (Agência Nacional de Transportes Terrestres) por sua atuação no setor rodoviário.
+Com sede em Balneário Camboriú, SC, a PRAIATUR se destaca por oferecer viagens de qualidade, conectando diversos destinos em todo o Brasil, sempre priorizando o conforto e a segurança de seus passageiros.
+A frota da PRAIATUR conta com veículos das categorias Executivo e Leito, equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável durante a viagem.
+Para tornar suas viagens ainda mais fáceis, a PRAIATUR está disponível na Buser, permitindo que você reserve suas viagens de maneira 100% digital, com segurança e praticidade.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a PRAIATUR diretamente na Buser e aproveite a praticidade e o conforto que oferecemos.
+A PRAIATUR é especializada em fretamento e turismo, proporcionando roteiros que ligam os principais destinos do Brasil com segurança e qualidade.
+Ao optar por uma viagem de ônibus da PRAIATUR na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade de reservar online, tudo com rapidez e segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="120" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>brasiltur</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Brasiltur</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 2006, a Brasiltur Transporte e Turismo Ltda, com sede em Manaus (AM), se destaca pela qualidade no fretamento de viagens, atuando de acordo com as normas da ANTT. Com especialização em serviços de transporte para turismo, eventos e viagens de lazer, a empresa conecta diversas regiões do Brasil.
+A frota da Brasiltur é formada por veículos modernos, que incluem categorias como leito e semi-leito. Todos os ônibus são equipados com ar-condicionado e poltronas reclináveis, proporcionando conforto e segurança ao longo de toda a viagem.
+Para planejar sua viagem com a Brasiltur, você pode reservar seus serviços por meio da Buser, que oferece um processo totalmente digital, unindo a tradição da empresa com a praticidade de um único canal.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Brasiltur na Buser e aproveite o conforto de viajar de ônibus.
+A Brasiltur é uma empresa focada em fretamento e turismo, oferecendo opções de transporte ideais para excursões e viagens em grupo.
+Ao escolher a Buser, você conta com uma viagem segura, atendimento 24 horas e a praticidade da remarcação, o que torna sua experiência mais tranquila e conveniente.
+Além disso, a Brasiltur disponibiliza poltronas confortáveis, assegurando que cada trajeto seja agradável e relaxante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="120" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>condor-tur</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Condor Tur</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 1988, a Condor Tur Transporte e Turismo Ltda. é uma empresa bem estabelecida no setor de fretamento e turismo, regulamentada pela ANTT. Ela se destaca especialmente na operação de transporte escolar e fretamento contínuo.
+Com um compromisso com o conforto e a segurança, a Condor Tur atende principalmente as regiões de Mogi das Cruzes e Salesópolis, conectando cidades como Araraquara, Barretos e Catanduva.
+Sua frota é composta por ônibus executivos e escolares, que contam com comodidades como ar-condicionado e poltronas reclináveis, tudo pensado para oferecer uma experiência de viagem agradável.
+Para reservar uma viagem com a Condor Tur, os usuários podem acessar a Buser, que proporciona um processo totalmente digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Agende sua viagem com a Condor Tur pela Buser e aproveite todo o conforto e segurança que oferecemos.
+A Condor Tur é uma empresa dedicada ao fretamento e turismo, com foco nas regiões de Mogi das Cruzes, Salesópolis e interior paulista. Nossos serviços incluem transporte escolar e viagens em grupo, sempre com atenção às suas necessidades.
+Ao agendar sua viagem de ônibus da Condor Tur na Buser, você tem acesso a um atendimento disponível 24 horas, poltronas confortáveis e a conveniência de um processo de reserva totalmente online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>demp-turismo</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Demp Turismo</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em setembro de 2008, a Demp Turismo se destacou no setor de transporte rodoviário, especialmente pelo seu serviço de fretamento de viagens para artistas e eventos. A empresa é reconhecida por operar com autorização da ANTT, o que assegura segurança e confiabilidade em suas operações.
+Com sede em Aparecida de Goiânia (GO), a Demp Turismo conecta diversas cidades e oferece fretamentos contínuos e eventuais para empresas, igrejas e famílias. Um dos seus principais diferenciais é a qualidade no transporte de bandas e artistas, sempre priorizando o conforto durante as viagens.
+Sua frota conta com ônibus executivos personalizados, equipados com poltronas reclináveis, Wi-Fi, ar-condicionado, tomadas USB e TVs, proporcionando uma experiência agradável aos passageiros.
+Para viajar com a Demp Turismo, você pode reservar serviços de fretamento através da Buser, que disponibiliza um processo digital prático e seguro, ideal para uma viagem tranquila.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Demp Turismo diretamente pela Buser e desfrute de praticidade e conforto.
+A Demp Turismo se destaca no fretamento de ônibus, atendendo bandas, eventos e turismo em Goiás, sempre priorizando a experiência do cliente.
+Optar pela Demp Turismo na Buser significa embarcar em uma viagem segura, com poltronas confortáveis e a facilidade de um atendimento 24 horas, o que torna sua experiência ainda mais agradável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="120" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>livre-transportes</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Livre Transportes</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em São Paulo, a Livre Transportes é uma empresa que se destaca no fretamento, sendo reconhecida pela sua atuação confiável e segura no transporte rodoviário coletivo de passageiros, sempre em conformidade com as regulamentações da ANTT.
+Com uma frota que abrange ônibus de grande porte, a empresa oferece viagens confortáveis ligando a região do Grande ABC a diversos destinos em São Paulo. Além disso, disponibiliza serviços para eventos e excursões em todo o Brasil.
+Os veículos são equipados com ar-condicionado, Wi-Fi, poltronas reclináveis e banheiro, assegurando uma experiência agradável e segura durante as viagens.
+Para tornar tudo mais fácil, a Livre Transportes pode ser encontrada na Buser, onde você pode reservar suas viagens de forma prática e totalmente digital.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Livre Transportes através da Buser e desfrute de conforto e praticidade.
+A Livre Transportes é uma empresa que se destaca no fretamento de ônibus e micro-ônibus, oferecendo serviços para turismo, eventos e transporte corporativo em todo o Brasil.
+Ao reservar sua viagem de ônibus da Livre Transportes na Buser, você tem acesso a atendimento 24h, viagens seguras e poltronas confortáveis, o que torna cada deslocamento mais tranquilo e agradável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>miramar-turismo</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MIRAMAR TURISMO</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há anos, a Miramar Turismo é uma empresa bem estabelecida no setor de fretamento e turismo, com autorização da ANTT (Agência Nacional de Transportes Terrestres) para operar em rotas interestaduais. A empresa se destaca pela sua vasta experiência na oferta de pacotes de viagens para diversos destinos.
+A Miramar Turismo conecta cidades como Curitiba, Foz do Iguaçu e Marília, sempre priorizando a segurança e o conforto dos passageiros durante as viagens. 
+Sua frota é moderna e conta com diferentes categorias de veículos, que proporcionam comodidades como ar-condicionado e poltronas reclináveis para uma experiência agradável. 
+Ao reservar sua viagem com a Miramar Turismo, você pode contar com a Buser, que oferece um processo totalmente digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a MIRAMAR TURISMO pela Buser e explore destinos incríveis com total comodidade.
+A MIRAMAR TURISMO é uma agência focada em fretamento e turismo, disponibilizando pacotes de viagens nacionais e internacionais para os melhores roteiros.
+Ao reservar sua viagem de ônibus da MIRAMAR TURISMO na Buser, você desfruta de atendimento 24 horas, cancelamento grátis e poltronas confortáveis, proporcionando uma experiência tranquila e agradável do início ao fim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="120" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>novos-rumos-turismo</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Novos Rumos Turismo</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em agosto de 2012 em Juiz de Fora, Minas Gerais, a Novos Rumos Turismo é conhecida pela sua tradição no transporte rodoviário, atuando de acordo com as normas da ANTT para fretamento interestadual.
+A empresa prioriza conforto e segurança, oferecendo fretamento contínuo e eventual para grupos, escolas, igrejas e empresas, com opções de viagens que vão desde o município até rotas intermunicipais e interestaduais.
+A frota da Novos Rumos conta com ônibus e vans equipados, proporcionando aos passageiros comodidades essenciais durante as viagens, como ar-condicionado e poltronas confortáveis.
+Para viajar com a Novos Rumos Turismo, você pode reservar suas viagens de maneira prática e segura por meio da Buser, que simplifica o processo digital de fretamentos.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Novos Rumos Turismo diretamente na Buser e desfrute de conforto e praticidade.
+A Novos Rumos Turismo se destaca no fretamento de ônibus e vans para excursões, atendendo grupos, famílias e empresas na região de Juiz de Fora, Minas Gerais.
+Ao reservar sua viagem de ônibus com a Novos Rumos Turismo pela Buser, você tem à disposição uma experiência segura, atendimento 24h e a facilidade de remarcação, o que torna seu planejamento muito mais tranquilo.</t>
         </is>
       </c>
     </row>

--- a/enviando/empresas_descricoes.xlsx
+++ b/enviando/empresas_descricoes.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -872,7 +872,7 @@
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>sao-jose-viagens</t>
+          <t>brasil-way-tour</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="39" ht="120" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>viacao-nova</t>
+          <t>expresso-adamantina</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1731,6 +1731,72 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>gimenes-turismo</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Gimenes Turismo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Com mais de 40 anos de atuação, a Gimenes Turismo é uma empresa familiar que se destaca pela confiabilidade e qualidade em fretamento para viagens, com foco especial em São Paulo, oferecendo serviços de bate e volta para compras e negócios. Autorizada pela ANTT, a Gimenes prioriza a segurança e o conforto de seus passageiros.&lt;br&gt;&lt;br&gt;A frota da empresa é moderna e conta com ônibus equipados para garantir uma viagem agradável, incluindo poltronas reclináveis, ar-condicionado e Wi-Fi a bordo.&lt;br&gt;&lt;br&gt;Ao escolher a Gimenes, você pode reservar suas viagens de maneira prática e segura por meio da Buser, que proporciona um processo 100% digital, combinando tradição e inovação.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem de ônibus com a Gimenes Turismo na Buser e aproveite toda a comodidade que você merece.&lt;br&gt;&lt;br&gt;A Gimenes Turismo é uma empresa familiar que se destaca no fretamento de ônibus para excursões, eventos e viagens em grupo. Ela também oferece transporte de encomendas entre São Paulo e Franca.&lt;br&gt;&lt;br&gt;Ao realizar sua reserva pela Buser, você tem à disposição um atendimento 24 horas, viagens seguras e poltronas confortáveis, proporcionando o máximo de conforto e tranquilidade durante o seu trajeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bompani-turismo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bompani Turismo</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fundada em 2013, a Bompani Turismo é uma empresa de fretamento rodoviário situada em Luiz Alves, Santa Catarina. Com um forte foco em agenciamento de viagens, a empresa opera com a autorização da ANTT, o que assegura qualidade e segurança em suas operações.&lt;br&gt;&lt;br&gt;A Bompani se especializa em oferecer viagens personalizadas e excursões de turismo, conectando uma variedade de cidades e destinos. Um de seus grandes diferenciais é o conforto, que a destaca na realização de roteiros turísticos tanto regionais quanto internacionais.&lt;br&gt;&lt;br&gt;Sua frota é composta por veículos bem equipados, que oferecem comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável ao longo da viagem.&lt;br&gt;&lt;br&gt;Para reservar sua viagem com a Bompani, você pode usar a Buser, que proporciona um processo totalmente digital e seguro para reservar fretamentos de maneira prática e eficiente.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Bompani Turismo diretamente pela Buser, garantindo praticidade e confiança em cada etapa.&lt;br&gt;&lt;br&gt;A Bompani Turismo é especializada em fretamento de ônibus para turismo, oferecendo roteiros regionais, excursões e viagens de compras com todo o conforto e segurança que você merece.&lt;br&gt;&lt;br&gt;Ao reservar sua viagem de ônibus com a Bompani Turismo na Buser, você tem à disposição atendimento 24 horas, um trajeto seguro e a possibilidade de cancelamento grátis, tornando sua experiência ainda mais tranquila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>jacson-turismo</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jacson Turismo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fundada em Chapecó, Santa Catarina, a Jacson Turismo é uma empresa bem estabelecida no setor de transporte rodoviário, com autorização da ANTT para realizar fretamentos interestaduais.&lt;br&gt;&lt;br&gt;A companhia se destaca por oferecer viagens regulares direcionadas a lojistas e compradores, interligando cidades como São Paulo, Brusque e Criciúma, com saídas programadas em dias específicos da semana.&lt;br&gt;&lt;br&gt;Sua frota é composta por ônibus leito, que proporcionam conforto e comodidade ao longo das viagens, além de contar com serviços como café da manhã e suporte para o transporte de mercadorias.&lt;br&gt;&lt;br&gt;As viagens podem ser reservadas de maneira prática e segura por meio da Buser, uma parceria que combina a tradição da Jacson Turismo com a conveniência do processo digital.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Garanta a sua viagem com a Jacson Turismo através da Buser, aproveitando toda a praticidade que você deseja.&lt;br&gt;&lt;br&gt;A Jacson Turismo é uma empresa de transporte rodoviário focada em fretamento, com roteiros que levam você a polos atacadistas, como São Paulo, Brusque e Criciúma.&lt;br&gt;&lt;br&gt;Ao reservar sua viagem de ônibus com a Jacson Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples, tornando sua experiência ainda mais agradável.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/enviando/empresas_descricoes.xlsx
+++ b/enviando/empresas_descricoes.xlsx
@@ -469,1331 +469,1347 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>trans-acreana-turismo</t>
+          <t>pitangui-turismo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Trans Acreana Turismo</t>
+          <t>Pitangui Turismo</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2009, a Trans Acreana Turismo se destaca como uma das principais empresas de fretamento e turismo no Acre, sendo reconhecida por sua tradição e a qualidade dos serviços oferecidos. Regulamentada pela ANTT, a companhia opera em rotas interestaduais de maneira segura e confiável.
-Com uma frota moderna, a Trans Acreana disponibiliza diversas categorias de veículos, que incluem opções com poltronas reclináveis, Wi-Fi via satélite e entradas USB. Isso proporciona conforto e comodidade para todos que embarcam em suas viagens.
-As principais rotas conectam a capital, Rio Branco, a várias cidades do interior do Acre e até ao Peru, o que a torna uma escolha popular para quem deseja explorar novos destinos.
-Para reservar uma viagem com a Trans Acreana, você pode contar com a Buser, uma plataforma digital que torna o processo prático e seguro, unindo a tradição da empresa à inovação no transporte.</t>
+          <t>Fundada em Minas Gerais, a Pitangui Turismo é uma empresa dedicada ao fretamento e turismo, reconhecida por sua longa trajetória no setor. Com autorização da ANTT, a empresa assegura segurança e qualidade em suas operações.
+Com um forte compromisso com o conforto e a segurança, a Pitangui Turismo conecta cidades como Belo Horizonte e São Paulo, oferecendo serviços de viagem e excursões personalizadas para grupos de diferentes tamanhos.
+Sua frota diversificada conta com ônibus equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, garantindo uma experiência agradável durante as viagens.
+Por meio da Buser, você pode reservar sua viagem com a Pitangui Turismo de forma prática e totalmente digital, unindo a tradição da empresa à inovação tecnológica.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Descubra sua viagem com a Trans Acreana Turismo na Buser, desfrutando de todo o conforto e segurança que você merece.
-A Trans Acreana Turismo se dedica ao fretamento e ao turismo, apresentando roteiros incríveis que conectam várias cidades do Acre e até mesmo a famosa linha internacional para o Peru.
-Ao reservar sua viagem de ônibus da Trans Acreana Turismo na Buser, você tem à disposição um atendimento 24 horas, poltronas confortáveis e um processo de reserva online descomplicado, tudo pensado para tornar sua experiência de viagem a mais agradável possível.</t>
+          <t>Reserve sua viagem com a Pitangui Turismo através da Buser e desfrute de praticidade e conforto.
+A Pitangui Turismo é especializada no fretamento de passageiros, oferecendo serviços de transporte e excursões voltados para viagens em grupo e roteiros turísticos, com ênfase nas rotas entre Minas Gerais e São Paulo.
+Optando pela Pitangui Turismo na Buser, você tem à disposição uma viagem segura, atendimento 24 horas e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e acessível.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>anatur</t>
+          <t>prime-viagens</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Anatur</t>
+          <t>Prime Viagens</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1994, a Anatur Turismo é uma empresa respeitada no setor de transporte de passageiros, atuando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres) para fretamento interestadual. Com mais de 29 anos de experiência, a Anatur se destaca pela qualidade em viagens de turismo em todo o Brasil.
-A empresa conecta diversas cidades, oferecendo roteiros personalizados e uma experiência de viagem inesquecível, sempre priorizando o conforto e a segurança dos passageiros.
-Sua frota é composta por veículos modernos, que proporcionam comodidades como ar-condicionado e poltronas reclináveis, garantindo uma viagem agradável.
-Para planejar sua viagem com a Anatur, você pode utilizar a Buser, que disponibiliza um processo 100% digital para reservar suas viagens de maneira prática e segura.</t>
+          <t>A Prime Viagens, que reúne diversas agências de turismo e operadoras em diferentes regiões do Brasil, é reconhecida por seu trabalho no fretamento e no turismo, sempre em conformidade com as regulamentações da ANTT.
+Essas empresas têm como prioridade oferecer viagens confortáveis e seguras, conectando várias cidades e destinos turísticos em diferentes estados, sempre se ajustando às necessidades de seus clientes.
+A frota disponível varia de acordo com a operadora, contando com veículos das categorias convencional, executivo e leito, além de comodidades como Wi-Fi, ar-condicionado e poltronas reclináveis para uma experiência agradável.
+Ao optar pela Prime Viagens, você pode reservar seu fretamento de maneira prática e segura através da Buser, que proporciona um processo totalmente digital e livre de taxas excessivas.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Anatur diretamente pela Buser, aproveitando toda a praticidade que você merece.
-A Anatur se destaca no fretamento e no transporte para turismo, proporcionando soluções de mobilidade para grupos em várias regiões do Brasil.
-Ao reservar sua viagem de ônibus da Anatur na Buser, você conta com atendimento 24h, cancelamento grátis e poltronas confortáveis, o que torna sua experiência tranquila do começo ao fim.</t>
+          <t>Reserve sua viagem com a Prime Viagens diretamente pela Buser, aproveitando toda a praticidade e segurança que oferecemos.
+A Prime Viagens é um nome comercial utilizado por diversas agências de turismo e operadoras de excursões em várias regiões do Brasil. Com ela, você encontra roteiros personalizados e serviços de fretamento que atendem às suas necessidades.
+Ao reservar sua viagem de ônibus da Prime Viagens na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e um processo de reserva totalmente online, garantindo uma experiência tranquila e acessível.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>expresso-diamante</t>
+          <t>rio-transporte</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Expresso Diamante</t>
+          <t>Rio Transporte</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2018 em Goiânia, Goiás, a Expresso Diamante se destaca no setor de fretamento e turismo, com autorização da ANTT para operar rotas interestaduais.
-A empresa conecta cidades nas regiões Centro-Oeste, Sudeste e Sul, oferecendo trajetos como Goiânia a Curitiba, Florianópolis e São Paulo, sempre priorizando o conforto e a segurança dos passageiros.
-Sua frota moderna é composta por ônibus semi-leito e Double Decker, que contam com ar-condicionado, Wi-Fi e banheiros a bordo para uma viagem mais agradável.
-Para reservar sua viagem com a Expresso Diamante, você pode utilizar a Buser, que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada em 2006, a Rio Transporte se destaca no setor de fretamento e turismo, operando de acordo com as diretrizes da ANTT (Agência Nacional de Transportes Terrestres). A empresa é conhecida por sua qualidade e confiabilidade nas operações.
+A Rio Transporte conecta diversas cidades do estado do Rio de Janeiro, priorizando o conforto e a segurança em suas viagens. Sua frota conta com micro-ônibus modernos, que oferecem assentos reclináveis, climatização, banheiros e entradas USB.
+Os passageiros têm a oportunidade de desfrutar de uma experiência de viagem completa, com serviços adicionais como kit de lanches e suporte contínuo ao longo do trajeto.
+Para viajar com a Rio Transporte, você pode reservar sua viagem por meio da Buser, uma parceria que proporciona um processo totalmente digital e prático, sem taxas abusivas.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Expresso Diamante diretamente na Buser, aproveitando toda a praticidade e segurança que oferecemos.
-A Expresso Diamante, com sede em Goiânia, é especializada em fretamento para turismo e eventos, conectando várias cidades das regiões Centro-Oeste, Sudeste e Sul do Brasil.
-Ao optar por uma viagem de ônibus da Expresso Diamante na Buser, você se beneficia de atendimento 24 horas, poltronas confortáveis e a conveniência de um processo de reserva totalmente online, tornando sua experiência ainda mais satisfatória.</t>
+          <t>Reserve sua viagem com a Rio Transporte pela Buser e desfrute de conforto e praticidade.
+A Rio Transporte se dedica ao fretamento de veículos para turismo e viagens, disponibilizando uma frota moderna e equipada com itens que garantem seu conforto, como assentos reclináveis e climatização.
+Ao optar pela Buser para sua reserva, você tem à disposição atendimento 24 horas, uma experiência de viagem segura e a comodidade de remarcação, o que torna cada deslocamento mais tranquilo e acessível.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>galaxia-turismo</t>
+          <t>seriema-turismo</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Galaxia Turismo</t>
+          <t>Seriema Turismo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Fundada há 25 anos, a Galaxia Turismo é uma empresa de fretamento rodoviário com sede em Contagem, Minas Gerais, reconhecida por sua experiência em criar pacotes de viagem para destinos populares como Caldas Novas, Olímpia e Angra dos Reis, sempre em conformidade com as normas da ANTT.
-A empresa se destaca ao oferecer viagens em grupo, utilizando ônibus modernos que contam com serviços adicionais, como a reserva de hotéis e guias turísticos credenciados, proporcionando conforto e segurança aos passageiros.
-Sua frota é composta por veículos equipados com comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante os trajetos.
-Para viajar com a Galaxia Turismo, você pode utilizar a plataforma da Buser, que facilita um processo digital seguro e prático para reservar suas viagens.</t>
+          <t>A Seriema Turismo, cuja data de fundação não é claramente especificada, se destaca no setor de transporte rodoviário. Regulamentada pela ANTT (Agência Nacional de Transportes Terrestres), a empresa é reconhecida por sua credibilidade.
+Com um foco em oferecer viagens seguras e confortáveis, a Seriema Turismo conecta diversas cidades e estados, mesmo que informações detalhadas sobre sua sede e rotas específicas não estejam disponíveis.
+Sua frota é composta por veículos que priorizam o conforto dos passageiros, equipados com poltronas reclináveis, ar-condicionado e, possivelmente, outras comodidades a bordo.
+Para realizar uma viagem com a Seriema Turismo, os passageiros podem acessar a plataforma Buser, que proporciona um processo 100% digital, tornando a compra de viagens mais segura e prática.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Galaxia Turismo pela Buser e desfrute de conforto e praticidade ao longo de sua jornada.
-A Galaxia Turismo é uma agência dedicada ao fretamento rodoviário, oferecendo pacotes de viagens em grupo para destinos incríveis como Caldas Novas, Olímpia e Porto Seguro. Além disso, disponibilizamos serviços como reserva de hotéis e guias turísticos.
-Ao agendar sua viagem de ônibus com a Galaxia Turismo na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e acessível.</t>
+          <t>Reserve sua viagem com a Seriema Turismo diretamente na Buser, e aproveite a praticidade e o conforto que oferecemos.
+A Seriema Turismo é especializada em fretamento e turismo, proporcionando soluções completas para suas viagens em grupo, sempre com total assistência e segurança.
+Ao reservar sua viagem de ônibus da Seriema Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e um processo de reserva totalmente online, sem complicações.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>horizonte-turismo</t>
+          <t>tj-turismo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Horizonte Turismo</t>
+          <t>Tj Turismo</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fundada em Belo Horizonte, Minas Gerais, a Horizonte Turismo é uma empresa especializada em fretamento e turismo, destacando-se no transporte de artistas e na realização de grandes eventos. Regida pela ANTT, a empresa é conhecida pela qualidade e segurança que oferece em suas viagens.
-Com uma frota de ônibus de alto padrão, incluindo modelos Double Decker, a Horizonte proporciona conforto em suas rotas de longa distância, atendendo a diversas necessidades de fretamento e excursões.
-Os veículos contam com comodidades como ar-condicionado e poltronas reclináveis, o que contribui para uma experiência agradável ao longo da viagem.
-Para reservar sua viagem com a Horizonte Turismo, você pode utilizar a Buser, um canal digital que torna o processo mais prático e seguro.</t>
+          <t>Fundada em 2017, a TJ Turismo é uma empresa especializada em fretamento e turismo, com autorização da ANTT para operar viagens interestaduais. Com uma sólida reputação no setor, a empresa oferece uma variedade de serviços de transporte para grupos e excursões.
+A TJ Turismo realiza viagens que conectam diversas cidades, priorizando sempre o conforto e a segurança dos passageiros. Suas operações incluem roteiros turísticos e traslados para aeroportos, atendendo às necessidades de diferentes tipos de viajantes.
+A frota da TJ Turismo é composta por veículos modernos, equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável durante as viagens.
+Para viajar com a TJ Turismo, você pode reservar seus serviços através da Buser, que disponibiliza um processo digital prático e seguro, unindo tradição e inovação no setor.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Horizonte Turismo na Buser, desfrutando de conforto e praticidade.
-A Horizonte Turismo se destaca no setor de fretamento e turismo, proporcionando transporte para excursões e eventos em todo o Brasil, com uma frota de ônibus de alto padrão.
-Ao fazer sua reserva de viagem com a Horizonte Turismo na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e flexível.</t>
+          <t>Reserve sua viagem de ônibus com a Tj Turismo diretamente pela Buser e aproveite toda a praticidade que você busca.
+A Tj Turismo se dedica ao fretamento de ônibus e vans, oferecendo transporte para excursões, eventos e passeios, sempre com foco no conforto e na segurança em cada trajeto.
+Ao realizar sua reserva pela Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais tranquila e flexível.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>matriz-transportes</t>
+          <t>vivitur</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Matriz Transportes</t>
+          <t>Vivitur</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1992, a Matriz Transportes, com sede em Goiânia (GO), é uma empresa de transporte rodoviário de passageiros reconhecida pela sua confiabilidade e qualidade no setor, atuando em conformidade com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
-Com mais de 30 anos de experiência, a empresa se destaca pelo conforto e segurança que proporciona em suas viagens, conectando cidades como Goiânia, Cuiabá, Palmas, Porto Velho e Rio Branco.
-Sua frota é composta por diferentes categorias de veículos, oferecendo comodidades como ar-condicionado, poltronas reclináveis e wi-fi, tudo pensado para tornar a sua viagem mais agradável.
-Ao escolher viajar com a Matriz Transportes, você pode utilizar a Buser, que oferece um processo 100% digital para a compra da sua viagem, unindo tradição e praticidade.</t>
+          <t>Fundada há várias décadas, a Vivitur se destaca no setor de transporte rodoviário, sendo amplamente reconhecida por sua confiabilidade e tradição. A empresa possui autorização da ANTT, o que assegura que suas operações estejam em conformidade nas rotas interestaduais.
+A Vivitur conecta diversas cidades com o objetivo de proporcionar viagens seguras e confortáveis. Seu ponto forte está na eficiência operacional e na qualidade do serviço oferecido aos passageiros.
+A frota da Vivitur conta com veículos de diferentes categorias, incluindo convencionais e executivos, que oferecem comodidades como ar-condicionado e poltronas reclináveis, garantindo maior conforto durante as viagens.
+Para aqueles que desejam viajar com a Vivitur, a Buser é uma opção prática para adquirir suas passagens, unindo a tradição da empresa com a modernidade de um processo digital.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Matriz Transportes na Buser e aproveite a praticidade e segurança que oferecemos.
-A Matriz Transportes é uma empresa brasileira com sede em Goiânia, especializada no transporte rodoviário de passageiros e cargas, ligando diversas cidades nos estados de Goiás, Acre, Pará, Rondônia, Tocantins e Mato Grosso.
-Ao optar pela Buser, você vivencia uma viagem segura, com poltronas confortáveis e um processo de compra 100% online, o que facilita ainda mais a sua experiência. Além disso, nosso atendimento está disponível 24 horas, garantindo que você tenha suporte sempre que precisar.</t>
+          <t>Adquira sua viagem de ônibus da Vivitur na Buser com facilidade e confiança.
+A Vivitur se destaca no transporte rodoviário, operando em várias regiões do Brasil, tanto em linhas regulares quanto em fretamento.
+Ao optar pela Buser, você desfruta de uma viagem segura, com poltronas confortáveis e atendimento disponível 24 horas, proporcionando uma experiência tranquila do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>mm-turismo</t>
+          <t>auto-viacao-jauense</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MM Turismo</t>
+          <t>Auto Viação Jauense</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Fundada em Belo Horizonte (MG), a MM Turismo é uma empresa bem estabelecida no setor de fretamento e turismo, devidamente autorizada pela ANTT. Com anos de atuação, a empresa se destaca pela busca constante por conforto e segurança em suas viagens, conectando diversas cidades e destinos.
-A frota da MM Turismo conta com ônibus em diferentes categorias, oferecendo comodidades como Wi-Fi, poltronas reclináveis, ar-condicionado e sanitários, proporcionando uma experiência agradável para os passageiros.
-Para viajar com a MM Turismo, você pode reservar suas viagens de maneira prática e segura através da plataforma Buser, que disponibiliza um processo 100% digital, livre de taxas abusivas.</t>
+          <t>Fundada em 13 de outubro de 1992, a Auto Viação Jauense é uma empresa de transporte rodoviário situada em Jaú, SP, com uma sólida reputação no setor, regulamentada pela ANTT.
+Com um foco especial em fretamento e turismo, a empresa conecta Jaú a diversos destinos, sendo o distrito de Potunduva um dos mais destacados. Seus serviços abrangem tanto fretamentos contínuos quanto eventuais, adaptando-se às necessidades dos clientes.
+A frota da Auto Viação Jauense conta com mais de 150 veículos, que proporcionam conforto aos passageiros, equipados com poltronas reclináveis e ar-condicionado, assegurando uma experiência de viagem agradável.
+Para reservar sua viagem com a Auto Viação Jauense, você pode acessar a Buser, que disponibiliza um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a MM Turismo diretamente pela Buser e desfrute da facilidade e segurança do fretamento.
-A MM Turismo é especialista em fretamento e turismo, proporcionando soluções para excursões e viagens em grupo, sempre focada em atender às expectativas dos clientes.
-Optando pela MM Turismo na Buser, você tem à disposição poltronas confortáveis, atendimento 24 horas e a conveniência de reservar sua viagem online, tudo pensado para oferecer um deslocamento tranquilo e eficiente.</t>
+          <t>Reserve sua viagem com a Auto Viação Jauense na Buser e experimente a facilidade de viajar com conforto e segurança.
+A Auto Viação Jauense se destaca no setor de fretamento e turismo, oferecendo serviços voltados para excursões e viagens em grupo, sempre priorizando a satisfação dos seus clientes.
+Ao reservar sua viagem de ônibus com a Auto Viação Jauense na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a conveniência de um processo completamente online.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>viacao-marlim</t>
+          <t>ebertur</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Viação Marlim</t>
+          <t>Ebertur</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fundada na década de 1980, a Viação Marlim é uma empresa de transporte rodoviário de passageiros e cargas, com sede em Ariquemes, Rondônia. Reconhecida por sua tradição na Região Norte do Brasil, atua em conformidade com as regulamentações da ANTT.
-A Viação Marlim conecta diversas cidades nos estados de Rondônia, Mato Grosso, Goiás e Acre, oferecendo serviços de viagens intermunicipais e interestaduais, sempre com ênfase em conforto e segurança.
-Sua frota inclui ônibus convencionais, executivos e semi-leitos, todos equipados com comodidades como Wi-Fi e ar-condicionado, garantindo uma experiência agradável ao longo do trajeto.
-Para viajar com a Viação Marlim, você pode utilizar a plataforma da Buser, que facilita a compra da sua viagem de forma digital, unindo tradição e praticidade na sua mobilidade.</t>
+          <t>Fundada em Baixo Guandu, no Espírito Santo, a Ebertur é uma empresa especializada em fretamento e turismo, reconhecida pela qualidade das suas viagens e devidamente regulamentada pela ANTT (Agência Nacional de Transportes Terrestres).
+Com uma atuação sólida no setor, a Ebertur se destaca pela segurança e conforto que proporciona em suas rotas, conectando importantes cidades como Belo Horizonte e Vitória.
+A frota da Ebertur conta com ônibus das categorias executivo e semi-leito, equipados com ar-condicionado e poltronas reclináveis, proporcionando uma experiência agradável ao longo da viagem.
+Para reservar sua viagem com a Ebertur, você pode utilizar a Buser, que oferece um processo totalmente digital e isento de taxas abusivas.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem de ônibus com a Viação Marlim na Buser, com toda a praticidade e segurança que você merece.
-A Viação Marlim é uma respeitada empresa de transporte rodoviário, oferecendo viagens intermunicipais e interestaduais que conectam várias cidades nos estados de Rondônia, Mato Grosso, Goiás e Acre.
-Optar pela Viação Marlim na Buser significa desfrutar de uma viagem segura, com poltronas confortáveis e um processo de compra simples e totalmente online, tornando sua experiência ainda mais agradável.</t>
+          <t>Descubra sua viagem com a Ebertur diretamente na Buser, onde conforto e praticidade se unem.
+A Ebertur é uma empresa focada em fretamento e turismo, situada em Baixo Guandu, Espírito Santo, e oferece roteiros para uma variedade de destinos.
+Ao reservar sua viagem de ônibus da Ebertur na Buser, você tem à disposição atendimento 24 horas, a opção de cancelamento grátis e poltronas confortáveis, garantindo uma experiência agradável e sem complicações.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>evt-transportes</t>
+          <t>expresso-biagini</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>EVT Transportes</t>
+          <t>Expresso Biagini</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2015, a EVT Transportes se destaca no setor de fretamento e turismo, contando com autorização da ANTT para operar viagens interestaduais. Desde o seu início como um pequeno serviço de táxi, a empresa tem expandido suas operações, sempre priorizando o conforto e a segurança dos passageiros.
-A EVT Transportes liga diversas cidades, oferecendo serviços de fretamento para excursões e turismo, com uma frota moderna e padronizada que atende às necessidades dos viajantes.
-Os veículos são projetados para proporcionar uma experiência agradável, mesmo que não sejam fornecidos detalhes específicos sobre as categorias de ônibus.
-Para reservar sua viagem com a EVT Transportes, basta acessar a plataforma da Buser, que proporciona um processo totalmente digital e livre de taxas excessivas.</t>
+          <t>Fundada em Belo Horizonte, Minas Gerais, a Expresso Biagini se destaca como uma empresa de transporte rodoviário, focada em proporcionar conforto e segurança em suas viagens de fretamento e turismo. Cumprindo rigorosamente as normas da ANTT, a empresa também oferece serviços de logística para eventos corporativos, além de disponibilizar roteiros variados, tanto de curto quanto de longo percurso.
+A frota da Expresso Biagini conta com ônibus modernos, incluindo os modelos Double Decker e poltronas semi-leito, garantindo uma experiência agradável para os passageiros. Os veículos são equipados com diversas comodidades que promovem o bem-estar durante todo o trajeto.
+Para viajar com a Expresso Biagini, você pode reservar seu fretamento através do canal oficial da Buser. O processo é totalmente digital, combinando a tradição da empresa com a praticidade das soluções tecnológicas.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a EVT Transportes diretamente na Buser e desfrute de toda a comodidade do fretamento.
-A EVT Transportes é uma empresa dedicada ao fretamento e turismo, disponibilizando serviços de transporte para excursões e viagens fechadas, sempre priorizando o conforto e a segurança.
-Ao reservar sua viagem de ônibus da EVT Transportes na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de um processo totalmente online, o que proporciona uma experiência tranquila do começo ao fim.</t>
+          <t>Descubra sua viagem com a Expresso Biagini na Buser, aproveitando toda a facilidade que você merece.
+A Expresso Biagini se destaca no fretamento rodoviário, disponibilizando serviços de transporte voltados para turismo e eventos corporativos, sempre com uma frota moderna e confortável.
+Ao reservar sua viagem de ônibus com a Expresso Biagini pela Buser, você conta com atendimento 24 horas, oferta de cancelamento grátis e poltronas aconchegantes, proporcionando uma experiência tranquila e prática do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>lopes-tur</t>
+          <t>fgs-turismo</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lopes Tur</t>
+          <t>FGS Turismo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1978, a Lopes Tur, também conhecida como Lopes Turismo e Transporte Ltda., é uma empresa de transporte rodoviário com sede em Carazinho, Rio Grande do Sul. A empresa se destaca pela qualidade e segurança em suas operações, sempre em conformidade com a regulamentação da ANTT.
-A Lopes Tur oferece viagens interestaduais que conectam o Sul ao Nordeste do Brasil. Suas rotas passam por estados como Santa Catarina, Paraná, São Paulo, Minas Gerais, Goiás, Tocantins e Maranhão, com especial atenção para a linha Carazinho-Balsas.
-A frota da Lopes Tur conta com ônibus das categorias convencional, executivo e semi-leito/leito, todos equipados com ar-condicionado e poltronas reclináveis, garantindo conforto durante a viagem.
-Para reservar sua viagem com a Lopes Tur, você pode utilizar a Buser, que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada em Ribeirão Preto, São Paulo, a FGS Turismo é uma empresa respeitada no setor de fretamento e turismo, com autorização da ANTT. Seu compromisso é proporcionar viagens seguras e confortáveis, atendendo a eventos, instituições de ensino e oferecendo excursões a diversos destinos turísticos pelo Brasil.
+A frota da FGS Turismo é moderna e conta com ônibus de grande porte, incluindo os sofisticados modelos Double Decker. Esses veículos são equipados com ar-condicionado e poltronas reclináveis, proporcionando o conforto ideal para viagens de longa distância.
+Para reservar sua viagem com a FGS Turismo, você pode utilizar o canal digital da Buser. Essa plataforma torna o processo mais fácil, combinando tradição e praticidade nas opções de fretamento disponíveis.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Lopes Tur pela Buser e experimente a praticidade do fretamento rodoviário.
-A Lopes Tur se destaca na realização de fretamentos e na organização de excursões rodoviárias, estabelecendo conexões entre o Sul e o Nordeste do Brasil, sempre priorizando o conforto e a satisfação dos passageiros.
-Ao reservar sua viagem de ônibus com a Lopes Tur na Buser, você conta com atendimento 24 horas, viagens seguras e a opção de cancelamento grátis, proporcionando uma experiência tranquila e sem imprevistos.</t>
+          <t>Reserve sua viagem com a FGS Turismo através da Buser e desfrute de conforto e praticidade em cada trajeto.
+A FGS Turismo é uma empresa focada em fretamento e turismo, oferecendo serviços para instituições, empresas e excursões a diversos destinos no Brasil, utilizando uma frota moderna e confortável.
+Ao reservar sua viagem de ônibus da FGS Turismo na Buser, você tem à disposição atendimento 24h, remarcação simples e poltronas confortáveis, o que torna sua experiência ainda mais tranquila e agradável.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>natal-turismo</t>
+          <t>hd-turismo</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Natal Turismo</t>
+          <t>HD Turismo</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fundada na década de 1980, a Natal Turismo, oficialmente Transportadora Turística Natal Ltda., é uma empresa reconhecida no setor de fretamento e turismo em Mogi das Cruzes, São Paulo. Com autorização da ANTT, a empresa é conhecida pela segurança e pontualidade em suas operações.
-A Natal Turismo conecta diversas cidades do Brasil, oferecendo fretamento para empresas e viagens rodoviárias, além de aluguel de veículos para turismo, sempre com atenção ao conforto dos passageiros.
-Sua frota inclui ônibus modernos, vans e micro-ônibus, todos equipados com ar-condicionado e comodidades que tornam a viagem mais agradável.
-Os serviços da Natal Turismo estão disponíveis através da Buser, que simplifica o processo de reserva, combinando a tradição da empresa com a conveniência do ambiente digital.</t>
+          <t>Fundada em Saquarema (RJ), a HD Turismo se destaca no setor de fretamento rodoviário, atuando de acordo com a regulamentação da ANTT. Especializada em viagens turísticas, a empresa disponibiliza serviços de aluguel de ônibus, micro-ônibus e vans para excursões e traslados.
+Com um foco constante em conforto e segurança, a HD Turismo conecta diversas cidades ao longo de suas rotas. Sua frota inclui veículos modernos, como ônibus de dois andares e leitos, todos equipados com comodidades como ar-condicionado e Wi-Fi, proporcionando uma viagem agradável.
+Para facilitar ainda mais sua experiência, você pode reservar suas viagens com a HD Turismo através da Buser, que oferece um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Natal Turismo pela Buser, desfrutando de total comodidade e segurança.
-A Natal Turismo é especializada em fretamento e oferece transporte para empresas, excursões e aluguel de veículos para turismo, contando com uma frota moderna e bem equipada.
-Ao reservar sua viagem de ônibus com a Natal Turismo na Buser, você tem à disposição um atendimento 24 horas, poltronas confortáveis e a conveniência de um processo de reserva 100% online, proporcionando praticidade do início ao fim.</t>
+          <t>Reserve sua viagem com a HD Turismo pela Buser e desfrute de conforto e praticidade em cada trajeto.
+Especializada em fretamento de ônibus, micro-ônibus e vans, a HD Turismo oferece soluções de transporte ideais para excursões, viagens turísticas e traslados de grupos.
+Ao optar pela HD Turismo na Buser, você tem à disposição um atendimento 24h, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>star-bus</t>
+          <t>lidia-turismo</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Star Bus</t>
+          <t>Lídia Turismo</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Com mais de 20 anos de experiência, a Star Bus Turismo é uma empresa de fretamento rodoviário localizada em Uberlândia, Minas Gerais. Reconhecida no setor, a companhia atua sob a supervisão da ANTT, oferecendo serviços de fretamento intermunicipal, interestadual e internacional.
-A Star Bus liga cidades como Belo Horizonte, Uberlândia e Uberaba, sempre priorizando o conforto e a segurança durante as viagens.
-Sua frota conta com diferentes tipos de veículos, garantindo aos passageiros comodidades como Wi-Fi, poltronas reclináveis e ar-condicionado.
-Para viajar com a Star Bus, você pode reservar sua viagem pela Buser, que disponibiliza um processo totalmente digital e seguro.</t>
+          <t>Fundada há mais de 30 anos, a Lídia Turismo é uma empresa respeitada no ramo de fretamento e excursões, atuando em conformidade com as regulamentações da ANTT. Com sede em Criciúma, Santa Catarina, a companhia se destaca por oferecer viagens tanto nacionais quanto internacionais, além de serviços de "bate-volta" para diversas cidades.
+A frota da Lídia Turismo é composta por veículos de alto padrão, que incluem ônibus double decker e leito-cama, todos equipados com poltronas reclináveis, Wi-Fi e geladeiras, garantindo conforto durante a viagem.
+Para planejar sua viagem com a Lídia Turismo, você pode reservar diretamente através da Buser, que disponibiliza um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Star Bus diretamente pela Buser e desfrute de conforto e segurança em cada trajeto.
-A Star Bus é especializada no fretamento de ônibus para turismo e viagens em grupo, oferecendo rotas que ligam cidades como Belo Horizonte, Uberlândia e Uberaba.
-Ao optar pela Star Bus na Buser, você se beneficia de atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples e eficiente.</t>
+          <t>Reserve sua viagem de ônibus com a Lídia Turismo através da Buser e desfrute de total praticidade e conforto.
+A Lídia Turismo se destaca no fretamento e em excursões, oferecendo uma variedade de viagens nacionais e internacionais com uma frota de alto padrão, que inclui ônibus leito-cama e double decker.
+Ao reservar sua viagem pela Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, proporcionando uma experiência tranquila e segura do início ao fim.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>viacao-pai-eterno</t>
+          <t>nova-opcao-turismo</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Viação Pai Eterno</t>
+          <t>Nova Opção Turismo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fundada em um ano que não está registrado, a Viação Pai Eterno se destaca pelo seu serviço de fretamento entre Minas Gerais e São Paulo, operando de acordo com as normas da ANTT.
-A empresa oferece conexões entre Frutal (MG) e São Paulo (SP), incluindo paradas em cidades como Fronteira (MG), Icém (SP), Nova Granada (SP), São José do Rio Preto (SP) e Campinas (SP), sempre priorizando o conforto e a segurança dos passageiros.
-Com uma frota de ônibus da categoria Semi-Leito, os viajantes desfrutam de poltronas reclináveis e espaço extra, garantindo uma experiência agradável durante toda a viagem.
-Para reservar sua viagem com a Viação Pai Eterno, você pode acessar a plataforma da Buser, que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada no Rio de Janeiro, a Nova Opção Turismo se destaca como uma empresa especializada em fretamento e turismo, conhecida por sua atuação no setor de viagens e excursões. A empresa opera de acordo com a regulamentação da ANTT, o que assegura a conformidade em suas operações de fretamento.
+Com um enfoque em viagens personalizadas, a Nova Opção Turismo disponibiliza serviços que conectam diversas cidades, incluindo excursões temáticas. Seus ônibus de grande porte, como os modelos Marcopolo Paradiso, proporcionam conforto e segurança durante os trajetos.
+A frota é composta por veículos modernos, equipados com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável aos passageiros.
+Para viajar com a Nova Opção Turismo, você pode reservar sua viagem através da Buser, que oferece um processo totalmente digital, unindo tradição e praticidade no planejamento da sua excursão.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Viação Pai Eterno diretamente pela Buser, aproveitando toda a praticidade e conforto que oferecemos.
-A Viação Pai Eterno é especializada em fretamento, proporcionando viagens personalizadas para grupos e eventos. Nossa frota de ônibus semi-leito assegura um conforto superior durante os trajetos.
-Ao reservar sua viagem de ônibus da Viação Pai Eterno na Buser, você se beneficia de atendimento 24 horas, a possibilidade de cancelamento grátis e um processo totalmente online, tornando sua experiência de viagem ainda mais agradável.</t>
+          <t>Reserve sua viagem com a Nova Opção Turismo na Buser e aproveite a comodidade de viajar com segurança e conforto.
+A Nova Opção Turismo é uma empresa dedicada ao fretamento, oferecendo serviços de excursões e pacotes de viagens, tanto para destinos regionais quanto nacionais.
+Ao optar pela sua viagem de ônibus com a Nova Opção Turismo na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de cancelar sua reserva sem complicações. Viajar ficou mais prático e acessível do que nunca.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>amado-turismo</t>
+          <t>pedra-azul</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Amado Turismo</t>
+          <t>Pedra Azul Ônibus</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2010, a Amado Turismo é uma empresa bem reconhecida no setor de transporte rodoviário de passageiros, operando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres). O que a destaca é a oferta de serviços tanto de linhas regulares quanto de fretamento para turismo, conectando importantes cidades de Goiás, Tocantins e Maranhão.
-Sua frota é composta por ônibus convencionais que priorizam o conforto e a segurança dos viajantes. Os veículos contam com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante as viagens.
-Você pode adquirir sua passagem de forma prática e digital na plataforma da Buser, que torna o processo de compra e reserva muito mais fácil.</t>
+          <t>Fundada em 2014, a Pedra Azul Transporte é uma empresa de fretamento e turismo situada em Vitória, Espírito Santo. Reconhecida pela qualidade de suas operações, a empresa é regulamentada pela ANTT, o que assegura segurança e confiabilidade em suas viagens.
+A Pedra Azul conecta diversas cidades por meio de rotas de fretamento, sempre priorizando o conforto e a segurança dos passageiros. Com uma frota moderna, a empresa se destaca ao oferecer ônibus equipados para proporcionar uma experiência agradável durante o trajeto.
+Os veículos da Pedra Azul contam com diferentes opções de conforto e configuração, incluindo poltronas reclináveis, ar-condicionado e Wi-Fi, garantindo uma viagem tranquila e conectada.
+Para viajar com a Pedra Azul, você pode reservar sua viagem pela Buser, onde o processo é totalmente digital, combinando a tradição da empresa com a praticidade das tecnologias atuais.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Adquira sua passagem de ônibus da Amado Turismo por meio da Buser e desfrute de uma experiência prática e segura.
-A Amado Turismo opera linhas regulares de ônibus e também realiza fretamento para excursões, oferecendo transporte entre várias regiões do Brasil, como Goiás, Tocantins e Maranhão.
-Optar pela Buser significa contar com atendimento 24 horas, garantindo suporte sempre que necessário. A possibilidade de remarcação e os preços acessíveis tornam sua viagem ainda mais conveniente e fácil.</t>
+          <t>Descubra sua próxima viagem com a Pedra Azul na Buser, onde conforto e praticidade estão sempre em primeiro lugar.
+Localizada em Vitória, Espírito Santo, a Pedra Azul se destaca no segmento de fretamento e turismo, disponibilizando um transporte rodoviário de alta qualidade, com uma frota moderna e bem equipada.
+Ao reservar sua viagem de ônibus com a Pedra Azul na Buser, você conta com atendimento disponível 24 horas, garantindo uma experiência segura e confortável. Além disso, a Buser facilita a remarcação e oferece cancelamento grátis, o que torna sua viagem ainda mais tranquila e flexível.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="120" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>belos-montes-viagens</t>
+          <t>sussantur-turismo</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Belos Montes Viagens</t>
+          <t>Sussantur Turismo</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2013 em Montes Claros, Minas Gerais, a Belos Montes Viagens se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres).
-A empresa é especialista em fretamento contínuo e eventual, conectando Montes Claros a destinos importantes como Belo Horizonte e Brasília. Além disso, oferece pacotes turísticos para lugares como Porto Seguro, Aparecida e Maceió.
-Sua frota conta com ônibus modernos, incluindo modelos de dois andares e veículos das categorias leito e semi-leito, proporcionando conforto em todas as viagens.
-Para reservar sua viagem com a Belos Montes Viagens, você pode usar a Buser, que disponibiliza um processo totalmente digital, tornando mais fácil encontrar os serviços de fretamento que você precisa.</t>
+          <t>Fundada há mais de 45 anos, a Sussantur Transporte, Turismo e Fretamento Ltda. é uma empresa brasileira reconhecida pela sua expertise em fretamento e turismo, regulamentada pela ANTT. 
+Com um forte foco no transporte corporativo, a Sussantur se empenha em oferecer uma logística eficiente para empresas. Além disso, disponibiliza serviços de fretamento eventual e turismo, incluindo excursões e city tours.
+A frota da Sussantur é moderna e diversificada, priorizando o conforto e a segurança durante as viagens. Os veículos contam com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável para todos os passageiros.
+Para viajar com a Sussantur, você pode reservar diretamente pela Buser, que proporciona um processo de reserva totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Belos Montes Viagens diretamente pela Buser, onde conforto e praticidade se encontram.
-A Belos Montes Viagens é uma empresa dedicada ao fretamento e turismo, disponibilizando pacotes para destinos populares e excursões em grupo, sempre com ônibus modernos e confortáveis.
-Ao optar pela Buser, você conta com uma experiência de viagem segura e tranquila, com atendimento 24 horas e a vantagem do cancelamento grátis, o que torna cada deslocamento mais flexível e acessível.</t>
+          <t>Reserve sua viagem com a Sussantur diretamente na Buser e aproveite a praticidade que você merece.
+Com mais de 45 anos de tradição, a Sussantur é uma empresa brasileira especializada em fretamento de ônibus para turismo, eventos e transporte corporativo. A empresa se destaca pela pontualidade e pelo conforto em cada trajeto.
+Ao reservar sua viagem de ônibus da Sussantur na Buser, você conta com uma experiência segura, poltronas confortáveis e atendimento 24 horas, o que torna sua jornada ainda mais tranquila e agradável.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>brasil-way-tour</t>
+          <t>vale-do-sul-turismo</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>São José Viagens</t>
+          <t>Vale do Sul Turismo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fundada há quase 80 anos em Belo Horizonte, a São José Viagens é uma operadora de destaque, conhecida por sua tradição em fretamento e turismo, e possui autorização da ANTT para realizar operações interestaduais.
-A empresa se diferencia ao oferecer viagens em grupo, priorizando conforto e segurança, enquanto conecta diversas rotas e destinos tanto dentro quanto fora de Minas Gerais.
-Com uma frota variada, a São José Viagens disponibiliza veículos equipados com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência agradável durante as viagens.
-Para viajar com a São José Viagens, você pode reservar diretamente pelo canal digital da Buser, que oferece um processo totalmente online e livre de taxas excessivas.</t>
+          <t>Fundada em Vespasiano, na Região Metropolitana de Belo Horizonte, a Vale do Sul Turismo é reconhecida pela sua tradição no fretamento e em serviços de viagem, operando de acordo com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
+A empresa se destaca ao oferecer transporte para empresas, escolas e eventos, priorizando sempre o conforto e a segurança em suas operações. Suas rotas abrangem excursões regionais e serviços para grupos, atendendo a diferentes demandas de viagem.
+A frota da Vale do Sul é composta por vans executivas e ônibus semi-leito, todos equipados com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante a viagem.
+Para reservar sua viagem com a Vale do Sul Turismo, você pode acessar a plataforma da Buser, que proporciona um processo totalmente digital e prático.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a São José Viagens diretamente na Buser e desfrute de toda a comodidade e segurança que oferecemos.
-A São José Viagens é uma respeitada operadora e agência de turismo com sede em Belo Horizonte, focada em excursões e viagens em grupo, apresentando roteiros tanto nacionais quanto internacionais.
-Ao fazer sua reserva de viagem de ônibus com a São José Viagens na Buser, você tem à disposição atendimento 24 horas, facilidade na remarcação e poltronas confortáveis, tornando seu trajeto relaxante e agradável.</t>
+          <t>Reserve sua viagem com a Vale do Sul Turismo pela Buser e desfrute de toda a praticidade e segurança que você merece.
+A Vale do Sul Turismo é especializada em fretamento e serviços de viagem, proporcionando transporte para empresas, escolas e eventos, além de oferecer pacotes de excursões regionais.
+Com a Buser, sua experiência de viagem se torna ainda mais conveniente: você tem à disposição atendimento 24h, cancelamento grátis e poltronas confortáveis, assegurando um trajeto tranquilo do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="120" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>expresso-satelite-norte</t>
+          <t>viacao-smart</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>EXPRESSO SATELITE NORTE</t>
+          <t>Viação Smart</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fundada em fevereiro de 1996, a Expresso Satélite Norte se destaca no setor de transporte rodoviário, sendo reconhecida pela qualidade e segurança de seus serviços, sempre em conformidade com as regulamentações da ANTT (Agência Nacional de Transportes Terrestres).
-A empresa oferece conexões entre diversos estados nas regiões Centro-Oeste, Norte e Nordeste do Brasil, com foco em viagens de longa distância que priorizam o conforto. Você pode escolher entre opções de ônibus Executivo, Leito e Leito-Cama, todas projetadas para proporcionar uma experiência agradável.
-Com uma frota moderna equipada com poltronas reclináveis, a Expresso Satélite Norte também disponibiliza serviços de encomendas e fretamento, ampliando suas possibilidades de transporte.
-Para tornar sua experiência ainda mais prática, a Expresso Satélite Norte está integrada à plataforma da Buser, permitindo que você reserve seu fretamento de forma 100% digital e segura.</t>
+          <t>Fundada em Campinas, São Paulo, a Viação Smart Fretamento e Locação Ltda. se destaca pela sua tradição no fretamento corporativo e de turismo, atuando de acordo com as normas da ANTT. 
+A empresa é reconhecida pela pontualidade e pelo conforto que proporciona, realizando transporte diário de funcionários e oferecendo viagens turísticas para destinos encantadores, como as cidades históricas de Minas Gerais. 
+Sua frota conta com micro-ônibus e ônibus premium, todos equipados com ar-condicionado, Wi-Fi e entradas USB, o que assegura uma viagem agradável e segura. 
+Para viajar com a Viação Smart, você pode reservar seu fretamento através do canal oficial da Buser, que disponibiliza um processo totalmente digital e livre de taxas abusivas.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com o Expresso Satélite Norte na Buser e desfrute de conforto e praticidade.
-O Expresso Satélite Norte se especializa em fretamento e turismo, disponibilizando roteiros que conectam diversas regiões do Brasil, incluindo o Centro-Oeste, Norte e Nordeste.
-Optar pela Buser significa embarcar em uma viagem segura, com poltronas confortáveis e atendimento 24 horas, o que torna sua experiência ainda mais prazerosa.</t>
+          <t>Descubra sua viagem com a Viação Smart diretamente pela Buser, de forma prática e segura.
+A Viação Smart se destaca no transporte de passageiros, com foco em fretamento corporativo e turismo, disponibilizando serviços para eventos e excursões.
+Ao reservar sua viagem de ônibus da Viação Smart na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, proporcionando uma experiência tranquila do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="120" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>jc-turismo</t>
+          <t>zelitur-turismo</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>JC Turismo</t>
+          <t>Zelitur Turismo</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1994 e situada em Valinhos, São Paulo, a JC Turismo se destaca no segmento de fretamento e transporte rodoviário, operando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres). A empresa é conhecida pela eficiência e qualidade de suas operações, oferecendo serviços de fretamento contínuo e eventual para eventos e excursões.
-A frota da JC Turismo conta com ônibus e micro-ônibus, priorizando sempre o conforto e a segurança dos passageiros. Os veículos são equipados para proporcionar uma experiência agradável, tanto em trajetos municipais quanto intermunicipais.
-Para viajar com a JC Turismo, você pode reservar suas viagens pela plataforma Buser, que oferece um processo totalmente digital e seguro, combinando tradição e inovação na mobilidade.</t>
+          <t>Fundada em Concórdia, Santa Catarina, a Zelitur é uma empresa de fretamento e turismo, destacando-se na região sul do Brasil. A companhia opera em conformidade com a regulamentação da ANTT, oferecendo serviços de transporte para eventos, excursões e turismo social.
+Com ênfase no conforto e segurança, a Zelitur conecta várias cidades por meio de sua frota de ônibus rodoviários, que inclui modelos Double Decker, projetados para longas distâncias.
+Os veículos são modernos e contam com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência de viagem agradável.
+Para reservar sua viagem com a Zelitur, você pode usar a Buser, uma plataforma digital que torna o processo mais prático e seguro.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a JC Turismo diretamente na Buser e desfrute de uma experiência prática e segura.
-A JC Turismo é uma empresa dedicada ao fretamento empresarial e ao turismo, oferecendo serviços de transporte rodoviário para excursões e eventos, sempre priorizando o conforto dos passageiros.
-Ao escolher a Buser, você tem à disposição uma viagem segura, poltronas confortáveis e atendimento 24 horas, o que torna sua experiência mais tranquila e acessível.</t>
+          <t>Reserve sua viagem com a Zelitur na Buser e desfrute do conforto das melhores opções de fretamento.
+A Zelitur é uma empresa focada no fretamento de ônibus, proporcionando transporte para eventos e turismo social. Sua frota inclui modelos de grande porte e Double Decker, garantindo diversidade para atender diferentes necessidades.
+Ao reservar sua viagem de ônibus da Zelitur na Buser, você tem à disposição um atendimento 24 horas, cancelamento grátis e poltronas confortáveis, assegurando uma experiência de viagem tranquila e agradável.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>marlim-azul-turismo</t>
+          <t>abelazeri-turismo</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Marlim Azul Turismo</t>
+          <t>Abelazeri Turismo</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2000, a Marlim Azul se destacou no setor de fretamento e turismo no Espírito Santo, sendo reconhecida pela ANTT. Com 25 anos de trajetória, a empresa se firmou como uma referência em viagens de turismo e fretamento.
-A Marlim Azul prioriza o conforto e a segurança, conectando diversas cidades e destinos tanto dentro do estado quanto em rotas interestaduais, sempre buscando atender às expectativas dos passageiros.
-Sua frota é composta por ônibus equipados com climatização, poltronas confortáveis e tecnologia de ponta, proporcionando uma experiência agradável ao longo de toda a viagem.
-Para reservar sua viagem com a Marlim Azul, você pode utilizar a plataforma da Buser, que oferece um processo 100% digital e seguro, unindo tradição e inovação na experiência de fretamento.</t>
+          <t>Fundada em Criciúma, Santa Catarina, a Abelazeri Turismo é uma referência no segmento de fretamento e turismo, com autorização da ANTT para operar viagens interestaduais.
+Com mais de dez anos de experiência, a empresa se destaca pela priorização da segurança e do conforto, conectando diversos destinos ao longo do Brasil.
+Sua frota moderna conta com ônibus de grande porte, como os modelos Marcopolo Paradiso G8 1800DD, que oferecem comodidades como ar-condicionado e poltronas reclináveis.
+Para viajar com a Abelazeri, você pode reservar suas viagens de maneira prática e segura por meio da Buser, desfrutando da conveniência de um processo totalmente digital.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Descubra sua próxima viagem com a Marlim Azul Turismo através da Buser, garantindo o conforto que você merece.
-A Marlim Azul Turismo se destaca no fretamento e turismo, proporcionando experiências inesquecíveis em viagens de grupo pelo Brasil e no exterior, tudo isso com uma frota moderna e segura.
-Ao reservar sua viagem de ônibus com a Marlim Azul Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples e prático, tornando sua experiência ainda mais agradável e descomplicada.</t>
+          <t>Reserve sua viagem com a Abelazeri Turismo pela Buser e desfrute de conforto e praticidade.
+A Abelazeri é uma empresa dedicada ao fretamento e às viagens de turismo, com sede em Criciúma, Santa Catarina. Ela disponibiliza ônibus modernos e espaçosos, incluindo opções de dois andares.
+Ao reservar sua viagem com a Abelazeri na Buser, você tem à disposição atendimento 24 horas, uma viagem segura e a conveniência de remarcação, o que torna sua experiência ainda mais tranquila e flexível.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="120" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>marlu-turismo</t>
+          <t>amarelinho-viacao</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Marlu Turismo</t>
+          <t>Amarelinho Viação</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Com mais de 20 anos de experiência, a Marlu Turismo se destaca como uma empresa de fretamento e turismo no Brasil, atuando de acordo com as normas da ANTT (Agência Nacional de Transportes Terrestres).
-Localizada em Duque de Caxias, no estado do Rio de Janeiro, a Marlu oferece uma variedade de opções para viagens de turismo interestadual, incluindo passeios em grupo e eventos religiosos, conectando diferentes cidades e destinos.
-A frota da Marlu Turismo é composta por veículos modernos, como os ônibus de dois andares Marcopolo Paradiso G8 DD, que contam com ar-condicionado e poltronas reclináveis, proporcionando uma experiência confortável durante as viagens.
-Para facilitar a reserva da sua viagem, a Marlu Turismo é parceira da Buser, possibilitando um processo 100% digital e seguro, ideal para quem valoriza praticidade ao reservar fretamento.</t>
+          <t>Fundada em 2019 por Camila Valdívia, a Viação Amarelinho conquistou reconhecimento no setor de transporte rodoviário e possui autorização da ANTT para operar rotas interestaduais.
+A empresa se destaca na oferta de serviços de fretamento e turismo, estabelecendo conexões entre cidades como São Paulo e Minas Gerais, sempre priorizando o conforto e a segurança dos passageiros.
+Sua frota conta com ônibus Double Deck, projetados para proporcionar uma experiência única, equipados com comodidades como Wi-Fi, poltronas reclináveis e ar-condicionado.
+Para tornar suas viagens ainda mais práticas, a Amarelinho Viação está disponível na plataforma Buser, onde você pode reservar suas viagens de forma segura e conveniente.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Marlu Turismo diretamente na Buser e aproveite a combinação de conforto e praticidade.
-Com mais de 20 anos de experiência, a Marlu Turismo se destaca no fretamento e turismo, oferecendo transporte para passeios, eventos e viagens em grupo.
-Ao optar por reservar sua viagem de ônibus da Marlu Turismo na Buser, você tem acesso a um atendimento 24h, poltronas confortáveis e um processo de reserva totalmente online, tornando sua experiência de viagem mais simples e agradável do início ao fim.</t>
+          <t>Reserve sua viagem com a Amarelinho Viação diretamente na Buser e desfrute de praticidade e confiança.
+A Amarelinho Viação é uma empresa dedicada ao fretamento para turismo e viagens em grupo, oferecendo serviços de transporte rodoviário que priorizam conforto e qualidade.
+Ao escolher a Amarelinho Viação para sua viagem de ônibus na Buser, você conta com atendimento 24 horas, facilidade para remarcação e um processo de reserva totalmente online, tornando sua experiência ainda mais tranquila.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>nobre-empresa</t>
+          <t>ao-juliano-turismo</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Nobre Empresa</t>
+          <t>Juliano Turismo</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fundada há mais de 9 anos, a Nobre Empresa se destaca no setor de fretamento e turismo, com a autorização da ANTT para operar viagens interestaduais de forma segura e de alta qualidade.
-A empresa conecta diversas cidades, sempre buscando proporcionar conforto e eficiência aos seus clientes durante as viagens, atendendo tanto o setor corporativo quanto grupos de turismo.
-A frota da Nobre é composta por veículos modernos, que contam com Wi-Fi, poltronas reclináveis e ar-condicionado, assegurando uma experiência agradável e confortável para os viajantes.
-Para realizar sua viagem com a Nobre, você pode reservar de maneira prática através da Buser, o que torna o processo digital seguro e ágil.</t>
+          <t>Com mais de 18 anos de experiência, a Juliano Turismo é uma empresa de transporte rodoviário reconhecida pela excelência em seus serviços de fretamento e turismo. Autorizada pela ANTT, a empresa se destaca ao oferecer pacotes turísticos e excursões regionais para diversos destinos, como Aparecida do Norte e Balneário Camboriú.
+A Juliano Turismo conecta cidades como Cravinhos e Ribeirão Preto, priorizando o conforto e a segurança de seus passageiros.
+Sua frota é composta por veículos que contam com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência agradável em todas as viagens.
+Para reservar sua viagem com a Juliano Turismo, você pode utilizar a Buser, que facilita um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Nobre Empresa diretamente pela Buser e desfrute de conforto e praticidade.
-A Nobre Empresa se destaca no fretamento de veículos para grupos, oferecendo soluções de transporte personalizadas para eventos, excursões e viagens.
-Ao reservar sua viagem de ônibus com a Nobre Empresa na Buser, você tem acesso a um atendimento 24h, poltronas confortáveis e a conveniência de realizar tudo online, sem complicações.
-Descubra a segurança e a eficiência que a Buser traz para suas viagens em grupo.</t>
+          <t>Adquira sua viagem de ônibus com a Juliano através da Buser e desfrute de um serviço de qualidade.
+A Juliano é uma empresa que atua em linhas regulares e fretamento, proporcionando opções que atendem a diferentes necessidades de transporte.
+Ao escolher a Buser, você tem acesso a vantagens como atendimento 24 horas, cancelamento grátis e poltronas confortáveis, garantindo que sua viagem seja tranquila e confortável.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="120" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>vanzella-transportes</t>
+          <t>betel-turismo</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Vanzella Transportes</t>
+          <t>Betel Turismo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Com mais de 20 anos de experiência, a Vanzella Transportes é uma empresa brasileira reconhecida pela sua atuação no setor de fretamento e turismo, devidamente regulamentada pela ANTT.
-A atuação da empresa é concentrada em Mato Grosso do Sul, onde proporciona serviços de transporte tanto compartilhado quanto privativo. Isso inclui conexões do Aeroporto Internacional de Campo Grande a destinos turísticos como Bonito e Serra da Bodoquena.
-Sua frota é diversificada, contando com vans para 15 passageiros, micro-ônibus para 26 e ônibus semi-leito ou leito, assegurando um alto nível de conforto durante suas viagens.
-Para planejar sua viagem com a Vanzella, você pode fazer a reserva através da Buser, que oferece um processo digital simples e seguro.</t>
+          <t>Fundada em 2018, a Betel Turismo é uma empresa de transporte rodoviário que se destaca pela seriedade e qualidade de suas operações, sempre em conformidade com a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
+Especializada no fretamento de viagens, a empresa oferece roteiros para diversos destinos, priorizando conforto e segurança, mesmo que a localização exata de sua sede não esteja divulgada.
+Sua frota é composta por veículos de categorias como leito e semi-leito, todos equipados com comodidades como ar-condicionado e Wi-Fi, garantindo uma experiência agradável para os passageiros.
+Ao reservar sua viagem com a Betel Turismo pela Buser, você usufrui de um processo 100% digital, que combina tradição e praticidade na sua mobilidade.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Vanzella Transportes diretamente pela Buser e aproveite todo o conforto e a praticidade que oferecemos.
-A Vanzella Transportes se destaca no setor de fretamento e turismo, proporcionando serviços de transporte compartilhado e privativo entre Campo Grande e destinos turísticos como Bonito.
-Com a Buser, sua experiência de viagem se torna ainda mais agradável, contando com atendimento 24 horas, poltronas confortáveis e a facilidade de realizar reservas online de maneira descomplicada.</t>
+          <t>Reserve sua viagem com a Betel Turismo diretamente pela Buser e aproveite um serviço prático e confiável.
+A Betel Turismo é especializada em fretamento e turismo, proporcionando experiências únicas em excursões e viagens para uma variedade de destinos, desde passeios religiosos até opções de lazer.
+Ao escolher a Buser, você tem a tranquilidade de uma viagem segura, com atendimento 24h e poltronas confortáveis, que tornam cada trajeto ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="120" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>expresso-joia</t>
+          <t>caburai-transportes</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>EXPRESSO JOIA</t>
+          <t>Caburai Transportes</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fundada na década de 1970 em Ibaití, no Paraná, a Expresso Jóia, anteriormente chamada de Viação Jóia, é uma empresa de transporte rodoviário de destaque, autorizada pela ANTT para operações interestaduais.
-Com mais de quarenta anos de experiência, a Expresso Jóia se destaca no fretamento de viagens turísticas, ligando cidades importantes entre os estados de São Paulo e Paraná, sempre priorizando a segurança e a qualidade dos serviços.
-A frota conta com veículos modernos, nas categorias executivo e leito, que vêm equipados com ar-condicionado e poltronas reclináveis, proporcionando conforto durante toda a viagem.
-Os interessados podem reservar suas viagens com a Expresso Jóia por meio da Buser, que oferece um processo totalmente digital, combinando praticidade com a tradição da empresa.</t>
+          <t>Fundada há várias décadas, a Caburai Transportes é uma empresa respeitada no setor de transporte rodoviário, devidamente regulamentada pela ANTT, o que assegura sua atuação em rotas interestaduais.
+Com uma operação sólida, a empresa se destaca pela confiabilidade e pela qualidade de suas viagens, conectando diversas cidades em todo o Brasil.
+Sua frota é composta por diferentes categorias de veículos, incluindo convencionais e executivos, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, garantindo conforto aos passageiros.
+Para planejar sua viagem com a Caburai Transportes, você pode utilizar a Buser, que proporciona um processo digital seguro e prático para a compra das suas viagens.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Expresso Jóia diretamente pela Buser e desfrute de conforto e praticidade na sua escolha.
-A Expresso Jóia se destaca no fretamento de passageiros, conectando várias cidades nos estados de São Paulo e Paraná, com opções ideais para grupos e turismo.
-Ao reservar sua viagem de ônibus da Expresso Jóia na Buser, você conta com atendimento 24 horas, uma experiência de viagem segura e a facilidade de remarcação, tornando seu planejamento muito mais tranquilo.</t>
+          <t>Adquira sua viagem de ônibus com a Caburai Transportes pela Buser, aproveitando a praticidade e a segurança que oferecemos.
+A Caburai Transportes é uma empresa especializada no transporte rodoviário de passageiros, atuando tanto no fretamento quanto no turismo, especialmente na região Norte do Brasil.
+Optando pela Buser, você conta com atendimento 24 horas e pode desfrutar de uma viagem segura e confortável. Além disso, a compra é feita de maneira online e descomplicada, facilitando ainda mais sua experiência.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="120" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>expresso-solucao</t>
+          <t>darosa-tur</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Expresso Solução</t>
+          <t>Darosa Tur</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 13 de agosto de 2020 em Brasília, a Expresso Solução Transportes e Turismo se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT.
-A empresa liga o Distrito Federal a importantes cidades de Minas Gerais, como Montes Claros e Pirapora, sempre colocando o conforto e a segurança dos passageiros em primeiro lugar.
-Sua frota conta com ônibus equipados com ar-condicionado, assentos reclináveis e Wi-Fi, proporcionando uma viagem agradável e tranquila.
-As viagens com a Expresso Solução podem ser reservadas por meio da Buser, que oferece um processo digital prático e seguro para os usuários.</t>
+          <t>Fundada há várias décadas, a Darosa Tur é uma empresa respeitada no setor de transporte rodoviário e está regulada pela ANTT (Agência Nacional de Transportes Terrestres), o que assegura que suas operações interestaduais estejam em conformidade com as normas.
+A empresa se destaca por priorizar o conforto e a segurança em seus serviços, conectando diversas cidades e estados, mesmo que informações específicas sobre sua sede e rotas não estejam disponíveis.
+A frota da Darosa Tur é composta por ônibus de diferentes categorias, incluindo opções com poltronas reclináveis, ar-condicionado e Wi-Fi, proporcionando uma experiência agradável aos passageiros.
+Para viajar com a Darosa Tur, você pode utilizar a Buser, que oferece um processo de compra digital. Essa união entre a tradição da empresa e a praticidade da tecnologia torna sua experiência ainda mais conveniente.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Expresso Solução diretamente na Buser, de forma simples e confiável.
-A Expresso Solução é uma empresa especializada em fretamento e turismo, ligando o Distrito Federal a diversas cidades de Minas Gerais e Goiás, sempre com foco no conforto e na segurança das rotas.
-Ao escolher a Buser, você encontra ainda mais vantagens, como atendimento disponível 24 horas, cancelamento grátis e poltronas confortáveis, permitindo que você relaxe e desfrute do trajeto.</t>
+          <t>Reserve sua viagem com a Darosa Tur na Buser e aproveite toda a comodidade que você merece.
+A Darosa Tur se destaca no fretamento e turismo, apresentando roteiros fascinantes e serviços personalizados para suas viagens em grupo.
+Optar pela Buser significa desfrutar de uma viagem segura, com atendimento 24 horas e a facilidade de remarcação, proporcionando mais praticidade durante sua jornada.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="120" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>grandino-turismo</t>
+          <t>fertur-viagens</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Grandino Turismo</t>
+          <t>Fertur Viagens</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2021, a Grandino Turismo se destaca no setor de fretamento e viagens turísticas no Brasil, com operações regulamentadas pela ANTT (Agência Nacional de Transportes Terrestres). A empresa é bem vista por sua confiabilidade e pela qualidade dos serviços oferecidos.
-A Grandino Turismo atende diversas regiões, priorizando conforto e segurança, e conecta cidades em São Paulo e arredores, como Guarulhos e Itaquaquecetuba.
-Sua frota moderna conta com ônibus executivos, Semi-Leito e Double Deck, todos equipados com ar-condicionado, Wi-Fi, entradas USB, poltronas reclináveis e geladeiras a bordo.
-Os serviços de fretamento da Grandino Turismo podem ser reservados na Buser, proporcionando um processo totalmente digital e prático para suas viagens.</t>
+          <t>Fundada em Santa Catarina, a Fertur Viagens é uma empresa bem reconhecida no setor de fretamento e turismo, com a regulamentação da ANTT, o que assegura um padrão elevado de qualidade e segurança em suas operações.
+Com foco em viagens em grupo e excursões, a Fertur conecta várias cidades, oferecendo roteiros para destinos populares no Brasil e na América do Sul, como Foz do Iguaçu e Natal Luz.
+A frota da Fertur conta com veículos confortáveis, equipados com poltronas reclináveis, ar-condicionado e Wi-Fi, proporcionando uma experiência agradável durante suas viagens.
+Para reservar sua viagem com a Fertur Viagens, você pode usar a Buser, que disponibiliza um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Grandino Turismo diretamente pela Buser e aproveite a praticidade e segurança que oferecemos.
-A Grandino Turismo se destaca no fretamento e nas viagens turísticas, proporcionando transporte de passageiros para várias regiões do Brasil com conforto e eficiência.
-Ao fazer sua reserva com a Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade do cancelamento grátis, o que torna sua experiência ainda mais agradável e despreocupada.</t>
+          <t>Faça sua reserva de viagem com a Fertur Viagens diretamente na Buser e desfrute da conveniência de um serviço online.
+A Fertur Viagens se destaca no fretamento e turismo, oferecendo excursões e pacotes para uma variedade de destinos no Brasil e na América do Sul, além de transporte universitário.
+Optando pela Buser, você tem à disposição um atendimento 24h, poltronas confortáveis e a facilidade do cancelamento grátis, o que torna sua viagem mais agradável e sem estresse.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="120" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>helios-empresa</t>
+          <t>guerro-transportes-e-viagens</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Helios Empresa</t>
+          <t>GUERRO TRANSPORTES E VIAGENS</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Fundada na década de 1940 em Carazinho, no Rio Grande do Sul, a Helios é uma empresa tradicional no setor de fretamento e turismo, além de atuar em conexões interestaduais regularizadas pela ANTT.
-Com mais de 75 anos de experiência, a Helios se destaca pela segurança e conforto, operando rotas que conectam as regiões Sul, Sudeste, Centro-Oeste e Norte do Brasil.
-Sua frota é composta por ônibus convencionais, semi-leito e leito, todos equipados com poltronas acolchoadas, ar-condicionado e Wi-Fi, o que garante uma experiência agradável ao longo da viagem.
-Você pode reservar suas viagens pela Buser, que oferece um processo 100% digital e seguro.</t>
+          <t>Fundada em 2012, a Guerro Transportes e Viagens se destaca no setor de fretamento e turismo no Brasil. Com a operação regulamentada pela ANTT (Agência Nacional de Transportes Terrestres), a empresa oferece viagens interestaduais que prezam pela segurança e confiabilidade.
+Com forte presença nas regiões do Sul do Brasil, a Guerro disponibiliza fretamentos para várias rotas, incluindo passeios a São Paulo e eventos especiais, como a Feira da Madrugada no Brás, sempre priorizando o conforto e a segurança dos passageiros.
+Sua frota é composta por ônibus de categoria leito total, equipados com ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante a viagem.
+Para viajar com a Guerro, você pode reservar sua viagem de fretamento através da Buser, que proporciona um processo totalmente digital, livre de taxas abusivas.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Helios diretamente pela Buser e aproveite a facilidade do fretamento.
-A Helios é uma empresa brasileira com tradição no transporte rodoviário, focada em fretamento e turismo, e possui uma presença marcante em rotas intermunicipais e interestaduais.
-Ao reservar sua viagem de ônibus da Helios na Buser, você desfruta da tranquilidade de um atendimento disponível 24 horas, da conveniência de um processo de reserva online e de poltronas confortáveis, tudo pensado para tornar sua experiência mais agradável.</t>
+          <t>Reserve sua viagem com a GUERRO TRANSPORTES E VIAGENS pela Buser e desfrute de conforto e praticidade.
+A GUERRO TRANSPORTES E VIAGENS é especialista em fretamento de ônibus para turismo e viagens em grupo, com forte atuação nas regiões do Sul do Brasil.
+Ao reservar sua viagem de ônibus com a GUERRO TRANSPORTES E VIAGENS na Buser, você terá acesso a um atendimento 24 horas, a segurança de uma viagem bem planejada e a possibilidade de cancelamento grátis, o que traz tranquilidade e flexibilidade em todo o processo.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="120" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>jr-turismo-empresa</t>
+          <t>life-transportes</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>JR Turismo Empresa</t>
+          <t>Life Transportes</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2015, a JR Turismo se destaca no setor de fretamento e turismo, sendo reconhecida pela segurança e conforto que proporciona aos seus clientes. A empresa opera em conformidade com as normas da ANTT, assegurando a qualidade no serviço de transporte.
-Com um foco especial em viagens intermunicipais e interestaduais, a JR Turismo conecta diversas cidades e oferece roteiros personalizados para passeios e excursões.
-Sua frota é composta por ônibus, micro-ônibus e vans, todos equipados com comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante a viagem.
-Para viajar com a JR Turismo, você pode reservar sua viagem através da Buser, uma plataforma digital que torna o processo de fretamento mais simples, unindo tradição e praticidade.</t>
+          <t>Com uma sólida tradição no transporte rodoviário, a Life Transportes se destaca no setor, atuando de acordo com as regulamentações da ANTT. 
+A empresa prioriza o conforto e a segurança, conectando várias cidades e estados, incluindo rotas interestaduais que atendem a um público diversificado. 
+Sua frota é composta por veículos modernos, com opções que variam entre convencional e executivo, além de oferecer comodidades como Wi-Fi, ar-condicionado e poltronas reclináveis. 
+Os clientes podem aproveitar suas viagens com a Life Transportes de maneira prática e segura por meio da Buser, que disponibiliza um processo totalmente digital para a compra e reserva das viagens.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a JR Turismo na Buser e desfrute da praticidade e segurança que você realmente merece.
-A JR Turismo é especialista no fretamento de vans, micro-ônibus e ônibus para viagens intermunicipais e interestaduais, oferecendo serviços de alta qualidade voltados para grupos e excursões.
-Ao reservar sua viagem de ônibus da JR Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, tudo isso para proporcionar uma experiência de viagem mais tranquila e conveniente.</t>
+          <t>Reserve sua viagem com a Life Transportes diretamente na Buser, garantindo praticidade e segurança.
+A Life Transportes se destaca no fretamento para turismo e viagens, apresentando soluções personalizadas para grupos e excursões.
+Ao reservar sua viagem de ônibus da Life Transportes na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a comodidade do cancelamento grátis, o que torna sua jornada ainda mais prazerosa.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="120" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>levare-transportes</t>
+          <t>oliver-turismo</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Levare Transportes</t>
+          <t>Oliver Turismo</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Fundada em um ano não especificado, a Levare Transportes é uma empresa brasileira de transporte rodoviário de passageiros, autorizada pela ANTT, e é reconhecida por oferecer um serviço de qualidade.
-A Levare tem como prioridade o conforto, conectando importantes cidades do estado de São Paulo, como São Paulo, São José do Rio Preto e Ribeirão Preto, a destinos como Rio de Janeiro, Brasília e Belo Horizonte.
-Sua frota é composta por ônibus leito-cama, equipados com poltronas reclináveis, Wi-Fi, tomadas e serviço de bordo, proporcionando uma experiência agradável durante a viagem.
-Os passageiros podem adquirir suas viagens pela Buser, um canal digital que torna o processo de compra mais seguro e prático.</t>
+          <t>Fundada em Nova Iguaçu (RJ), a Oliver Turismo é uma empresa especializada em fretamento e agenciamento de viagens, reconhecida pela organização de excursões e passeios. Ela opera de acordo com a regulamentação da ANTT.
+Com mais de dez anos de experiência, a Oliver Turismo tem como prioridade oferecer conforto e segurança em suas viagens, conectando diferentes localidades por meio de serviços personalizados.
+A frota da empresa é composta por ônibus modernos e bem equipados, que dispõem de comodidades como ar-condicionado e poltronas reclináveis. Isso proporciona uma experiência agradável durante a viagem.
+Para reservar sua viagem com a Oliver Turismo, você pode contar com a Buser, que torna o processo 100% digital e seguro.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Levare Transportes diretamente na Buser e desfrute da qualidade que você merece.
-A Levare Transportes é uma empresa brasileira que se destaca por oferecer viagens de alto padrão, utilizando ônibus leito-cama e proporcionando um serviço diferenciado em rotas que ligam importantes cidades.
-Ao escolher a Buser, você tem a tranquilidade de contar com uma viagem segura, poltronas confortáveis e a praticidade de adquirir sua passagem online de forma rápida e simples. E, para completar, o atendimento 24 horas está sempre à disposição para auxiliar em qualquer necessidade que você possa ter.</t>
+          <t>Reserve sua viagem com a Oliver Turismo diretamente pela Buser e desfrute de conforto e praticidade em todas as etapas.
+A Oliver Turismo se destaca no fretamento e na organização de viagens e excursões, especialmente em sua unidade em Nova Iguaçu (RJ), onde oferece serviços de qualidade para grupos e eventos.
+Ao reservar sua viagem de ônibus da Oliver Turismo na Buser, você tem à disposição atendimento 24h, poltronas confortáveis e um processo de reserva online simples, garantindo uma experiência mais tranquila e agradável.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="120" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>roderotas</t>
+          <t>sairu-turismo</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>RodeRotas</t>
+          <t>SAIRU TURISMO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Com mais de 50 anos de história, a RodeRotas, também conhecida como Rotas de Viação do Triângulo, é uma empresa brasileira que atua no transporte rodoviário de passageiros, sempre em conformidade com as diretrizes da ANTT (Agência Nacional de Transportes Terrestres).
-A companhia é reconhecida por sua conexão entre cidades como Brasília, Belém, Goiânia, São Paulo, Foz do Iguaçu e Uberlândia, oferecendo viagens de longa e média distância. O foco em segurança e conforto para os passageiros é uma das suas marcas registradas.
-A frota da RodeRotas é equipada com veículos que priorizam o bem-estar dos viajantes, disponibilizando comodidades como ar-condicionado e poltronas reclináveis, o que contribui para uma experiência agradável ao longo da viagem.
-Para reservar sua viagem com a RodeRotas, você pode utilizar a Buser, que proporciona um processo de compra totalmente digital, combinando tradição e praticidade na sua mobilidade.</t>
+          <t>Com mais de 35 anos de experiência, a Sairú Turismo é uma empresa brasileira dedicada ao fretamento e ao turismo, atuando sob a regulamentação da ANTT. A companhia se destaca na realização de viagens intermunicipais, interestaduais e internacionais, atendendo a diversos tipos de turismo, como lazer e eventos.
+A Sairú utiliza ônibus rodoviários de padrão executivo, conectando cidades com conforto e segurança. Os veículos são equipados com ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável para todos os passageiros.
+A frota da Sairú foi projetada para atender a diferentes demandas, oferecendo serviços que se adequam às necessidades de grupos e eventos. Com uma estrutura focada no turismo, a empresa se esforça para criar experiências de viagem memoráveis.
+Quem deseja viajar com a Sairú pode reservar suas viagens através da Buser, que facilita o processo com uma plataforma digital segura e prática, unindo tradição e inovação no setor.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem de ônibus da RodeRotas na Buser e viaje com conforto e segurança.
-A RodeRotas é uma reconhecida empresa de transporte rodoviário de passageiros, atuando principalmente em trajetos de longa e média distância, ligando grandes cidades do Brasil, como Brasília, São Paulo e Foz do Iguaçu.
-Ao optar pela Buser, você usufrui de uma viagem segura, poltronas confortáveis e a praticidade de um processo de compra totalmente online, proporcionando uma experiência tranquila do início ao fim da sua jornada.</t>
+          <t>Reserve sua viagem com a SAIRU TURISMO na Buser e aproveite momentos incríveis com conforto e segurança.
+A SAIRU TURISMO é especializada em fretamento e serviços de turismo, proporcionando transporte coletivo para lazer, eventos e excursões em grupo, tudo isso com uma frota equipada para oferecer uma experiência de viagem superior.
+Ao escolher a Buser, você conta com um atendimento 24 horas, a possibilidade de cancelamento grátis e poltronas confortáveis, o que torna sua viagem ainda mais prazerosa e prática.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="120" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>scatur-empresa</t>
+          <t>viacao-clewis</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Scatur Empresa</t>
+          <t>Viação Clewis</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Fundada em Tietê, São Paulo, a Scatur se destaca no setor de fretamento e turismo, atuando de acordo com as normas da ANTT. Priorizando a segurança e o conforto, a empresa oferece transporte planejado para eventos, fretamento empresarial e viagens escolares, conectando várias cidades do interior paulista, como Sumaré e Indaiatuba.
-A frota da Scatur é variada, contando com ônibus, micro-ônibus e vans, todos equipados com comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma viagem agradável.
-Os serviços de viagem da Scatur podem ser reservados de maneira prática e segura por meio da Buser, que disponibiliza um processo digital eficiente.</t>
+          <t>Fundada em Americana, São Paulo, a Viação Clewis é uma empresa reconhecida pela segurança e conforto que oferece em seus serviços de fretamento e turismo, sempre em conformidade com as diretrizes da ANTT (Agência Nacional de Transportes Terrestres).
+Com 45 anos de experiência, a empresa conecta cidades importantes, como São Paulo e Campinas, e também disponibiliza serviços de transporte escolar e locação de veículos.
+Sua frota é composta por ônibus e micro-ônibus modernos, incluindo modelos Mascarello e Marcopolo Paradiso, todos equipados com ar-condicionado e poltronas reclináveis para garantir uma viagem agradável.
+Para reservar suas viagens com a Viação Clewis, você pode utilizar a Buser, que oferece um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Scatur pela Buser e desfrute de praticidade e segurança.
-A Scatur se destaca no fretamento para turismo, além de oferecer serviços de transporte escolar e empresarial, com soluções adaptadas às diversas necessidades de deslocamento.
-Ao garantir sua viagem de ônibus da Scatur na Buser, você tem acesso a atendimento 24 horas, uma experiência de viagem segura e a conveniência da remarcação, que torna seus planos ainda mais flexíveis.</t>
+          <t>Reserve sua viagem com a Viação Clewis diretamente na Buser, proporcionando praticidade e segurança.
+A Viação Clewis é especializada em fretamento e turismo, oferecendo serviços de transporte de passageiros em várias rotas no interior de São Paulo e conexões com a capital.
+Ao reservar sua viagem de ônibus da Viação Clewis na Buser, você conta com atendimento disponível 24 horas, poltronas confortáveis e um processo de reserva totalmente online, o que torna sua experiência muito mais tranquila e acessível.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="120" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>actur-viagens</t>
+          <t>alianca</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Actur Viagens</t>
+          <t>Aliança ônibus</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fundada em Belo Horizonte, Minas Gerais, a Actur Viagens é uma empresa que se especializa no fretamento de veículos para turismo e eventos. Com autorização da ANTT, a empresa se destaca pela sua confiabilidade e pela qualidade no transporte rodoviário.
-Com anos de experiência no setor, a Actur oferece serviços que abrangem transporte corporativo e turismo, realizando viagens em grupo, city tours e traslados para eventos. A empresa conecta diversas cidades, garantindo uma experiência de viagem memorável.
-Sua frota é composta por ônibus, micro-ônibus, vans e carros executivos, todos projetados para proporcionar conforto e segurança durante os trajetos.
-A Actur Viagens está disponível na Buser, permitindo que você reserve suas viagens de maneira prática e segura, através de um processo totalmente digital.</t>
+          <t>Fundada em um contexto de mobilidade urbana, a Aliança se destaca como uma empresa reconhecida pela ênfase na segurança e no conforto de suas operações de transporte rodoviário. Regulamentada pela ANTT, a empresa assegura que suas atividades estejam em conformidade nas rotas interestaduais.
+Com mais de três décadas de experiência, a Aliança conecta diversas cidades, proporcionando soluções práticas para quem busca uma viagem tranquila e confortável. O foco da empresa está na qualidade do serviço e no atendimento ao cliente.
+A frota da Aliança é composta por veículos projetados para oferecer conforto, com poltronas reclináveis e ar-condicionado, criando uma experiência agradável durante a viagem.
+Para planejar sua viagem com a Aliança, você pode utilizar a Buser, uma plataforma que facilita a compra e a reserva de suas viagens de forma 100% digital, promovendo praticidade e segurança.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Actur Viagens diretamente na Buser e tenha praticidade para todos os destinos.
-Especializada em fretamento e turismo, a Actur Viagens oferece transporte para eventos, excursões e traslados na região de Belo Horizonte.
-Ao reservar sua viagem de ônibus com a Actur Viagens na Buser, você desfruta de atendimento 24 horas, poltronas confortáveis e a facilidade de cancelar sem custos.
-Aproveite a flexibilidade e a segurança que a Buser proporciona, tornando sua experiência de viagem ainda mais tranquila e acessível.</t>
+          <t>Adquira sua viagem de ônibus da Aliança pela Buser, com toda a praticidade e segurança que você precisa.
+A Aliança se destaca no transporte de pessoas, proporcionando opções para diversas modalidades, incluindo fretamento e turismo.
+Optando pela Buser, você conta com atendimento 24 horas, poltronas confortáveis e a conveniência de comprar sua viagem de maneira totalmente online, sem nenhum transtorno.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="120" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>centauro-turismo</t>
+          <t>bruno-tur</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Centauro Turismo</t>
+          <t>Bruno Tur</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 30 de agosto de 1989, a Centauro Turismo, localizada em Belo Horizonte (MG), é uma empresa bem reconhecida no ramo de fretamento e turismo, operando com a autorização da ANTT (Agência Nacional de Transportes Terrestres).
-A Centauro Turismo se destaca pela variedade de serviços de aluguel de ônibus, micro-ônibus e vans, atendendo a necessidades de viagens corporativas, excursões e eventos, conectando diversas cidades em Minas Gerais e regiões adjacentes.
-Sua frota moderna conta com ônibus executivos, semi-leitos e modelos Double-Decker, todos equipados com ar-condicionado e poltronas reclináveis, proporcionando um agradável conforto durante a viagem.
-Para reservar sua viagem com a Centauro Turismo, você pode utilizar a Buser, um canal oficial que oferece um processo totalmente digital e seguro.</t>
+          <t>Fundada em 30 de agosto de 2019, a Bruno Tur, também conhecida como Nbs Turismo e Transporte, é uma empresa de transporte rodoviário de passageiros com sede em Goiânia, Goiás. Com autorização da ANTT, a empresa opera linhas regulares e realiza fretamento, destacando-se pela confiança que transmite no setor.
+A Bruno Tur conecta diversas cidades de Goiás, incluindo o trajeto entre Iporá e Goiânia, sempre priorizando o conforto e a segurança de seus passageiros durante as viagens.
+Sua frota é composta por veículos equipados com comodidades essenciais, focando no bem-estar dos viajantes.
+Para garantir sua passagem, você pode acessar a plataforma da Buser, que oferece um processo totalmente digital e seguro, combinando a tradição com a praticidade.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Centauro Turismo pela Buser e explore destinos incríveis com todo o conforto e segurança.
-A Centauro Turismo se destaca no fretamento e aluguel de ônibus, vans e micro-ônibus, atendendo a diversas necessidades como excursões, eventos e traslados especiais. Além disso, oferece pacotes turísticos feitos sob medida para você.
-Ao optar pela Buser, você desfruta de uma experiência prática e econômica, com atendimento disponível 24 horas, poltronas confortáveis e a flexibilidade de cancelamento grátis, proporcionando tranquilidade do início ao fim.</t>
+          <t>Reserve sua passagem de ônibus com a Bruno Tur na Buser e descubra como é fácil viajar com conforto.
+A Bruno Tur é uma empresa de transporte rodoviário que opera linhas regulares de ônibus e também realiza fretamento para turismo, conectando diversas localidades em Goiás e além.
+Ao optar pela Buser, você tem à disposição atendimento 24 horas, viagens seguras e a comodidade de remarcação, o que torna sua experiência de viagem mais tranquila e sem imprevistos.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="120" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>mactur-fretamentos</t>
+          <t>cantur-turismo</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Mactur Fretamentos</t>
+          <t>Cantur Turismo</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1990, a Mactur Fretamentos e Turismo está localizada em Valinhos, São Paulo, e possui mais de 30 anos de experiência no setor de transporte rodoviário, sendo regulamentada pela ANTT para operações interestaduais.
-A empresa oferece serviços de fretamento contínuo e eventual, conectando diversas cidades e destinos pelo Brasil, sempre priorizando o conforto e a segurança durante as viagens.
-Sua frota variada inclui ônibus convencionais, micro-ônibus e modelos Double Decker, todos com comodidades como ar-condicionado e Wi-Fi para garantir uma experiência agradável.
-Para viajar com a Mactur, você pode reservar diretamente pelo site da Buser, o que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada em Santa Catarina, a Cantur Turismo é uma empresa especializada em fretamento e serviços de turismo, destacando-se pela sua atuação no setor. Está registrada na ANTT (Agência Nacional de Transportes Terrestres), o que assegura a legalidade de suas operações.
+Com uma frota que conta com ônibus executivos e semi-leito, a Cantur prioriza o conforto e a segurança durante as viagens, atendendo a diversas rotas e destinos turísticos.
+Os veículos vêm equipados com comodidades como Wi-Fi e ar-condicionado, garantindo uma experiência agradável para os passageiros.
+Ao reservar sua viagem com a Cantur Turismo pela Buser, você une a tradição da empresa à praticidade de um processo totalmente digital.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Mactur Fretamentos diretamente pela Buser, onde você encontra comodidade e segurança.
-A Mactur Fretamentos e Turismo é uma empresa brasileira com mais de 30 anos de experiência, focada no fretamento de ônibus e no transporte para excursões e viagens em grupo, atuando em todo o Brasil.
-Ao realizar a reserva de sua viagem de ônibus com a Mactur Fretamentos na Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e a facilidade de cancelamento grátis, o que torna sua experiência ainda mais agradável.</t>
+          <t>Descubra a sua viagem de ônibus com a Cantur Turismo na Buser, aproveitando toda a comodidade que você merece.
+A Cantur Turismo se destaca no fretamento e turismo, proporcionando serviços de transporte rodoviário para excursões e viagens em grupo, com uma frota de ônibus confortáveis, ideal para longas distâncias.
+Ao reservar sua viagem pela Buser, você tem acesso a atendimento 24h, viagens seguras e cancelamento grátis, o que torna sua experiência mais tranquila e sem complicações.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="120" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>mf-turismo</t>
+          <t>espaco-turismo</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MF Turismo</t>
+          <t>Espaço Turismo</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Com mais de 15 anos de experiência, a MF Turismo é uma empresa respeitada no setor de fretamento e turismo, devidamente regulamentada pela ANTT para operar em rotas interestaduais.
-Focada em proporcionar experiências de viagem, tanto para turismo quanto para fretamentos empresariais, a empresa conecta diversas cidades, como Votuporanga e São José do Rio Preto, sempre com ênfase em conforto e segurança.
-A frota da MF Turismo conta com ônibus de grande porte, incluindo modelos Double Decker e semi-leito, que oferecem comodidades como ar-condicionado e poltronas reclináveis para uma viagem mais agradável.
-Para planejar sua viagem com a MF Turismo, você pode reservar pelo canal digital da Buser, que torna o processo simples e seguro.</t>
+          <t>Fundada em Salvador, a Espaço Turismo se destaca no setor de fretamento e turismo, sendo reconhecida por sua tradição em organizar viagens para grupos. A empresa possui autorização da ANTT, o que assegura que opera em conformidade com as normas de transporte rodoviário.
+Com mais de 30 anos de experiência, a Espaço Turismo conecta diversas cidades, oferecendo um diferencial em conforto e segurança em suas viagens.
+A frota é composta por veículos executivos e leito, todos equipados com Wi-Fi, poltronas reclináveis e ar-condicionado, garantindo uma experiência agradável ao longo do trajeto.
+Os interessados podem reservar suas viagens com a Espaço Turismo através da Buser, que disponibiliza um processo 100% digital e seguro para a realização de fretamentos.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a MF Turismo diretamente na Buser, desfrutando de praticidade e segurança.
-A MF Turismo se destaca como uma empresa especializada em fretamento e turismo, proporcionando transporte de passageiros para uma variedade de rotas. Sua frota é composta por ônibus de grande porte, micro-ônibus e vans, atendendo diferentes necessidades.
-Ao optar por uma viagem de ônibus da MF Turismo na Buser, você tem à disposição atendimento 24h, poltronas confortáveis e a facilidade de remarcação, assegurando uma experiência tranquila do início ao fim.</t>
+          <t>Descubra sua viagem de ônibus com a Espaço Turismo na Buser, onde conforto e praticidade se encontram.
+A Espaço Turismo é uma agência de viagens reconhecida por sua especialização em fretamento e turismo, proporcionando experiências memoráveis em uma variedade de destinos.
+Ao reservar sua viagem pela Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples, que torna tudo mais fácil e agradável.
+Com a Buser, você pode viajar com segurança e flexibilidade, contando com políticas de cancelamento grátis que se ajustam às suas necessidades.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="120" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>paraquett-turismo</t>
+          <t>expresso-cearense</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Paraquett Turismo</t>
+          <t>Expresso Cearense</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fundada há quase cinco anos, a Paraquett Turismo, com sede em Cabo Frio (RJ), se destaca no fretamento de ônibus, prestando serviços para excursões, eventos corporativos e transferências. A empresa é autorizada pela ANTT, o que assegura a qualidade nas suas operações.
-Voltada para o conforto dos passageiros, a frota da Paraquett conta com ônibus leito e semi-leito, equipados com poltronas reclináveis e banheiros. A empresa conecta diversas cidades da Região dos Lagos, oferecendo viagens seguras e agradáveis.
-Para planejar sua viagem com a Paraquett Turismo, você pode reservar seus serviços por meio da Buser, que disponibiliza um processo digital prático e seguro.</t>
+          <t>Fundada em uma data incerta, a Expresso Cearense se destaca no setor de fretamento e viagens rodoviárias, sendo regulada pela ANTT (Agência Nacional de Transportes Terrestres). Com uma tradição que remete a uma operadora histórica que atuava entre o Ceará e o Sudeste, a empresa mantém um registro ativo mais recente.
+A Expresso Cearense conecta estados como Ceará e São Paulo, oferecendo um diferencial em conforto e segurança durante suas viagens. Seus fretamentos atendem a diversas rotas e destinos, sempre com o compromisso de proporcionar uma boa experiência aos passageiros.
+Sua frota é composta por ônibus modernos, incluindo categorias como executivo e leito. Todos os veículos são equipados com comodidades como ar-condicionado, Wi-Fi e poltronas reclináveis, garantindo uma viagem agradável.
+Para viajar com a Expresso Cearense, você pode reservar sua viagem através da Buser, que disponibiliza um processo 100% digital, unindo a tradição da empresa à facilidade das reservas online.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Paraquett Turismo diretamente pela Buser e aproveite a praticidade e o conforto que oferecemos.
-A Paraquett Turismo é uma empresa dedicada ao fretamento de ônibus para viagens em grupo, excursões e eventos, localizada em Cabo Frio, no Rio de Janeiro.
-Ao reservar sua viagem de ônibus com a Paraquett Turismo na Buser, você conta com segurança, poltronas confortáveis e atendimento 24 horas, que tornam cada trajeto mais agradável e tranquilo.</t>
+          <t>Descubra sua viagem com a Expresso Cearense na Buser, onde conforto e praticidade são prioridades.
+A Expresso Cearense se destaca como uma empresa dedicada ao fretamento e ao turismo, proporcionando viagens que ligam diferentes regiões do Brasil com segurança e eficiência.
+Ao optar pela Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de reservar sua viagem de maneira prática e online, tornando cada momento ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="120" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>transpen</t>
+          <t>expresso-nogueira</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TRANSPEN</t>
+          <t>Expresso Nogueira</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1996, a Transpen Transporte Coletivo e Encomendas é uma empresa brasileira de transporte rodoviário de passageiros, conhecida por sua sólida atuação no setor e regulamentada pela ANTT.
-A empresa opera principalmente em rotas nos estados de São Paulo e Paraná, com um foco especial no conforto e na segurança das viagens.
-Sua frota é composta por ônibus das categorias convencional, executivo e leito-cama, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável para os passageiros.
-Para planejar sua viagem com a Transpen, você pode acessar a Buser, que disponibiliza um processo 100% digital, combinando a tradição com a praticidade na aquisição de passagens.</t>
+          <t>Fundada em Minas Gerais, a Expresso Nogueira é uma empresa de transporte rodoviário que se destaca na mobilidade urbana. Com regulamentação da ANTT, a empresa assegura segurança e confiabilidade em suas operações.
+Priorizando conforto e segurança, a Expresso Nogueira conecta diversas cidades de Minas Gerais, oferecendo serviços de transporte eficientes para seus passageiros.
+Sua frota é composta por veículos modernos, projetados para garantir uma experiência de viagem agradável, com comodidades como ar-condicionado e poltronas reclináveis.
+As passagens da Expresso Nogueira podem ser compradas de maneira prática e segura pela Buser, que combina tradição e inovação em um processo totalmente digital.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem de ônibus da TRANSPEN pela Buser e experimente a praticidade de viajar com conforto.
-A TRANSPEN é uma empresa brasileira que realiza o transporte rodoviário de passageiros, ligando cidades nos estados de São Paulo e Paraná, além de outras regiões.
-Na Buser, você encontra uma viagem segura, com preços acessíveis e poltronas confortáveis, proporcionando uma experiência tranquila e descomplicada.</t>
+          <t>Compre sua passagem de ônibus da Expresso Nogueira na Buser e desfrute de uma viagem confortável e segura.
+A Expresso Nogueira proporciona serviços de transporte rodoviário em Minas Gerais, conectando várias cidades de maneira eficiente e de qualidade.
+Ao escolher a Buser, você torna sua viagem ainda mais atrativa, com atendimento disponível 24 horas, preços acessíveis e a facilidade de remarcação.
+Viaje com serenidade e aproveite cada instante com a Expresso Nogueira, ciente de que sua experiência será segura e prática.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="120" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>bella-vita-transportes</t>
+          <t>gr-turismo</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Bella Vita Transportes</t>
+          <t>GR TURISMO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fundada em São Paulo, a Bella Vita Transportes é uma empresa de transporte rodoviário de passageiros com vasta experiência no setor. Regulamentada pela ANTT, a empresa assegura que suas operações interestaduais estejam em conformidade com as normas vigentes.
-A Bella Vita conecta estados importantes como São Paulo, Minas Gerais, Bahia, Sergipe, Paraná, Rio de Janeiro e Goiás, destacando-se pelo conforto e segurança que proporciona em suas viagens.
-Sua frota inclui ônibus das categorias convencional, semi-leito e leito, todos equipados com comodidades que garantem uma viagem tranquila, como ar-condicionado e poltronas reclináveis.
-Para reservar sua viagem com a Bella Vita, você pode utilizar a Buser. A plataforma oferece um processo 100% digital e seguro, combinando tradição e praticidade na compra de bilhetes.</t>
+          <t>Fundada em 1º de maio de 1996, a GR Turismo é uma empresa de transporte rodoviário conhecida pela sua atuação no fretamento e turismo, devidamente regulamentada pela ANTT (Agência Nacional de Transportes Terrestres).
+Com sede em Saquarema, Rio de Janeiro, a empresa se destaca ao oferecer serviços de transporte de passageiros em várias rotas, sempre com foco no conforto e na segurança dos viajantes.
+Sua frota é composta por ônibus modernos, nas categorias executivo e leito, que contam com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi.
+Para viajar com a GR Turismo, você pode reservar seu fretamento de maneira prática e segura através da Buser, que proporciona um processo totalmente digital.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem de ônibus com a Bella Vita Transportes pela Buser, desfrutando de praticidade e confiança.
-A Bella Vita Transportes é uma empresa brasileira que opera viagens de longa distância, ligando estados como São Paulo, Minas Gerais, Bahia, Sergipe, Paraná, Rio de Janeiro e Goiás, com uma variedade de categorias de conforto em veículos modernos.
-Optando pela Buser, você conta com uma viagem segura, atendimento disponível 24 horas e a facilidade de remarcar, o que torna sua experiência ainda mais tranquila e flexível.</t>
+          <t>Reserve sua viagem com a GR TURISMO diretamente pela Buser e aproveite a praticidade e o conforto que oferecemos.
+A GR TURISMO é uma empresa dedicada ao fretamento e ao turismo, proporcionando excursões e transporte de passageiros em várias regiões do Brasil.
+Ao reservar sua viagem de ônibus da GR TURISMO na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a opção de cancelamento grátis, o que torna sua experiência ainda mais agradável e segura.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="120" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>expresso-adamantina</t>
+          <t>gran-express</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Viação Nova</t>
+          <t>Gran Express</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fundada pela Expresso Adamantina, a Viação Nova é uma empresa de transporte rodoviário que atua no setor de viagens de passageiros. É reconhecida por disponibilizar bilhetes digitais e operar rotas intermunicipais e interestaduais. Sua atuação é regulamentada pela ANTT, assegurando que esteja alinhada com as normas do setor.
-A empresa conecta diversas cidades por meio de suas rotas, sempre priorizando o conforto e a segurança dos passageiros. Embora não haja informações específicas sobre a sede, a Viação Nova se destaca pela qualidade de seus serviços.
-A frota da Viação Nova é composta por veículos modernos, que oferecem comodidades como ar-condicionado e poltronas reclináveis, proporcionando uma experiência confortável durante toda a viagem.
-Os passageiros podem adquirir suas viagens com a Viação Nova através da plataforma digital da Buser, que oferece um processo totalmente digital, unindo a tradição da viação à conveniência das compras online.</t>
+          <t>Fundada em 2006, a Gran Express, também conhecida como Expresso Diamante Log, se destaca no setor de transporte rodoviário de passageiros e cargas, operando sob a regulamentação da ANTT (Agência Nacional de Transportes Terrestres).
+Com uma forte presença em Cuiabá (MT), a Gran Express já acumula mais de 17 anos de experiência, dedicando-se a viagens de fretamento e intermunicipais que conectam estados como Rondônia, Acre e Goiás.
+A frota da empresa é diversificada, com ônibus de diferentes categorias, como executivo e leito, que oferecem uma série de comodidades, incluindo ar-condicionado, Wi-Fi e poltronas reclináveis, tudo pensado para garantir um conforto extra durante suas viagens.
+Para planejar sua viagem com a Gran Express, você pode contar com a Buser, que disponibiliza um processo totalmente digital para reservas de fretamento, unindo a tradição da empresa com a praticidade na mobilidade.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Adquira sua viagem de ônibus da Viação Nova na Buser, com toda a praticidade e conforto que você merece.
-A Viação Nova é uma empresa de transporte rodoviário que disponibiliza bilhetes digitais para rotas intermunicipais e interestaduais, proporcionando uma experiência de viagem que é tanto eficiente quanto acessível.
-Ao fazer sua reserva pela Buser, você conta com atendimento 24 horas, a opção de cancelamento grátis e poltronas confortáveis, o que torna sua jornada ainda mais agradável e segura.</t>
+          <t>Reserve sua viagem com a Gran Express pela Buser e explore destinos incríveis com todo o conforto e segurança que você merece.
+A Gran Express se destaca no fretamento de ônibus para turismo e viagens em grupo, especialmente em Cuiabá, e oferece conexões com estados como Rondônia, Acre e Goiás.
+Ao optar por reservar sua viagem de ônibus com a Gran Express na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de fazer sua reserva online, o que torna toda a experiência muito mais tranquila.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="120" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>helly-tur</t>
+          <t>grecco</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Helly Tur</t>
+          <t>Grecco ônibus</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fundada há mais de 25 anos, a Helly Tur é uma empresa especializada em fretamento e turismo, com reconhecimento no setor de transporte rodoviário e autorização da ANTT para operar rotas interestaduais.
-Com sede em Franca, São Paulo, a empresa se destaca pela segurança e conforto que proporciona em suas viagens, conectando diversas cidades e estados.
-A frota da Helly Tur conta com veículos convencionais e executivos, todos equipados com ar-condicionado, Wi-Fi e poltronas reclináveis, proporcionando um trajeto agradável.
-Para viajar com a Helly Tur, você pode reservar sua viagem por meio da Buser, um canal que oferece um processo 100% digital e prático.</t>
+          <t>Fundada há várias décadas, a Grecco se destaca no setor de transporte rodoviário e opera sob a regulamentação da ANTT (Agência Nacional de Transportes Terrestres), o que assegura a segurança e a qualidade das operações interestaduais.
+Com um forte compromisso com o conforto e a segurança, a empresa conecta diversas cidades e estados, disponibilizando opções de transporte que se adaptam a diferentes perfis de viagem.
+A frota da Grecco conta com veículos de várias categorias, incluindo ônibus convencionais e executivos, todos equipados com comodidades como Wi-Fi, ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável durante o trajeto.
+Para quem deseja viajar com a Grecco, a aquisição das passagens pode ser feita de forma simples e rápida através da Buser, que oferece um processo 100% digital e seguro, combinando tradição com praticidade.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Helly Tur diretamente na Buser, desfrutando de praticidade e segurança.
-Com mais de 25 anos de experiência, a Helly Tur se destaca no setor de fretamento e turismo, oferecendo soluções de transporte para diversas ocasiões.
-Ao optar pela sua viagem de ônibus da Helly Tur na Buser, você tem acesso a um atendimento 24 horas, poltronas confortáveis e um processo de reserva totalmente online, garantindo que sua experiência seja agradável e descomplicada.</t>
+          <t>Reserve sua viagem de ônibus da Grecco na Buser e aproveite a praticidade e a segurança que oferecemos.
+A Grecco se destaca no transporte rodoviário, atuando tanto em linhas regulares quanto em fretamento, sempre priorizando o conforto dos passageiros.
+Ao optar pela Buser, você conta com uma viagem segura, poltronas confortáveis e um processo de compra totalmente online, tornando sua experiência de viagem mais fácil desde o início até o final.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="120" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>pioneira-transportes</t>
+          <t>maciel-turismo</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Pioneira Transportes</t>
+          <t>Maciel Turismo</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2008, a Pioneira Transportes e Logística, localizada em Hortolândia (SP), se destaca no setor de fretamento e turismo, oferecendo viagens em itinerários interestaduais. A empresa valoriza o conforto e a segurança, conectando diversas cidades com um serviço de alta qualidade.
-Com uma frota moderna e diversificada, a Pioneira conta com ônibus adaptados, equipados com infraestrutura adequada para garantir uma experiência agradável durante a viagem. Entre as comodidades disponíveis, estão ar-condicionado e poltronas reclináveis.
-Ao optar pela Pioneira Transportes, você pode reservar sua viagem de forma prática e segura através da Buser, que disponibiliza um processo totalmente digital e livre de taxas abusivas.</t>
+          <t>A Maciel é uma empresa de transporte rodoviário que atua no setor há vários anos e é reconhecida por sua regulamentação pela ANTT (Agência Nacional de Transportes Terrestres) para operações interestaduais.
+Com um foco em proporcionar viagens seguras e confortáveis, a Maciel conecta diversas cidades e estados, embora não tenha fornecido informações detalhadas sobre suas rotas.
+Sua frota conta com veículos de diferentes categorias, oferecendo aos passageiros comodidades como ar-condicionado e poltronas reclináveis, o que contribui para uma experiência agradável durante a viagem.
+Para viajar com a Maciel, você pode utilizar a Buser, que disponibiliza um processo 100% digital para a compra da sua viagem, combinando tradição e praticidade de forma eficiente.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Pioneira Transportes pela Buser e aproveite a praticidade e a segurança que oferecemos.
-A Pioneira Transportes se destaca no fretamento e turismo, disponibilizando opções de transporte para grupos e excursões em uma variedade de destinos.
-Ao escolher a Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e um processo de reserva completamente online, o que torna sua viagem ainda mais tranquila do começo ao fim.</t>
+          <t>Adquira sua viagem de ônibus da Maciel pela Buser e aproveite toda a praticidade que você busca.
+A Maciel é uma empresa dedicada ao transporte de passageiros, oferecendo serviços de fretamento e também operando em linhas regulares, ligando diversas regiões do Brasil.
+Ao optar pela Maciel na Buser, você desfruta de uma viagem segura, poltronas confortáveis e atendimento 24h, o que torna sua experiência de viagem tranquila do começo ao fim.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="120" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>praiatur</t>
+          <t>manaus-tur</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PRAIATUR</t>
+          <t>Manaus Tur</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fundada há mais de 45 anos, a PRAIATUR é uma destacada empresa de fretamento e turismo, reconhecida pela ANTT (Agência Nacional de Transportes Terrestres) por sua atuação no setor rodoviário.
-Com sede em Balneário Camboriú, SC, a PRAIATUR se destaca por oferecer viagens de qualidade, conectando diversos destinos em todo o Brasil, sempre priorizando o conforto e a segurança de seus passageiros.
-A frota da PRAIATUR conta com veículos das categorias Executivo e Leito, equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi, proporcionando uma experiência agradável durante a viagem.
-Para tornar suas viagens ainda mais fáceis, a PRAIATUR está disponível na Buser, permitindo que você reserve suas viagens de maneira 100% digital, com segurança e praticidade.</t>
+          <t>Fundada há muitos anos, a Manaus Tur é uma empresa respeitada no setor de transporte rodoviário, autorizada pela ANTT, o que assegura a segurança e a conformidade de suas operações interestaduais.
+Com um foco em conforto e segurança, a empresa conecta diversas cidades por meio de suas rotas, que atendem a diferentes necessidades de viagem, tanto para fretamento quanto para turismo.
+A frota da Manaus Tur é composta por veículos de várias categorias, oferecendo comodidades como ar-condicionado, poltronas reclináveis e sanitários, proporcionando uma experiência agradável durante suas viagens.
+Para embarcar com a Manaus Tur, você pode utilizar a plataforma da Buser, que proporciona um processo totalmente digital para a compra e reserva, unindo tradição e praticidade na hora de viajar.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a PRAIATUR diretamente na Buser e aproveite a praticidade e o conforto que oferecemos.
-A PRAIATUR é especializada em fretamento e turismo, proporcionando roteiros que ligam os principais destinos do Brasil com segurança e qualidade.
-Ao optar por uma viagem de ônibus da PRAIATUR na Buser, você conta com atendimento 24 horas, poltronas confortáveis e a facilidade de reservar online, tudo com rapidez e segurança.</t>
+          <t>Reserve sua viagem com a Manaus Tur diretamente na Buser e desfrute da praticidade de um serviço de fretamento especializado.
+A Manaus Tur se dedica ao fretamento e ao turismo, proporcionando transporte para eventos, excursões e viagens em grupo, sempre priorizando conforto e segurança.
+Ao escolher a Manaus Tur para sua viagem de ônibus na Buser, você tem acesso a atendimento 24 horas, a opção de cancelamento grátis e poltronas confortáveis, o que torna sua experiência ainda mais agradável.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="120" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>brasiltur</t>
+          <t>olympus-viagens</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Brasiltur</t>
+          <t>Olympus Viagens</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 2006, a Brasiltur Transporte e Turismo Ltda, com sede em Manaus (AM), se destaca pela qualidade no fretamento de viagens, atuando de acordo com as normas da ANTT. Com especialização em serviços de transporte para turismo, eventos e viagens de lazer, a empresa conecta diversas regiões do Brasil.
-A frota da Brasiltur é formada por veículos modernos, que incluem categorias como leito e semi-leito. Todos os ônibus são equipados com ar-condicionado e poltronas reclináveis, proporcionando conforto e segurança ao longo de toda a viagem.
-Para planejar sua viagem com a Brasiltur, você pode reservar seus serviços por meio da Buser, que oferece um processo totalmente digital, unindo a tradição da empresa com a praticidade de um único canal.</t>
+          <t>Fundada em 19 de junho de 2000, a Olympus Viagens e Turismo LTDA se destaca no setor de transporte rodoviário e é reconhecida pela ANTT (Agência Nacional de Transportes Terrestres) e pela certificação de qualidade ISO 9001.
+Com sede na região metropolitana de Belo Horizonte (MG), a empresa tem como foco o fretamento, oferecendo serviços intermunicipais, interestaduais e internacionais, conectando municípios como Betim e Contagem.
+A frota da Olympus é variada, com veículos projetados para atender diferentes tipos de viagem, garantindo conforto e segurança aos passageiros.
+Por meio da Buser, você pode reservar sua viagem com a Olympus Viagens, desfrutando de um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Brasiltur na Buser e aproveite o conforto de viajar de ônibus.
-A Brasiltur é uma empresa focada em fretamento e turismo, oferecendo opções de transporte ideais para excursões e viagens em grupo.
-Ao escolher a Buser, você conta com uma viagem segura, atendimento 24 horas e a praticidade da remarcação, o que torna sua experiência mais tranquila e conveniente.
-Além disso, a Brasiltur disponibiliza poltronas confortáveis, assegurando que cada trajeto seja agradável e relaxante.</t>
+          <t>Reserve sua viagem com a Olympus Viagens pela Buser e desfrute de toda a comodidade e segurança que oferecemos.
+A Olympus Viagens é uma empresa focada em fretamento de ônibus e turismo, localizada em Belo Horizonte, com uma forte presença na região metropolitana.
+Ao optar pela Olympus Viagens na Buser, você conta com atendimento 24 horas, viagens seguras e poltronas confortáveis, o que torna sua experiência tranquila e agradável.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="120" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>condor-tur</t>
+          <t>soares-turismo</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Condor Tur</t>
+          <t>Soares Turismo</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Fundada em 1988, a Condor Tur Transporte e Turismo Ltda. é uma empresa bem estabelecida no setor de fretamento e turismo, regulamentada pela ANTT. Ela se destaca especialmente na operação de transporte escolar e fretamento contínuo.
-Com um compromisso com o conforto e a segurança, a Condor Tur atende principalmente as regiões de Mogi das Cruzes e Salesópolis, conectando cidades como Araraquara, Barretos e Catanduva.
-Sua frota é composta por ônibus executivos e escolares, que contam com comodidades como ar-condicionado e poltronas reclináveis, tudo pensado para oferecer uma experiência de viagem agradável.
-Para reservar uma viagem com a Condor Tur, os usuários podem acessar a Buser, que proporciona um processo totalmente digital e seguro.</t>
+          <t>Fundada em 1980, a Soares Turismo é uma empresa de transporte rodoviário que se destaca no fretamento e turismo, regulamentada pela ANTT. Com uma forte presença na Região Nordeste, a empresa liga diversas cidades por meio de suas rotas intermunicipais e interestaduais.
+A Soares Turismo dispõe de uma frota moderna, priorizando o conforto e a segurança dos passageiros, com um mix de ônibus clássicos e contemporâneos bem cuidados. É reconhecida por seu compromisso com a qualidade nas viagens.
+Os veículos oferecem opções com poltronas reclináveis e ar-condicionado, garantindo uma experiência agradável para todos os viajantes.
+Para reservar sua viagem com a Soares Turismo, você pode utilizar a Buser, que proporciona um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Agende sua viagem com a Condor Tur pela Buser e aproveite todo o conforto e segurança que oferecemos.
-A Condor Tur é uma empresa dedicada ao fretamento e turismo, com foco nas regiões de Mogi das Cruzes, Salesópolis e interior paulista. Nossos serviços incluem transporte escolar e viagens em grupo, sempre com atenção às suas necessidades.
-Ao agendar sua viagem de ônibus da Condor Tur na Buser, você tem acesso a um atendimento disponível 24 horas, poltronas confortáveis e a conveniência de um processo de reserva totalmente online.</t>
+          <t>Reserve sua viagem com a Soares Turismo diretamente pela Buser e desfrute de praticidade e segurança.
+A Soares Turismo se destaca como uma empresa dedicada ao fretamento e ao turismo, oferecendo transporte rodoviário de passageiros em rotas intermunicipais e interestaduais, especialmente na Região Nordeste do Brasil.
+Ao escolher a Buser, você encontra ainda mais benefícios: atendimento 24 horas, poltronas confortáveis e a conveniência de reservar online, tudo pensado para que sua experiência seja tranquila e econômica.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="120" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>demp-turismo</t>
+          <t>tiquin</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Demp Turismo</t>
+          <t>Tiquin ônibus</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fundada em setembro de 2008, a Demp Turismo se destacou no setor de transporte rodoviário, especialmente pelo seu serviço de fretamento de viagens para artistas e eventos. A empresa é reconhecida por operar com autorização da ANTT, o que assegura segurança e confiabilidade em suas operações.
-Com sede em Aparecida de Goiânia (GO), a Demp Turismo conecta diversas cidades e oferece fretamentos contínuos e eventuais para empresas, igrejas e famílias. Um dos seus principais diferenciais é a qualidade no transporte de bandas e artistas, sempre priorizando o conforto durante as viagens.
-Sua frota conta com ônibus executivos personalizados, equipados com poltronas reclináveis, Wi-Fi, ar-condicionado, tomadas USB e TVs, proporcionando uma experiência agradável aos passageiros.
-Para viajar com a Demp Turismo, você pode reservar serviços de fretamento através da Buser, que disponibiliza um processo digital prático e seguro, ideal para uma viagem tranquila.</t>
+          <t>Com mais de 30 anos de experiência, a Tiquin se destaca como uma empresa de transporte rodoviário especializada no fretamento de viagens, sempre respeitando as normas da ANTT (Agência Nacional de Transportes Terrestres).
+A atuação da Tiquin é centrada na região Sul do Brasil, onde conecta diversas cidades, proporcionando conforto e segurança aos passageiros durante suas jornadas.
+Sua frota conta com veículos equipados com poltronas reclináveis, ar-condicionado e Wi-Fi, oferecendo uma experiência de viagem bastante agradável.
+Para quem deseja explorar novos destinos, é possível reservar viagens com a Tiquin por meio da Buser, que oferece um processo totalmente digital e prático, combinando tradição e inovação.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Demp Turismo diretamente pela Buser e desfrute de praticidade e conforto.
-A Demp Turismo se destaca no fretamento de ônibus, atendendo bandas, eventos e turismo em Goiás, sempre priorizando a experiência do cliente.
-Optar pela Demp Turismo na Buser significa embarcar em uma viagem segura, com poltronas confortáveis e a facilidade de um atendimento 24 horas, o que torna sua experiência ainda mais agradável.</t>
+          <t>Reserve sua viagem com a Tiquin na Buser e desfrute de toda a comodidade que você merece.
+A Tiquin se destaca no setor de fretamento e turismo, oferecendo serviços de transporte para grupos em várias regiões do Brasil.
+Ao reservar sua viagem de ônibus da Tiquin na Buser, você tem acesso a atendimento 24h, poltronas confortáveis e um processo totalmente online, que facilita sua experiência.
+Viajar com a Tiquin pela Buser proporciona segurança e flexibilidade, garantindo uma experiência tranquila do início ao fim.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="120" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>livre-transportes</t>
+          <t>viacao-irmaos-teixeira</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Livre Transportes</t>
+          <t>Viação Irmãos Teixeira</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Fundada em São Paulo, a Livre Transportes é uma empresa que se destaca no fretamento, sendo reconhecida pela sua atuação confiável e segura no transporte rodoviário coletivo de passageiros, sempre em conformidade com as regulamentações da ANTT.
-Com uma frota que abrange ônibus de grande porte, a empresa oferece viagens confortáveis ligando a região do Grande ABC a diversos destinos em São Paulo. Além disso, disponibiliza serviços para eventos e excursões em todo o Brasil.
-Os veículos são equipados com ar-condicionado, Wi-Fi, poltronas reclináveis e banheiro, assegurando uma experiência agradável e segura durante as viagens.
-Para tornar tudo mais fácil, a Livre Transportes pode ser encontrada na Buser, onde você pode reservar suas viagens de forma prática e totalmente digital.</t>
+          <t>Fundada em 1951, a Viação Irmãos Teixeira, popularmente conhecida como Teixeira Turismo, é uma empresa tradicional no transporte rodoviário de passageiros, com autorização da ANTT. Ela se destaca por sua atuação entre Belo Horizonte e municípios do Centro-Oeste de Minas Gerais, como Divinópolis e Itaúna, além de operar linhas intermunicipais em localidades como Formiga e Arcos.
+A frota da Viação Irmãos Teixeira é composta por ônibus convencionais e executivos, proporcionando conforto e segurança aos passageiros, com recursos como ar-condicionado e poltronas reclináveis.
+Para viajar com a Viação Irmãos Teixeira, você pode comprar sua passagem de maneira prática e segura pela Buser, que oferece um processo 100% digital, combinando tradição e inovação.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Livre Transportes através da Buser e desfrute de conforto e praticidade.
-A Livre Transportes é uma empresa que se destaca no fretamento de ônibus e micro-ônibus, oferecendo serviços para turismo, eventos e transporte corporativo em todo o Brasil.
-Ao reservar sua viagem de ônibus da Livre Transportes na Buser, você tem acesso a atendimento 24h, viagens seguras e poltronas confortáveis, o que torna cada deslocamento mais tranquilo e agradável.</t>
+          <t>Adquira sua passagem de ônibus da Viação Irmãos Teixeira na Buser, desfrutando de praticidade e segurança.
+A Viação Irmãos Teixeira opera linhas regulares de ônibus e também realiza fretamento para excursões, conectando várias cidades de Minas Gerais com um serviço de alta qualidade.
+Ao comprar sua passagem pela Buser, você usufrui de uma viagem segura, com atendimento disponível 24 horas e a facilidade de remarcação, proporcionando tranquilidade em todo o trajeto.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="120" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>miramar-turismo</t>
+          <t>viacao-serra-azul</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MIRAMAR TURISMO</t>
+          <t>Viação Serra Azul</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Fundada há anos, a Miramar Turismo é uma empresa bem estabelecida no setor de fretamento e turismo, com autorização da ANTT (Agência Nacional de Transportes Terrestres) para operar em rotas interestaduais. A empresa se destaca pela sua vasta experiência na oferta de pacotes de viagens para diversos destinos.
-A Miramar Turismo conecta cidades como Curitiba, Foz do Iguaçu e Marília, sempre priorizando a segurança e o conforto dos passageiros durante as viagens. 
-Sua frota é moderna e conta com diferentes categorias de veículos, que proporcionam comodidades como ar-condicionado e poltronas reclináveis para uma experiência agradável. 
-Ao reservar sua viagem com a Miramar Turismo, você pode contar com a Buser, que oferece um processo totalmente digital e seguro.</t>
+          <t>Fundada há mais de 20 anos, a Viação Serra Azul se destaca no setor de fretamento e turismo, operando com autorização da ANTT (Agência Nacional de Transportes Terrestres). 
+Com uma forte presença no Rio Grande do Sul, a empresa disponibiliza serviços de transporte para eventos e passeios, conectando localidades como Marau, Passo Fundo, Santa Rosa e Gravataí, além de atuar em regiões como Rondônia. 
+A frota da Viação Serra Azul é composta por ônibus executivos, semi-leitos e leitos, proporcionando conforto e comodidades como ar-condicionado e poltronas reclináveis. 
+Para realizar sua viagem com a Viação Serra Azul, você pode reservar através da plataforma digital da Buser, que oferece um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a MIRAMAR TURISMO pela Buser e explore destinos incríveis com total comodidade.
-A MIRAMAR TURISMO é uma agência focada em fretamento e turismo, disponibilizando pacotes de viagens nacionais e internacionais para os melhores roteiros.
-Ao reservar sua viagem de ônibus da MIRAMAR TURISMO na Buser, você desfruta de atendimento 24 horas, cancelamento grátis e poltronas confortáveis, proporcionando uma experiência tranquila e agradável do início ao fim.</t>
+          <t>Reserve sua viagem com a Viação Serra Azul diretamente na Buser e desfrute de conforto e praticidade.
+A Viação Serra Azul se dedica ao fretamento e turismo, disponibilizando transporte para empresas, eventos e passeios. Sua frota é variada e inclui desde ônibus executivos até vans.
+Ao agendar sua viagem de ônibus com a Viação Serra Azul na Buser, você tem à disposição atendimento 24 horas, poltronas confortáveis e a facilidade de remarcação, o que torna sua experiência ainda mais conveniente.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="120" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>novos-rumos-turismo</t>
+          <t>busmar</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Novos Rumos Turismo</t>
+          <t>Busmar ônibus</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Fundada em agosto de 2012 em Juiz de Fora, Minas Gerais, a Novos Rumos Turismo é conhecida pela sua tradição no transporte rodoviário, atuando de acordo com as normas da ANTT para fretamento interestadual.
-A empresa prioriza conforto e segurança, oferecendo fretamento contínuo e eventual para grupos, escolas, igrejas e empresas, com opções de viagens que vão desde o município até rotas intermunicipais e interestaduais.
-A frota da Novos Rumos conta com ônibus e vans equipados, proporcionando aos passageiros comodidades essenciais durante as viagens, como ar-condicionado e poltronas confortáveis.
-Para viajar com a Novos Rumos Turismo, você pode reservar suas viagens de maneira prática e segura por meio da Buser, que simplifica o processo digital de fretamentos.</t>
+          <t>Fundada em Maraú, no Rio Grande do Sul, a Busmar Tours é uma empresa bem estabelecida no setor de fretamento rodoviário, autorizada pela ANTT para operar viagens tanto nacionais quanto internacionais.
+Com mais de dez anos de experiência, a Busmar se destaca pelo conforto e pela qualidade de seus serviços, oferecendo rotas que conectam diversas regiões do Brasil, com foco em viagens de longa distância.
+Sua frota conta com ônibus de dois andares e diferentes categorias, como leito e semi-leito, todos equipados com comodidades como ar-condicionado, poltronas reclináveis e Wi-Fi.
+Para reservar sua viagem com a Busmar, você pode usar a Buser, que proporciona um processo totalmente digital e seguro.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Reserve sua viagem com a Novos Rumos Turismo diretamente na Buser e desfrute de conforto e praticidade.
-A Novos Rumos Turismo se destaca no fretamento de ônibus e vans para excursões, atendendo grupos, famílias e empresas na região de Juiz de Fora, Minas Gerais.
-Ao reservar sua viagem de ônibus com a Novos Rumos Turismo pela Buser, você tem à disposição uma experiência segura, atendimento 24h e a facilidade de remarcação, o que torna seu planejamento muito mais tranquilo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>gimenes-turismo</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Gimenes Turismo</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Com mais de 40 anos de atuação, a Gimenes Turismo é uma empresa familiar que se destaca pela confiabilidade e qualidade em fretamento para viagens, com foco especial em São Paulo, oferecendo serviços de bate e volta para compras e negócios. Autorizada pela ANTT, a Gimenes prioriza a segurança e o conforto de seus passageiros.&lt;br&gt;&lt;br&gt;A frota da empresa é moderna e conta com ônibus equipados para garantir uma viagem agradável, incluindo poltronas reclináveis, ar-condicionado e Wi-Fi a bordo.&lt;br&gt;&lt;br&gt;Ao escolher a Gimenes, você pode reservar suas viagens de maneira prática e segura por meio da Buser, que proporciona um processo 100% digital, combinando tradição e inovação.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Reserve sua viagem de ônibus com a Gimenes Turismo na Buser e aproveite toda a comodidade que você merece.&lt;br&gt;&lt;br&gt;A Gimenes Turismo é uma empresa familiar que se destaca no fretamento de ônibus para excursões, eventos e viagens em grupo. Ela também oferece transporte de encomendas entre São Paulo e Franca.&lt;br&gt;&lt;br&gt;Ao realizar sua reserva pela Buser, você tem à disposição um atendimento 24 horas, viagens seguras e poltronas confortáveis, proporcionando o máximo de conforto e tranquilidade durante o seu trajeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>bompani-turismo</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Bompani Turismo</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Fundada em 2013, a Bompani Turismo é uma empresa de fretamento rodoviário situada em Luiz Alves, Santa Catarina. Com um forte foco em agenciamento de viagens, a empresa opera com a autorização da ANTT, o que assegura qualidade e segurança em suas operações.&lt;br&gt;&lt;br&gt;A Bompani se especializa em oferecer viagens personalizadas e excursões de turismo, conectando uma variedade de cidades e destinos. Um de seus grandes diferenciais é o conforto, que a destaca na realização de roteiros turísticos tanto regionais quanto internacionais.&lt;br&gt;&lt;br&gt;Sua frota é composta por veículos bem equipados, que oferecem comodidades como ar-condicionado e poltronas reclináveis, garantindo uma experiência agradável ao longo da viagem.&lt;br&gt;&lt;br&gt;Para reservar sua viagem com a Bompani, você pode usar a Buser, que proporciona um processo totalmente digital e seguro para reservar fretamentos de maneira prática e eficiente.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Reserve sua viagem com a Bompani Turismo diretamente pela Buser, garantindo praticidade e confiança em cada etapa.&lt;br&gt;&lt;br&gt;A Bompani Turismo é especializada em fretamento de ônibus para turismo, oferecendo roteiros regionais, excursões e viagens de compras com todo o conforto e segurança que você merece.&lt;br&gt;&lt;br&gt;Ao reservar sua viagem de ônibus com a Bompani Turismo na Buser, você tem à disposição atendimento 24 horas, um trajeto seguro e a possibilidade de cancelamento grátis, tornando sua experiência ainda mais tranquila.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>jacson-turismo</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Jacson Turismo</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Fundada em Chapecó, Santa Catarina, a Jacson Turismo é uma empresa bem estabelecida no setor de transporte rodoviário, com autorização da ANTT para realizar fretamentos interestaduais.&lt;br&gt;&lt;br&gt;A companhia se destaca por oferecer viagens regulares direcionadas a lojistas e compradores, interligando cidades como São Paulo, Brusque e Criciúma, com saídas programadas em dias específicos da semana.&lt;br&gt;&lt;br&gt;Sua frota é composta por ônibus leito, que proporcionam conforto e comodidade ao longo das viagens, além de contar com serviços como café da manhã e suporte para o transporte de mercadorias.&lt;br&gt;&lt;br&gt;As viagens podem ser reservadas de maneira prática e segura por meio da Buser, uma parceria que combina a tradição da Jacson Turismo com a conveniência do processo digital.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Garanta a sua viagem com a Jacson Turismo através da Buser, aproveitando toda a praticidade que você deseja.&lt;br&gt;&lt;br&gt;A Jacson Turismo é uma empresa de transporte rodoviário focada em fretamento, com roteiros que levam você a polos atacadistas, como São Paulo, Brusque e Criciúma.&lt;br&gt;&lt;br&gt;Ao reservar sua viagem de ônibus com a Jacson Turismo na Buser, você conta com atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples, tornando sua experiência ainda mais agradável.</t>
+          <t>Reserve sua viagem com a Busmar diretamente na Buser e desfrute de uma experiência prática e segura.
+A Busmar se destaca no fretamento rodoviário e turismo, proporcionando viagens nacionais e internacionais em ônibus confortáveis e modernos.
+Ao reservar sua viagem de ônibus com a Busmar na Buser, você conta com atendimento 24 horas, preços acessíveis e a conveniência de um processo de reserva totalmente online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="120" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>c-r-santos-transportes</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>C R SANTOS TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Fundada há várias décadas, a C R Santos Transportes é uma empresa respeitada no setor de transporte rodoviário e opera de acordo com a regulamentação da ANTT. Sua dedicação à qualidade a torna uma opção confiável para os viajantes.
+A empresa cobre diversas rotas, priorizando sempre o conforto e a segurança durante as viagens. Embora a localização exata de sua sede não esteja clara, é amplamente reconhecida por conectar importantes cidades e estados.
+A frota da C R Santos Transportes é composta por veículos modernos que oferecem categorias voltadas para o conforto, incluindo poltronas reclináveis e ar-condicionado. Em algumas unidades, os passageiros também podem encontrar Wi-Fi e tomadas disponíveis.
+Para quem deseja viajar com a C R Santos Transportes, a Buser oferece um processo totalmente digital, que combina a tradição do transporte com a praticidade necessária para facilitar sua viagem.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a C R SANTOS TRANSPORTES diretamente na Buser, desfrutando de praticidade e confiança.
+Especializada em fretamento, a C R SANTOS TRANSPORTES oferece soluções de transporte para excursões e viagens em grupo, sempre priorizando o conforto e a segurança dos passageiros.
+Com a Buser, você tem acesso a atendimento 24h, viagens seguras e a opção de cancelamento grátis, o que torna sua experiência ainda mais tranquila e flexível.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="120" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>viagens-chapeco</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Viagens Chapecó</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em 1981, a Viagens Chapecó Transporte e Turismo é uma empresa com forte tradição no setor de fretamento e turismo, reconhecida na Região Oeste de Santa Catarina e devidamente autorizada pela ANTT.
+Com mais de 40 anos de experiência, a empresa se destaca ao disponibilizar serviços de fretamento e pacotes de viagem para diversos destinos, tanto nacionais quanto internacionais, incluindo passeios pela América do Sul.
+Sua frota moderna conta com ônibus de última geração, como os impressionantes modelos de dois andares Paradiso Double Decker, que garantem conforto e segurança aos passageiros.
+Para reservar sua viagem com a Viagens Chapecó, você pode acessar a plataforma digital da Buser, que proporciona um processo totalmente digital e seguro.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a Viagens Chapecó diretamente pela Buser e desfrute de praticidade e conforto.
+Especializada em fretamento e turismo, a Viagens Chapecó oferece pacotes completos para diversos destinos, tanto nacionais quanto internacionais, contando com uma frota moderna e de alta qualidade.
+Ao escolher a Buser, sua experiência de viagem se torna ainda mais vantajosa. Você tem acesso a atendimento 24h, poltronas confortáveis e a facilidade de remarcação, o que torna tudo mais tranquilo e flexível.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="120" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>vip-brasil</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>VIP Brasil</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Fundada em Goiânia (GO), a Viação VIP Brasil se destaca no setor de fretamento e turismo, seguindo as diretrizes da ANTT (Agência Nacional de Transportes Terrestres). A empresa conecta Goiânia a São Paulo e a vários destinos em estados como Pará, Tocantins e Maranhão.
+A VIP Brasil proporciona uma experiência de viagem única, com um forte compromisso com o conforto e a segurança dos passageiros. Sua frota inclui ônibus leito total e leito-cama, todos equipados com ar-condicionado, água mineral, banheiros e tomadas USB, garantindo comodidade durante a viagem.
+Para viajar com a VIP Brasil, você pode reservar através da Buser, que oferece um processo digital simples e seguro, combinando a tradição da empresa com a conveniência dos serviços online.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Reserve sua viagem com a VIP Brasil diretamente na Buser e desfrute de conforto e praticidade.
+Especializada em fretamento e turismo, a VIP Brasil oferece transporte para diversos destinos, incluindo São Paulo, Pará, Tocantins e Maranhão, com ênfase em viagens voltadas para compras e turismo.
+Ao reservar sua viagem de ônibus da VIP Brasil na Buser, você tem acesso a atendimento 24 horas, poltronas confortáveis e um processo de reserva online simples, tudo pensado para garantir que sua experiência seja ainda mais prazerosa.</t>
         </is>
       </c>
     </row>
